--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -5320,7 +5320,7 @@
         <v>136261113</v>
       </c>
       <c r="B43" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>136346850</v>
       </c>
       <c r="B44" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>136346893</v>
       </c>
       <c r="B45" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>136557175</v>
       </c>
       <c r="B46" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>136258592</v>
       </c>
       <c r="B53" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>136422293</v>
       </c>
       <c r="B54" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>136631756</v>
       </c>
       <c r="B55" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>136631891</v>
       </c>
       <c r="B56" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>136631926</v>
       </c>
       <c r="B78" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>136557135</v>
       </c>
       <c r="B81" t="n">
-        <v>91588</v>
+        <v>91590</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>136635740</v>
       </c>
       <c r="B82" t="n">
-        <v>91588</v>
+        <v>91590</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>136258570</v>
       </c>
       <c r="B88" t="n">
-        <v>92780</v>
+        <v>92783</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>136422316</v>
       </c>
       <c r="B89" t="n">
-        <v>92780</v>
+        <v>92783</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>136557228</v>
       </c>
       <c r="B90" t="n">
-        <v>92780</v>
+        <v>92783</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>136329900</v>
       </c>
       <c r="B225" t="n">
-        <v>106483</v>
+        <v>106486</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>136422457</v>
       </c>
       <c r="B226" t="n">
-        <v>106483</v>
+        <v>106486</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>136347172</v>
       </c>
       <c r="B239" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>136394245</v>
       </c>
       <c r="B240" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -5320,7 +5320,7 @@
         <v>136261113</v>
       </c>
       <c r="B43" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>136346850</v>
       </c>
       <c r="B44" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>136346893</v>
       </c>
       <c r="B45" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>136557175</v>
       </c>
       <c r="B46" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>136258592</v>
       </c>
       <c r="B53" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>136422293</v>
       </c>
       <c r="B54" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>136631756</v>
       </c>
       <c r="B55" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>136631891</v>
       </c>
       <c r="B56" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>136631926</v>
       </c>
       <c r="B78" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>136258570</v>
       </c>
       <c r="B88" t="n">
-        <v>92783</v>
+        <v>92784</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>136422316</v>
       </c>
       <c r="B89" t="n">
-        <v>92783</v>
+        <v>92784</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>136557228</v>
       </c>
       <c r="B90" t="n">
-        <v>92783</v>
+        <v>92784</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>136329900</v>
       </c>
       <c r="B225" t="n">
-        <v>106486</v>
+        <v>106487</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>136422457</v>
       </c>
       <c r="B226" t="n">
-        <v>106486</v>
+        <v>106487</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>136347172</v>
       </c>
       <c r="B239" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>136394245</v>
       </c>
       <c r="B240" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -5320,7 +5320,7 @@
         <v>136261113</v>
       </c>
       <c r="B43" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>136346850</v>
       </c>
       <c r="B44" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>136346893</v>
       </c>
       <c r="B45" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>136557175</v>
       </c>
       <c r="B46" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>136258592</v>
       </c>
       <c r="B53" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>136422293</v>
       </c>
       <c r="B54" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>136631756</v>
       </c>
       <c r="B55" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>136631891</v>
       </c>
       <c r="B56" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>136631926</v>
       </c>
       <c r="B78" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>136557135</v>
       </c>
       <c r="B81" t="n">
-        <v>91592</v>
+        <v>91594</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>136635740</v>
       </c>
       <c r="B82" t="n">
-        <v>91592</v>
+        <v>91594</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>136778691</v>
       </c>
       <c r="B87" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>136778733</v>
       </c>
       <c r="B88" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>136258570</v>
       </c>
       <c r="B90" t="n">
-        <v>92789</v>
+        <v>92791</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>136422316</v>
       </c>
       <c r="B91" t="n">
-        <v>92789</v>
+        <v>92791</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>136557228</v>
       </c>
       <c r="B92" t="n">
-        <v>92789</v>
+        <v>92791</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>136329900</v>
       </c>
       <c r="B236" t="n">
-        <v>106492</v>
+        <v>106494</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
         <v>136422457</v>
       </c>
       <c r="B237" t="n">
-        <v>106492</v>
+        <v>106494</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>136347172</v>
       </c>
       <c r="B250" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>136394245</v>
       </c>
       <c r="B251" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ272"/>
+  <dimension ref="A1:AZ273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18400,32 +18400,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>136346869</v>
+        <v>136973330</v>
       </c>
       <c r="B158" t="n">
-        <v>58164</v>
+        <v>58169</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18443,13 +18443,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>687222</v>
+        <v>686764</v>
       </c>
       <c r="R158" t="n">
-        <v>6563288</v>
+        <v>6562843</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18473,12 +18473,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18504,13 +18504,13 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136346869</t>
+          <t>https://artportalen.se/Sighting/136973330</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>136631771</v>
+        <v>136346869</v>
       </c>
       <c r="B159" t="n">
         <v>58164</v>
@@ -18553,13 +18553,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>686948</v>
+        <v>687222</v>
       </c>
       <c r="R159" t="n">
-        <v>6563152</v>
+        <v>6563288</v>
       </c>
       <c r="S159" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18583,12 +18583,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18614,16 +18614,16 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136631771</t>
+          <t>https://artportalen.se/Sighting/136346869</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121859656</v>
+        <v>136631771</v>
       </c>
       <c r="B160" t="n">
-        <v>5199</v>
+        <v>58164</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18631,16 +18631,16 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>105930</v>
+        <v>103023</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -18649,19 +18649,27 @@
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>687094</v>
+        <v>686948</v>
       </c>
       <c r="R160" t="n">
-        <v>6563235</v>
+        <v>6563152</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18685,22 +18693,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18711,48 +18709,28 @@
       </c>
       <c r="AG160" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL160" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859656</t>
+          <t>https://artportalen.se/Sighting/136631771</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126061088</v>
+        <v>121859656</v>
       </c>
       <c r="B161" t="n">
         <v>5199</v>
@@ -18783,14 +18761,14 @@
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>686865</v>
+        <v>687094</v>
       </c>
       <c r="R161" t="n">
-        <v>6562977</v>
+        <v>6563235</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18817,22 +18795,22 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18856,12 +18834,12 @@
       </c>
       <c r="AL161" t="inlineStr">
         <is>
-          <t>Klen torr granlåga.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>Picea abies # Klen torr granlåga.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr"/>
@@ -18872,19 +18850,19 @@
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061088</t>
+          <t>https://artportalen.se/Sighting/121859656</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126061109</v>
+        <v>126061088</v>
       </c>
       <c r="B162" t="n">
         <v>5199</v>
@@ -18919,10 +18897,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>686946</v>
+        <v>686865</v>
       </c>
       <c r="R162" t="n">
-        <v>6562741</v>
+        <v>6562977</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18954,7 +18932,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18964,7 +18942,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19004,22 +18982,22 @@
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061109</t>
+          <t>https://artportalen.se/Sighting/126061088</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121859629</v>
+        <v>126061109</v>
       </c>
       <c r="B163" t="n">
-        <v>8455</v>
+        <v>5199</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19027,34 +19005,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>686792</v>
+        <v>686946</v>
       </c>
       <c r="R163" t="n">
-        <v>6563030</v>
+        <v>6562741</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19081,22 +19059,22 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19110,17 +19088,22 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL163" t="inlineStr">
+        <is>
+          <t>Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr"/>
@@ -19131,19 +19114,19 @@
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859629</t>
+          <t>https://artportalen.se/Sighting/126061109</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121859631</v>
+        <v>121859629</v>
       </c>
       <c r="B164" t="n">
         <v>8455</v>
@@ -19178,10 +19161,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>686934</v>
+        <v>686792</v>
       </c>
       <c r="R164" t="n">
-        <v>6563148</v>
+        <v>6563030</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19213,7 +19196,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -19223,7 +19206,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19264,13 +19247,13 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859631</t>
+          <t>https://artportalen.se/Sighting/121859629</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>122929535</v>
+        <v>121859631</v>
       </c>
       <c r="B165" t="n">
         <v>8455</v>
@@ -19298,29 +19281,20 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>686612</v>
+        <v>686934</v>
       </c>
       <c r="R165" t="n">
-        <v>6562882</v>
+        <v>6563148</v>
       </c>
       <c r="S165" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -19344,22 +19318,22 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19370,31 +19344,46 @@
       </c>
       <c r="AG165" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929535</t>
+          <t>https://artportalen.se/Sighting/121859631</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>136259916</v>
+        <v>122929535</v>
       </c>
       <c r="B166" t="n">
-        <v>8463</v>
+        <v>8455</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19419,29 +19408,29 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>686457</v>
+        <v>686612</v>
       </c>
       <c r="R166" t="n">
-        <v>6563062</v>
+        <v>6562882</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19465,12 +19454,22 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19479,34 +19478,33 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136259916</t>
+          <t>https://artportalen.se/Sighting/122929535</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125974903</v>
+        <v>136259916</v>
       </c>
       <c r="B167" t="n">
-        <v>8444</v>
+        <v>8463</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19514,28 +19512,24 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
@@ -19547,17 +19541,17 @@
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>söder om Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>686838</v>
+        <v>686457</v>
       </c>
       <c r="R167" t="n">
-        <v>6562733</v>
+        <v>6563062</v>
       </c>
       <c r="S167" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -19581,17 +19575,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>gammal björklåga med spår längs hela stammen</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19604,47 +19593,27 @@
       <c r="AG167" t="b">
         <v>0</v>
       </c>
-      <c r="AJ167" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK167" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM167" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Betula pendula</t>
-        </is>
-      </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125974903</t>
+          <t>https://artportalen.se/Sighting/136259916</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126061086</v>
+        <v>125974903</v>
       </c>
       <c r="B168" t="n">
         <v>8444</v>
@@ -19672,20 +19641,33 @@
           <t>Janson, 1856</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>söder om Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>686932</v>
+        <v>686838</v>
       </c>
       <c r="R168" t="n">
-        <v>6563067</v>
+        <v>6562733</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -19712,19 +19694,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>15:00</t>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>gammal björklåga med spår längs hela stammen</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19733,50 +19710,51 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vårtbjörk</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
         <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL168" t="inlineStr">
-        <is>
-          <t>Barklös björklåga.</t>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>Betula # Barklös björklåga.</t>
+          <t>Wood surface of dead wood # Betula pendula</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061086</t>
+          <t>https://artportalen.se/Sighting/125974903</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126061105</v>
+        <v>126061086</v>
       </c>
       <c r="B169" t="n">
         <v>8444</v>
@@ -19811,10 +19789,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>686860</v>
+        <v>686932</v>
       </c>
       <c r="R169" t="n">
-        <v>6562743</v>
+        <v>6563067</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19846,7 +19824,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -19856,7 +19834,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19878,9 +19856,14 @@
           <t>Betula</t>
         </is>
       </c>
+      <c r="AL169" t="inlineStr">
+        <is>
+          <t>Barklös björklåga.</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Betula # Barklös björklåga.</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
@@ -19891,22 +19874,22 @@
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061105</t>
+          <t>https://artportalen.se/Sighting/126061086</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>136635739</v>
+        <v>126061105</v>
       </c>
       <c r="B170" t="n">
-        <v>8452</v>
+        <v>8444</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19934,17 +19917,17 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Utanför Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>686973</v>
+        <v>686860</v>
       </c>
       <c r="R170" t="n">
-        <v>6563106</v>
+        <v>6562743</v>
       </c>
       <c r="S170" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19968,27 +19951,22 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Björklåga</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19999,31 +19977,46 @@
       </c>
       <c r="AG170" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Vendela Ström</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Vendela Ström</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136635739</t>
+          <t>https://artportalen.se/Sighting/126061105</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>136767157</v>
+        <v>136635739</v>
       </c>
       <c r="B171" t="n">
-        <v>56875</v>
+        <v>8452</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20031,37 +20024,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>205992</v>
+        <v>106554</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Norrby torp, Tyresta, Srm</t>
+          <t>Utanför Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>687260</v>
+        <v>686973</v>
       </c>
       <c r="R171" t="n">
-        <v>6563241</v>
+        <v>6563106</v>
       </c>
       <c r="S171" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -20085,22 +20078,27 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>04:39</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>04:39</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Björklåga</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -20115,24 +20113,24 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Vendela Ström</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Vendela Ström</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767157</t>
+          <t>https://artportalen.se/Sighting/136635739</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>136867583</v>
+        <v>136767157</v>
       </c>
       <c r="B172" t="n">
         <v>56875</v>
@@ -20167,10 +20165,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>687164</v>
+        <v>687260</v>
       </c>
       <c r="R172" t="n">
-        <v>6563337</v>
+        <v>6563241</v>
       </c>
       <c r="S172" t="n">
         <v>25</v>
@@ -20197,22 +20195,22 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>04:12</t>
+          <t>04:39</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>04:12</t>
+          <t>04:39</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20238,13 +20236,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867583</t>
+          <t>https://artportalen.se/Sighting/136767157</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>136867591</v>
+        <v>136867583</v>
       </c>
       <c r="B173" t="n">
         <v>56875</v>
@@ -20279,10 +20277,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>686871</v>
+        <v>687164</v>
       </c>
       <c r="R173" t="n">
-        <v>6563175</v>
+        <v>6563337</v>
       </c>
       <c r="S173" t="n">
         <v>25</v>
@@ -20309,22 +20307,22 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>04:19</t>
+          <t>04:12</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>04:19</t>
+          <t>04:12</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20350,16 +20348,16 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867591</t>
+          <t>https://artportalen.se/Sighting/136867583</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>136767122</v>
+        <v>136867591</v>
       </c>
       <c r="B174" t="n">
-        <v>56887</v>
+        <v>56875</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20367,21 +20365,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -20391,10 +20389,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>686692</v>
+        <v>686871</v>
       </c>
       <c r="R174" t="n">
-        <v>6563011</v>
+        <v>6563175</v>
       </c>
       <c r="S174" t="n">
         <v>25</v>
@@ -20421,22 +20419,22 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>04:19</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>04:19</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20462,13 +20460,13 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767122</t>
+          <t>https://artportalen.se/Sighting/136867591</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>136767160</v>
+        <v>136767122</v>
       </c>
       <c r="B175" t="n">
         <v>56887</v>
@@ -20503,10 +20501,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>687260</v>
+        <v>686692</v>
       </c>
       <c r="R175" t="n">
-        <v>6563241</v>
+        <v>6563011</v>
       </c>
       <c r="S175" t="n">
         <v>25</v>
@@ -20533,22 +20531,22 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>01:27</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>01:27</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20574,13 +20572,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767160</t>
+          <t>https://artportalen.se/Sighting/136767122</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>136867584</v>
+        <v>136767160</v>
       </c>
       <c r="B176" t="n">
         <v>56887</v>
@@ -20615,10 +20613,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>687164</v>
+        <v>687260</v>
       </c>
       <c r="R176" t="n">
-        <v>6563337</v>
+        <v>6563241</v>
       </c>
       <c r="S176" t="n">
         <v>25</v>
@@ -20645,22 +20643,22 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>01:27</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>01:27</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20686,13 +20684,13 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867584</t>
+          <t>https://artportalen.se/Sighting/136767160</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>136867597</v>
+        <v>136867584</v>
       </c>
       <c r="B177" t="n">
         <v>56887</v>
@@ -20727,10 +20725,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>686871</v>
+        <v>687164</v>
       </c>
       <c r="R177" t="n">
-        <v>6563175</v>
+        <v>6563337</v>
       </c>
       <c r="S177" t="n">
         <v>25</v>
@@ -20757,22 +20755,22 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>23:43</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>23:43</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20798,36 +20796,40 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867597</t>
+          <t>https://artportalen.se/Sighting/136867584</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>136767120</v>
+        <v>136867597</v>
       </c>
       <c r="B178" t="n">
-        <v>56866</v>
+        <v>56887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr"/>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
@@ -20835,10 +20837,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>686692</v>
+        <v>686871</v>
       </c>
       <c r="R178" t="n">
-        <v>6563011</v>
+        <v>6563175</v>
       </c>
       <c r="S178" t="n">
         <v>25</v>
@@ -20865,22 +20867,22 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>23:43</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>23:43</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20906,13 +20908,13 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767120</t>
+          <t>https://artportalen.se/Sighting/136867597</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>136767159</v>
+        <v>136767120</v>
       </c>
       <c r="B179" t="n">
         <v>56866</v>
@@ -20943,10 +20945,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>687260</v>
+        <v>686692</v>
       </c>
       <c r="R179" t="n">
-        <v>6563241</v>
+        <v>6563011</v>
       </c>
       <c r="S179" t="n">
         <v>25</v>
@@ -20973,22 +20975,22 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -21014,13 +21016,13 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767159</t>
+          <t>https://artportalen.se/Sighting/136767120</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>136867586</v>
+        <v>136767159</v>
       </c>
       <c r="B180" t="n">
         <v>56866</v>
@@ -21051,10 +21053,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>687164</v>
+        <v>687260</v>
       </c>
       <c r="R180" t="n">
-        <v>6563337</v>
+        <v>6563241</v>
       </c>
       <c r="S180" t="n">
         <v>25</v>
@@ -21081,22 +21083,22 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -21122,13 +21124,13 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867586</t>
+          <t>https://artportalen.se/Sighting/136767159</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>136867588</v>
+        <v>136867586</v>
       </c>
       <c r="B181" t="n">
         <v>56866</v>
@@ -21159,10 +21161,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>686871</v>
+        <v>687164</v>
       </c>
       <c r="R181" t="n">
-        <v>6563175</v>
+        <v>6563337</v>
       </c>
       <c r="S181" t="n">
         <v>25</v>
@@ -21189,22 +21191,22 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>22:16</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>22:16</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21230,16 +21232,16 @@
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867588</t>
+          <t>https://artportalen.se/Sighting/136867586</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>136767162</v>
+        <v>136867588</v>
       </c>
       <c r="B182" t="n">
-        <v>56889</v>
+        <v>56866</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21247,23 +21249,19 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
@@ -21271,10 +21269,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>687260</v>
+        <v>686871</v>
       </c>
       <c r="R182" t="n">
-        <v>6563241</v>
+        <v>6563175</v>
       </c>
       <c r="S182" t="n">
         <v>25</v>
@@ -21301,22 +21299,22 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>00:57</t>
+          <t>22:16</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>00:57</t>
+          <t>22:16</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21342,13 +21340,13 @@
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767162</t>
+          <t>https://artportalen.se/Sighting/136867588</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>136867594</v>
+        <v>136767162</v>
       </c>
       <c r="B183" t="n">
         <v>56889</v>
@@ -21383,10 +21381,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>686871</v>
+        <v>687260</v>
       </c>
       <c r="R183" t="n">
-        <v>6563175</v>
+        <v>6563241</v>
       </c>
       <c r="S183" t="n">
         <v>25</v>
@@ -21413,22 +21411,22 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>00:57</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>00:57</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21454,33 +21452,33 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867594</t>
+          <t>https://artportalen.se/Sighting/136767162</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>111182876</v>
+        <v>136867594</v>
       </c>
       <c r="B184" t="n">
-        <v>58790</v>
+        <v>56889</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>208245</v>
+        <v>206002</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -21488,29 +21486,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>686971</v>
+        <v>686871</v>
       </c>
       <c r="R184" t="n">
-        <v>6563333</v>
+        <v>6563175</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21534,12 +21523,22 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21548,31 +21547,30 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
-      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111182876</t>
+          <t>https://artportalen.se/Sighting/136867594</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>126061089</v>
+        <v>111182876</v>
       </c>
       <c r="B185" t="n">
         <v>58790</v>
@@ -21605,21 +21603,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>686871</v>
+        <v>686971</v>
       </c>
       <c r="R185" t="n">
-        <v>6562972</v>
+        <v>6563333</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21646,22 +21644,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21670,30 +21658,31 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
+      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061089</t>
+          <t>https://artportalen.se/Sighting/111182876</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>126061098</v>
+        <v>126061089</v>
       </c>
       <c r="B186" t="n">
         <v>58790</v>
@@ -21721,17 +21710,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr"/>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>686857</v>
+        <v>686871</v>
       </c>
       <c r="R186" t="n">
-        <v>6562875</v>
+        <v>6562972</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21763,7 +21761,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -21773,7 +21771,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21793,19 +21791,19 @@
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061098</t>
+          <t>https://artportalen.se/Sighting/126061089</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128095464</v>
+        <v>126061098</v>
       </c>
       <c r="B187" t="n">
         <v>58790</v>
@@ -21833,30 +21831,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>687155</v>
+        <v>686857</v>
       </c>
       <c r="R187" t="n">
-        <v>6563193</v>
+        <v>6562875</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21883,12 +21868,22 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21897,34 +21892,33 @@
       <c r="AE187" t="b">
         <v>0</v>
       </c>
-      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128095464</t>
+          <t>https://artportalen.se/Sighting/126061098</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>134488564</v>
+        <v>128095464</v>
       </c>
       <c r="B188" t="n">
-        <v>58812</v>
+        <v>58790</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21955,7 +21949,11 @@
         </is>
       </c>
       <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
@@ -21965,10 +21963,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>687272</v>
+        <v>687155</v>
       </c>
       <c r="R188" t="n">
-        <v>6563263</v>
+        <v>6563193</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21995,17 +21993,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>Ca 2-3 cm lång.</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -22032,16 +22025,16 @@
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134488564</t>
+          <t>https://artportalen.se/Sighting/128095464</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>126061108</v>
+        <v>134488564</v>
       </c>
       <c r="B189" t="n">
-        <v>58817</v>
+        <v>58812</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22049,21 +22042,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -22071,26 +22064,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>686907</v>
+        <v>687272</v>
       </c>
       <c r="R189" t="n">
-        <v>6562760</v>
+        <v>6563263</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -22117,22 +22105,17 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Ca 2-3 cm lång.</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -22141,33 +22124,34 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
+      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061108</t>
+          <t>https://artportalen.se/Sighting/134488564</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>136777569</v>
+        <v>126061108</v>
       </c>
       <c r="B190" t="n">
-        <v>58872</v>
+        <v>58817</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22192,20 +22176,34 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr"/>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Norrby torp, Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>687280</v>
+        <v>686907</v>
       </c>
       <c r="R190" t="n">
-        <v>6563262</v>
+        <v>6562760</v>
       </c>
       <c r="S190" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -22229,22 +22227,22 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22264,22 +22262,22 @@
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136777569</t>
+          <t>https://artportalen.se/Sighting/126061108</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>126061081</v>
+        <v>136777569</v>
       </c>
       <c r="B191" t="n">
-        <v>58815</v>
+        <v>58872</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22287,51 +22285,37 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>208250</v>
+        <v>208249</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>687058</v>
+        <v>687280</v>
       </c>
       <c r="R191" t="n">
-        <v>6563228</v>
+        <v>6563262</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -22355,22 +22339,22 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22390,22 +22374,22 @@
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061081</t>
+          <t>https://artportalen.se/Sighting/136777569</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>117554483</v>
+        <v>126061081</v>
       </c>
       <c r="B192" t="n">
-        <v>99035</v>
+        <v>58815</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22413,41 +22397,51 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>219790</v>
+        <v>208250</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>686878</v>
+        <v>687058</v>
       </c>
       <c r="R192" t="n">
-        <v>6562971</v>
+        <v>6563228</v>
       </c>
       <c r="S192" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -22471,12 +22465,22 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22485,31 +22489,30 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
-      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117554483</t>
+          <t>https://artportalen.se/Sighting/126061081</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>126003792</v>
+        <v>117554483</v>
       </c>
       <c r="B193" t="n">
         <v>99035</v>
@@ -22544,17 +22547,17 @@
       <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>687046</v>
+        <v>686878</v>
       </c>
       <c r="R193" t="n">
-        <v>6563346</v>
+        <v>6562971</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -22578,12 +22581,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22610,13 +22613,13 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126003792</t>
+          <t>https://artportalen.se/Sighting/117554483</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126005160</v>
+        <v>126003792</v>
       </c>
       <c r="B194" t="n">
         <v>99035</v>
@@ -22655,10 +22658,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>687034</v>
+        <v>687046</v>
       </c>
       <c r="R194" t="n">
-        <v>6563204</v>
+        <v>6563346</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22717,13 +22720,13 @@
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126005160</t>
+          <t>https://artportalen.se/Sighting/126003792</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>126061084</v>
+        <v>126005160</v>
       </c>
       <c r="B195" t="n">
         <v>99035</v>
@@ -22752,16 +22755,20 @@
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>687014</v>
+        <v>687034</v>
       </c>
       <c r="R195" t="n">
-        <v>6563215</v>
+        <v>6563204</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22788,22 +22795,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22812,30 +22809,31 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061084</t>
+          <t>https://artportalen.se/Sighting/126005160</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>126061091</v>
+        <v>126061084</v>
       </c>
       <c r="B196" t="n">
         <v>99035</v>
@@ -22870,10 +22868,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>686871</v>
+        <v>687014</v>
       </c>
       <c r="R196" t="n">
-        <v>6562972</v>
+        <v>6563215</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22905,7 +22903,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -22915,7 +22913,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22941,13 +22939,13 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061091</t>
+          <t>https://artportalen.se/Sighting/126061084</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>126061099</v>
+        <v>126061091</v>
       </c>
       <c r="B197" t="n">
         <v>99035</v>
@@ -22982,10 +22980,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>686857</v>
+        <v>686871</v>
       </c>
       <c r="R197" t="n">
-        <v>6562875</v>
+        <v>6562972</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -23017,7 +23015,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -23027,7 +23025,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -23047,19 +23045,19 @@
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061099</t>
+          <t>https://artportalen.se/Sighting/126061091</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>126061102</v>
+        <v>126061099</v>
       </c>
       <c r="B198" t="n">
         <v>99035</v>
@@ -23094,10 +23092,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>686837</v>
+        <v>686857</v>
       </c>
       <c r="R198" t="n">
-        <v>6562829</v>
+        <v>6562875</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -23129,7 +23127,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -23139,7 +23137,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -23165,13 +23163,13 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061102</t>
+          <t>https://artportalen.se/Sighting/126061099</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>126233785</v>
+        <v>126061102</v>
       </c>
       <c r="B199" t="n">
         <v>99035</v>
@@ -23200,24 +23198,16 @@
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>686839</v>
+        <v>686837</v>
       </c>
       <c r="R199" t="n">
-        <v>6563016</v>
+        <v>6562829</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -23244,12 +23234,22 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -23258,31 +23258,30 @@
       <c r="AE199" t="b">
         <v>0</v>
       </c>
-      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126233785</t>
+          <t>https://artportalen.se/Sighting/126061102</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>126234010</v>
+        <v>126233785</v>
       </c>
       <c r="B200" t="n">
         <v>99035</v>
@@ -23325,10 +23324,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>687160</v>
+        <v>686839</v>
       </c>
       <c r="R200" t="n">
-        <v>6563261</v>
+        <v>6563016</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -23381,19 +23380,19 @@
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234010</t>
+          <t>https://artportalen.se/Sighting/126233785</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>126234159</v>
+        <v>126234010</v>
       </c>
       <c r="B201" t="n">
         <v>99035</v>
@@ -23421,13 +23420,13 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
@@ -23436,13 +23435,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>687297</v>
+        <v>687160</v>
       </c>
       <c r="R201" t="n">
-        <v>6563381</v>
+        <v>6563261</v>
       </c>
       <c r="S201" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -23472,11 +23471,6 @@
       <c r="AA201" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>Ett flertal i blomning.</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23497,19 +23491,19 @@
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Ulf Johansson</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234159</t>
+          <t>https://artportalen.se/Sighting/126234010</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>126234439</v>
+        <v>126234159</v>
       </c>
       <c r="B202" t="n">
         <v>99035</v>
@@ -23539,34 +23533,26 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
       <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>686777</v>
+        <v>687297</v>
       </c>
       <c r="R202" t="n">
-        <v>6563073</v>
+        <v>6563381</v>
       </c>
       <c r="S202" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -23596,6 +23582,11 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Ett flertal i blomning.</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23611,24 +23602,24 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234439</t>
+          <t>https://artportalen.se/Sighting/126234159</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>126234644</v>
+        <v>126234439</v>
       </c>
       <c r="B203" t="n">
         <v>99035</v>
@@ -23658,7 +23649,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -23666,7 +23657,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
@@ -23675,10 +23670,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>686837</v>
+        <v>686777</v>
       </c>
       <c r="R203" t="n">
-        <v>6562967</v>
+        <v>6563073</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23737,13 +23732,13 @@
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234644</t>
+          <t>https://artportalen.se/Sighting/126234439</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>126234771</v>
+        <v>126234644</v>
       </c>
       <c r="B204" t="n">
         <v>99035</v>
@@ -23773,7 +23768,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -23786,14 +23781,14 @@
       <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Norrby mosse OSO, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>686976</v>
+        <v>686837</v>
       </c>
       <c r="R204" t="n">
-        <v>6563107</v>
+        <v>6562967</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23852,16 +23847,16 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234771</t>
+          <t>https://artportalen.se/Sighting/126234644</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>133767702</v>
+        <v>126234771</v>
       </c>
       <c r="B205" t="n">
-        <v>99112</v>
+        <v>99035</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23886,21 +23881,29 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse OSO, Srm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>686845</v>
+        <v>686976</v>
       </c>
       <c r="R205" t="n">
-        <v>6563325</v>
+        <v>6563107</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23927,12 +23930,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23948,27 +23951,27 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133767702</t>
+          <t>https://artportalen.se/Sighting/126234771</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>126061092</v>
+        <v>133767702</v>
       </c>
       <c r="B206" t="n">
-        <v>99022</v>
+        <v>99112</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23976,43 +23979,38 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>686880</v>
+        <v>686845</v>
       </c>
       <c r="R206" t="n">
-        <v>6562892</v>
+        <v>6563325</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -24039,22 +24037,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -24063,30 +24051,31 @@
       <c r="AE206" t="b">
         <v>0</v>
       </c>
+      <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="b">
         <v>0</v>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061092</t>
+          <t>https://artportalen.se/Sighting/133767702</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>126061094</v>
+        <v>126061092</v>
       </c>
       <c r="B207" t="n">
         <v>99022</v>
@@ -24130,10 +24119,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>686866</v>
+        <v>686880</v>
       </c>
       <c r="R207" t="n">
-        <v>6562874</v>
+        <v>6562892</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -24165,7 +24154,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -24175,7 +24164,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -24201,13 +24190,13 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061094</t>
+          <t>https://artportalen.se/Sighting/126061092</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>126061100</v>
+        <v>126061094</v>
       </c>
       <c r="B208" t="n">
         <v>99022</v>
@@ -24237,7 +24226,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -24251,10 +24240,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>686857</v>
+        <v>686866</v>
       </c>
       <c r="R208" t="n">
-        <v>6562875</v>
+        <v>6562874</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -24286,7 +24275,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -24296,7 +24285,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -24322,43 +24311,43 @@
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061100</t>
+          <t>https://artportalen.se/Sighting/126061094</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>86686018</v>
+        <v>126061100</v>
       </c>
       <c r="B209" t="n">
-        <v>99118</v>
+        <v>99022</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -24366,23 +24355,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Tyresta S Ungfars kärr, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>686831</v>
+        <v>686857</v>
       </c>
       <c r="R209" t="n">
-        <v>6563296</v>
+        <v>6562875</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -24409,17 +24391,22 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2020-07-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2020-07-04</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>Från Ungfars kärrs södra spets och ca 200 meter österut. Ungefär hälften av skotten utanför parkens gräns. 4 blomstänglar. Området var bökat av vildsvin. Vissa skott var uppgrävda.</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -24428,31 +24415,30 @@
       <c r="AE209" t="b">
         <v>0</v>
       </c>
-      <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="b">
         <v>0</v>
       </c>
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86686018</t>
+          <t>https://artportalen.se/Sighting/126061100</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>96672256</v>
+        <v>86686018</v>
       </c>
       <c r="B210" t="n">
         <v>99118</v>
@@ -24480,24 +24466,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>NO Norrby mosse, Srm</t>
+          <t>Tyresta S Ungfars kärr, Srm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>686848</v>
+        <v>686831</v>
       </c>
       <c r="R210" t="n">
-        <v>6563295</v>
+        <v>6563296</v>
       </c>
       <c r="S210" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -24521,12 +24519,17 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2020-07-04</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2020-07-04</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>Från Ungfars kärrs södra spets och ca 200 meter österut. Ungefär hälften av skotten utanför parkens gräns. 4 blomstänglar. Området var bökat av vildsvin. Vissa skott var uppgrävda.</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24542,24 +24545,24 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96672256</t>
+          <t>https://artportalen.se/Sighting/86686018</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>97242656</v>
+        <v>96672256</v>
       </c>
       <c r="B211" t="n">
         <v>99118</v>
@@ -24588,21 +24591,23 @@
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>OSO Ungfars mosse, Srm</t>
+          <t>NO Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>686846</v>
+        <v>686848</v>
       </c>
       <c r="R211" t="n">
-        <v>6563316</v>
+        <v>6563295</v>
       </c>
       <c r="S211" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -24626,22 +24631,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="Z211" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -24650,30 +24645,31 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
+      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Thomas Strid, Bodil Ravn, Ulf Johansson, Tiina Laantee</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97242656</t>
+          <t>https://artportalen.se/Sighting/96672256</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>97243108</v>
+        <v>97242656</v>
       </c>
       <c r="B212" t="n">
         <v>99118</v>
@@ -24706,17 +24702,17 @@
       <c r="L212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Tyresta, Srm</t>
+          <t>OSO Ungfars mosse, Srm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>686847</v>
+        <v>686846</v>
       </c>
       <c r="R212" t="n">
-        <v>6563308</v>
+        <v>6563316</v>
       </c>
       <c r="S212" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -24745,7 +24741,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -24755,7 +24751,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24781,13 +24777,13 @@
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97243108</t>
+          <t>https://artportalen.se/Sighting/97242656</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>97330311</v>
+        <v>97243108</v>
       </c>
       <c r="B213" t="n">
         <v>99118</v>
@@ -24815,29 +24811,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Tyresta NP, SSV Bylsjön (*knärot* /stjälk/), Srm</t>
+          <t>Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q213" t="n">
         <v>686847</v>
       </c>
       <c r="R213" t="n">
-        <v>6563309</v>
+        <v>6563308</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -24859,24 +24848,24 @@
           <t>Österhaninge</t>
         </is>
       </c>
-      <c r="X213" t="inlineStr">
-        <is>
-          <t>AB-Han-0218</t>
-        </is>
-      </c>
       <c r="Y213" t="inlineStr">
         <is>
           <t>2021-11-20</t>
         </is>
       </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA213" t="inlineStr">
         <is>
           <t>2021-11-20</t>
         </is>
       </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>/Ej räknad/</t>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24891,28 +24880,24 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Tiina Laantee, Ulf Johansson, Bodil Ravn, Thomas Strid</t>
-        </is>
-      </c>
-      <c r="AY213" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Thomas Strid, Bodil Ravn, Ulf Johansson, Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97330311</t>
+          <t>https://artportalen.se/Sighting/97243108</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>98104097</v>
+        <v>97330311</v>
       </c>
       <c r="B214" t="n">
         <v>99118</v>
@@ -24942,27 +24927,24 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Tyresta NP, SSV Bylsjön (*knärot* /stjälk/), Srm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>686934</v>
+        <v>686847</v>
       </c>
       <c r="R214" t="n">
-        <v>6563325</v>
+        <v>6563309</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24987,19 +24969,24 @@
           <t>Österhaninge</t>
         </is>
       </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>AB-Han-0218</t>
+        </is>
+      </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>Intill djurstig och granlåga</t>
+          <t>/Ej räknad/</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -25008,31 +24995,34 @@
       <c r="AE214" t="b">
         <v>0</v>
       </c>
-      <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
       </c>
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
-        </is>
-      </c>
-      <c r="AY214" t="inlineStr"/>
+          <t>Tiina Laantee, Ulf Johansson, Bodil Ravn, Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98104097</t>
+          <t>https://artportalen.se/Sighting/97330311</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>104249959</v>
+        <v>98104097</v>
       </c>
       <c r="B215" t="n">
         <v>99118</v>
@@ -25060,24 +25050,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>687011</v>
+        <v>686934</v>
       </c>
       <c r="R215" t="n">
-        <v>6562869</v>
+        <v>6563325</v>
       </c>
       <c r="S215" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -25101,17 +25099,17 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>Samma lokal som noterades 17/11-21. Ca 25 ex. Koordinaterna har varierat något vid besöken.</t>
+          <t>Intill djurstig och granlåga</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -25127,24 +25125,24 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104249959</t>
+          <t>https://artportalen.se/Sighting/98104097</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>109890506</v>
+        <v>104249959</v>
       </c>
       <c r="B216" t="n">
         <v>99118</v>
@@ -25179,17 +25177,17 @@
       <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Ö Norrby Mosse, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>686831</v>
+        <v>687011</v>
       </c>
       <c r="R216" t="n">
-        <v>6563216</v>
+        <v>6562869</v>
       </c>
       <c r="S216" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -25213,12 +25211,17 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>Samma lokal som noterades 17/11-21. Ca 25 ex. Koordinaterna har varierat något vid besöken.</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -25245,13 +25248,13 @@
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109890506</t>
+          <t>https://artportalen.se/Sighting/104249959</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>119475594</v>
+        <v>109890506</v>
       </c>
       <c r="B217" t="n">
         <v>99118</v>
@@ -25279,29 +25282,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>Ö Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>686995</v>
+        <v>686831</v>
       </c>
       <c r="R217" t="n">
-        <v>6563315</v>
+        <v>6563216</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -25328,12 +25323,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -25360,13 +25355,13 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119475594</t>
+          <t>https://artportalen.se/Sighting/109890506</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>121859637</v>
+        <v>119475594</v>
       </c>
       <c r="B218" t="n">
         <v>99118</v>
@@ -25394,17 +25389,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>686863</v>
+        <v>686995</v>
       </c>
       <c r="R218" t="n">
-        <v>6563252</v>
+        <v>6563315</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -25431,22 +25438,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z218" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB218" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -25455,30 +25452,31 @@
       <c r="AE218" t="b">
         <v>0</v>
       </c>
+      <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="b">
         <v>0</v>
       </c>
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859637</t>
+          <t>https://artportalen.se/Sighting/119475594</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>121859638</v>
+        <v>121859637</v>
       </c>
       <c r="B219" t="n">
         <v>99118</v>
@@ -25513,10 +25511,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>686826</v>
+        <v>686863</v>
       </c>
       <c r="R219" t="n">
-        <v>6563286</v>
+        <v>6563252</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -25548,7 +25546,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -25558,7 +25556,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -25584,13 +25582,13 @@
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859638</t>
+          <t>https://artportalen.se/Sighting/121859637</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>121859639</v>
+        <v>121859638</v>
       </c>
       <c r="B220" t="n">
         <v>99118</v>
@@ -25625,10 +25623,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>686827</v>
+        <v>686826</v>
       </c>
       <c r="R220" t="n">
-        <v>6563296</v>
+        <v>6563286</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25660,7 +25658,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -25670,7 +25668,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -25696,13 +25694,13 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859639</t>
+          <t>https://artportalen.se/Sighting/121859638</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>121859640</v>
+        <v>121859639</v>
       </c>
       <c r="B221" t="n">
         <v>99118</v>
@@ -25737,10 +25735,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>686837</v>
+        <v>686827</v>
       </c>
       <c r="R221" t="n">
-        <v>6563297</v>
+        <v>6563296</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25772,7 +25770,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -25782,7 +25780,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -25808,13 +25806,13 @@
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859640</t>
+          <t>https://artportalen.se/Sighting/121859639</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>121859642</v>
+        <v>121859640</v>
       </c>
       <c r="B222" t="n">
         <v>99118</v>
@@ -25843,24 +25841,16 @@
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>686834</v>
+        <v>686837</v>
       </c>
       <c r="R222" t="n">
-        <v>6563305</v>
+        <v>6563297</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25892,7 +25882,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -25902,7 +25892,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -25911,7 +25901,6 @@
       <c r="AE222" t="b">
         <v>0</v>
       </c>
-      <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="b">
         <v>0</v>
       </c>
@@ -25929,13 +25918,13 @@
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859642</t>
+          <t>https://artportalen.se/Sighting/121859640</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>121859643</v>
+        <v>121859642</v>
       </c>
       <c r="B223" t="n">
         <v>99118</v>
@@ -25964,6 +25953,14 @@
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
@@ -25973,7 +25970,7 @@
         <v>686834</v>
       </c>
       <c r="R223" t="n">
-        <v>6563309</v>
+        <v>6563305</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -26005,7 +26002,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -26015,7 +26012,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -26024,6 +26021,7 @@
       <c r="AE223" t="b">
         <v>0</v>
       </c>
+      <c r="AF223" t="inlineStr"/>
       <c r="AG223" t="b">
         <v>0</v>
       </c>
@@ -26041,13 +26039,13 @@
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859643</t>
+          <t>https://artportalen.se/Sighting/121859642</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>121859644</v>
+        <v>121859643</v>
       </c>
       <c r="B224" t="n">
         <v>99118</v>
@@ -26082,10 +26080,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>686844</v>
+        <v>686834</v>
       </c>
       <c r="R224" t="n">
-        <v>6563303</v>
+        <v>6563309</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26117,7 +26115,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -26127,7 +26125,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -26153,13 +26151,13 @@
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859644</t>
+          <t>https://artportalen.se/Sighting/121859643</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>121859646</v>
+        <v>121859644</v>
       </c>
       <c r="B225" t="n">
         <v>99118</v>
@@ -26194,7 +26192,7 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>686841</v>
+        <v>686844</v>
       </c>
       <c r="R225" t="n">
         <v>6563303</v>
@@ -26229,7 +26227,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -26239,7 +26237,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -26265,13 +26263,13 @@
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859646</t>
+          <t>https://artportalen.se/Sighting/121859644</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>121859647</v>
+        <v>121859646</v>
       </c>
       <c r="B226" t="n">
         <v>99118</v>
@@ -26306,10 +26304,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>686854</v>
+        <v>686841</v>
       </c>
       <c r="R226" t="n">
-        <v>6563286</v>
+        <v>6563303</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26341,7 +26339,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -26351,7 +26349,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -26377,13 +26375,13 @@
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859647</t>
+          <t>https://artportalen.se/Sighting/121859646</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>121859649</v>
+        <v>121859647</v>
       </c>
       <c r="B227" t="n">
         <v>99118</v>
@@ -26418,10 +26416,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>686851</v>
+        <v>686854</v>
       </c>
       <c r="R227" t="n">
-        <v>6563299</v>
+        <v>6563286</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26453,7 +26451,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -26463,7 +26461,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -26489,13 +26487,13 @@
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859649</t>
+          <t>https://artportalen.se/Sighting/121859647</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>121859650</v>
+        <v>121859649</v>
       </c>
       <c r="B228" t="n">
         <v>99118</v>
@@ -26530,10 +26528,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>686895</v>
+        <v>686851</v>
       </c>
       <c r="R228" t="n">
-        <v>6563306</v>
+        <v>6563299</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26565,7 +26563,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -26575,7 +26573,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -26601,13 +26599,13 @@
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859650</t>
+          <t>https://artportalen.se/Sighting/121859649</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>122220583</v>
+        <v>121859650</v>
       </c>
       <c r="B229" t="n">
         <v>99118</v>
@@ -26635,29 +26633,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>686996</v>
+        <v>686895</v>
       </c>
       <c r="R229" t="n">
-        <v>6562864</v>
+        <v>6563306</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26684,17 +26670,22 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>Samma lokal som rapporterats -21 och -22 men en ny klon. Den förra har möjligen haft lite problem med grisbök.</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -26703,31 +26694,30 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
-      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122220583</t>
+          <t>https://artportalen.se/Sighting/121859650</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>122781008</v>
+        <v>122220583</v>
       </c>
       <c r="B230" t="n">
         <v>99118</v>
@@ -26755,21 +26745,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr"/>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr"/>
       <c r="N230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Knärot, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>686833</v>
+        <v>686996</v>
       </c>
       <c r="R230" t="n">
-        <v>6563215</v>
+        <v>6562864</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -26796,17 +26794,17 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AC230" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Samma lokal som rapporterats -21 och -22 men en ny klon. Den förra har möjligen haft lite problem med grisbök.</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -26822,24 +26820,24 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122781008</t>
+          <t>https://artportalen.se/Sighting/122220583</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>126418709</v>
+        <v>122781008</v>
       </c>
       <c r="B231" t="n">
         <v>99118</v>
@@ -26867,29 +26865,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr"/>
       <c r="N231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Knärot, Srm</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>686771</v>
+        <v>686833</v>
       </c>
       <c r="R231" t="n">
-        <v>6563297</v>
+        <v>6563215</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26916,17 +26906,17 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26942,24 +26932,24 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418709</t>
+          <t>https://artportalen.se/Sighting/122781008</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>126418756</v>
+        <v>126418709</v>
       </c>
       <c r="B232" t="n">
         <v>99118</v>
@@ -26989,7 +26979,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -27006,10 +26996,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>686781</v>
+        <v>686771</v>
       </c>
       <c r="R232" t="n">
-        <v>6563292</v>
+        <v>6563297</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -27046,7 +27036,7 @@
       </c>
       <c r="AC232" t="inlineStr">
         <is>
-          <t>En av dem i knopp.</t>
+          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -27073,13 +27063,13 @@
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418756</t>
+          <t>https://artportalen.se/Sighting/126418709</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127932426</v>
+        <v>126418756</v>
       </c>
       <c r="B233" t="n">
         <v>99118</v>
@@ -27109,7 +27099,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -27126,10 +27116,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>686998</v>
+        <v>686781</v>
       </c>
       <c r="R233" t="n">
-        <v>6563316</v>
+        <v>6563292</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -27156,17 +27146,17 @@
       </c>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AC233" t="inlineStr">
         <is>
-          <t>Återfynd, rapporterad -24 med 3 ex. Nu 5 ex.</t>
+          <t>En av dem i knopp.</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -27193,13 +27183,13 @@
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127932426</t>
+          <t>https://artportalen.se/Sighting/126418756</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>128341941</v>
+        <v>127932426</v>
       </c>
       <c r="B234" t="n">
         <v>99118</v>
@@ -27229,7 +27219,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -27246,10 +27236,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>687244</v>
+        <v>686998</v>
       </c>
       <c r="R234" t="n">
-        <v>6563404</v>
+        <v>6563316</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -27276,12 +27266,17 @@
       </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>Återfynd, rapporterad -24 med 3 ex. Nu 5 ex.</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -27308,13 +27303,13 @@
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128341941</t>
+          <t>https://artportalen.se/Sighting/127932426</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>129564285</v>
+        <v>128341941</v>
       </c>
       <c r="B235" t="n">
         <v>99118</v>
@@ -27342,8 +27337,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr"/>
       <c r="N235" t="inlineStr"/>
@@ -27353,10 +27356,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>686625</v>
+        <v>687244</v>
       </c>
       <c r="R235" t="n">
-        <v>6563000</v>
+        <v>6563404</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27383,12 +27386,12 @@
       </c>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -27415,16 +27418,16 @@
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129564285</t>
+          <t>https://artportalen.se/Sighting/128341941</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>133767721</v>
+        <v>129564285</v>
       </c>
       <c r="B236" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27460,10 +27463,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>686845</v>
+        <v>686625</v>
       </c>
       <c r="R236" t="n">
-        <v>6563325</v>
+        <v>6563000</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27490,12 +27493,12 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -27522,38 +27525,38 @@
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133767721</t>
+          <t>https://artportalen.se/Sighting/129564285</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>96643458</v>
+        <v>133767721</v>
       </c>
       <c r="B237" t="n">
-        <v>106244</v>
+        <v>99195</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -27563,14 +27566,14 @@
       <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Vargklåva mosse S om, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>687154</v>
+        <v>686845</v>
       </c>
       <c r="R237" t="n">
-        <v>6563329</v>
+        <v>6563325</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27597,12 +27600,12 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -27618,24 +27621,24 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96643458</t>
+          <t>https://artportalen.se/Sighting/133767721</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>96858761</v>
+        <v>96643458</v>
       </c>
       <c r="B238" t="n">
         <v>106244</v>
@@ -27670,17 +27673,17 @@
       <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Vargklåva mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>687064</v>
+        <v>687154</v>
       </c>
       <c r="R238" t="n">
-        <v>6563258</v>
+        <v>6563329</v>
       </c>
       <c r="S238" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -27704,17 +27707,12 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>Två bestånd</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -27741,13 +27739,13 @@
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96858761</t>
+          <t>https://artportalen.se/Sighting/96643458</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>97204577</v>
+        <v>96858761</v>
       </c>
       <c r="B239" t="n">
         <v>106244</v>
@@ -27782,17 +27780,17 @@
       <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>SO Norrby mosse, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>687019</v>
+        <v>687064</v>
       </c>
       <c r="R239" t="n">
-        <v>6562889</v>
+        <v>6563258</v>
       </c>
       <c r="S239" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -27816,12 +27814,17 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>Två bestånd</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -27837,24 +27840,24 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97204577</t>
+          <t>https://artportalen.se/Sighting/96858761</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>100252927</v>
+        <v>97204577</v>
       </c>
       <c r="B240" t="n">
         <v>106244</v>
@@ -27889,17 +27892,17 @@
       <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>SO Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>687152</v>
+        <v>687019</v>
       </c>
       <c r="R240" t="n">
-        <v>6563326</v>
+        <v>6562889</v>
       </c>
       <c r="S240" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -27923,12 +27926,12 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -27955,13 +27958,13 @@
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100252927</t>
+          <t>https://artportalen.se/Sighting/97204577</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>116743172</v>
+        <v>100252927</v>
       </c>
       <c r="B241" t="n">
         <v>106244</v>
@@ -27990,16 +27993,20 @@
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Ungfars kärr, Ungfars kärr, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>687088</v>
+        <v>687152</v>
       </c>
       <c r="R241" t="n">
-        <v>6563243</v>
+        <v>6563326</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -28026,12 +28033,12 @@
       </c>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -28040,30 +28047,31 @@
       <c r="AE241" t="b">
         <v>0</v>
       </c>
+      <c r="AF241" t="inlineStr"/>
       <c r="AG241" t="b">
         <v>0</v>
       </c>
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116743172</t>
+          <t>https://artportalen.se/Sighting/100252927</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>125965889</v>
+        <v>116743172</v>
       </c>
       <c r="B242" t="n">
         <v>106244</v>
@@ -28098,10 +28106,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>687076</v>
+        <v>687088</v>
       </c>
       <c r="R242" t="n">
-        <v>6563220</v>
+        <v>6563243</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -28128,12 +28136,12 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -28159,13 +28167,13 @@
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125965889</t>
+          <t>https://artportalen.se/Sighting/116743172</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>126003574</v>
+        <v>125965889</v>
       </c>
       <c r="B243" t="n">
         <v>106244</v>
@@ -28194,20 +28202,16 @@
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
-      <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ungfars kärr, Ungfars kärr, Srm</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>686803</v>
+        <v>687076</v>
       </c>
       <c r="R243" t="n">
-        <v>6563098</v>
+        <v>6563220</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -28234,12 +28238,12 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -28248,31 +28252,30 @@
       <c r="AE243" t="b">
         <v>0</v>
       </c>
-      <c r="AF243" t="inlineStr"/>
       <c r="AG243" t="b">
         <v>0</v>
       </c>
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126003574</t>
+          <t>https://artportalen.se/Sighting/125965889</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>126061078</v>
+        <v>126003574</v>
       </c>
       <c r="B244" t="n">
         <v>106244</v>
@@ -28301,16 +28304,20 @@
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>687085</v>
+        <v>686803</v>
       </c>
       <c r="R244" t="n">
-        <v>6563229</v>
+        <v>6563098</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -28337,22 +28344,12 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z244" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB244" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -28361,30 +28358,31 @@
       <c r="AE244" t="b">
         <v>0</v>
       </c>
+      <c r="AF244" t="inlineStr"/>
       <c r="AG244" t="b">
         <v>0</v>
       </c>
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061078</t>
+          <t>https://artportalen.se/Sighting/126003574</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>126061079</v>
+        <v>126061078</v>
       </c>
       <c r="B245" t="n">
         <v>106244</v>
@@ -28419,10 +28417,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>687082</v>
+        <v>687085</v>
       </c>
       <c r="R245" t="n">
-        <v>6563241</v>
+        <v>6563229</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -28454,7 +28452,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -28464,7 +28462,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -28490,13 +28488,13 @@
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061079</t>
+          <t>https://artportalen.se/Sighting/126061078</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>126234373</v>
+        <v>126061079</v>
       </c>
       <c r="B246" t="n">
         <v>106244</v>
@@ -28524,29 +28522,17 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J246" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>686756</v>
+        <v>687082</v>
       </c>
       <c r="R246" t="n">
-        <v>6563092</v>
+        <v>6563241</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28573,12 +28559,22 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -28587,31 +28583,30 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
-      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234373</t>
+          <t>https://artportalen.se/Sighting/126061079</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>126234937</v>
+        <v>126234373</v>
       </c>
       <c r="B247" t="n">
         <v>106244</v>
@@ -28649,23 +28644,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr"/>
       <c r="N247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>687103</v>
+        <v>686756</v>
       </c>
       <c r="R247" t="n">
-        <v>6563191</v>
+        <v>6563092</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28724,16 +28715,16 @@
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234937</t>
+          <t>https://artportalen.se/Sighting/126234373</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>136329900</v>
+        <v>126234937</v>
       </c>
       <c r="B248" t="n">
-        <v>106494</v>
+        <v>106244</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28758,21 +28749,33 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr"/>
-      <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr"/>
       <c r="N248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>686462</v>
+        <v>687103</v>
       </c>
       <c r="R248" t="n">
-        <v>6563046</v>
+        <v>6563191</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28799,12 +28802,12 @@
       </c>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28820,24 +28823,24 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136329900</t>
+          <t>https://artportalen.se/Sighting/126234937</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>136422457</v>
+        <v>136329900</v>
       </c>
       <c r="B249" t="n">
         <v>106494</v>
@@ -28876,10 +28879,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>687270</v>
+        <v>686462</v>
       </c>
       <c r="R249" t="n">
-        <v>6563384</v>
+        <v>6563046</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28906,12 +28909,12 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28938,16 +28941,16 @@
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136422457</t>
+          <t>https://artportalen.se/Sighting/136329900</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>96643468</v>
+        <v>136422457</v>
       </c>
       <c r="B250" t="n">
-        <v>97989</v>
+        <v>106494</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28955,46 +28958,38 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J250" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr"/>
       <c r="N250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Vargklåva mosse S om, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>687268</v>
+        <v>687270</v>
       </c>
       <c r="R250" t="n">
-        <v>6563319</v>
+        <v>6563384</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -29021,17 +29016,12 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>Strax nedom klippbrant</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -29047,24 +29037,24 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96643468</t>
+          <t>https://artportalen.se/Sighting/136422457</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>116746465</v>
+        <v>96643468</v>
       </c>
       <c r="B251" t="n">
         <v>97989</v>
@@ -29092,17 +29082,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr"/>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="N251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Norrby mosse, Norrby mosse, Srm</t>
+          <t>Vargklåva mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>686888</v>
+        <v>687268</v>
       </c>
       <c r="R251" t="n">
-        <v>6563206</v>
+        <v>6563319</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -29129,12 +29131,17 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>Strax nedom klippbrant</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -29143,33 +29150,34 @@
       <c r="AE251" t="b">
         <v>0</v>
       </c>
+      <c r="AF251" t="inlineStr"/>
       <c r="AG251" t="b">
         <v>0</v>
       </c>
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116746465</t>
+          <t>https://artportalen.se/Sighting/96643468</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>135827249</v>
+        <v>116746465</v>
       </c>
       <c r="B252" t="n">
-        <v>98209</v>
+        <v>97989</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29195,20 +29203,16 @@
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
-      <c r="J252" t="inlineStr"/>
-      <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr"/>
-      <c r="N252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse, Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>687270</v>
+        <v>686888</v>
       </c>
       <c r="R252" t="n">
-        <v>6563321</v>
+        <v>6563206</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -29235,17 +29239,12 @@
       </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>Återfynd, tidigare rapporterad 2021.</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -29254,34 +29253,33 @@
       <c r="AE252" t="b">
         <v>0</v>
       </c>
-      <c r="AF252" t="inlineStr"/>
       <c r="AG252" t="b">
         <v>0</v>
       </c>
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135827249</t>
+          <t>https://artportalen.se/Sighting/116746465</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>121742517</v>
+        <v>135827249</v>
       </c>
       <c r="B253" t="n">
-        <v>97983</v>
+        <v>98209</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29289,16 +29287,16 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -29307,16 +29305,20 @@
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="N253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Norrby mosse, Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>686859</v>
+        <v>687270</v>
       </c>
       <c r="R253" t="n">
-        <v>6562875</v>
+        <v>6563321</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -29343,12 +29345,17 @@
       </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>Återfynd, tidigare rapporterad 2021.</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -29357,30 +29364,31 @@
       <c r="AE253" t="b">
         <v>0</v>
       </c>
+      <c r="AF253" t="inlineStr"/>
       <c r="AG253" t="b">
         <v>0</v>
       </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121742517</t>
+          <t>https://artportalen.se/Sighting/135827249</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>122928987</v>
+        <v>121742517</v>
       </c>
       <c r="B254" t="n">
         <v>97983</v>
@@ -29409,20 +29417,16 @@
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="J254" t="inlineStr"/>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
-      <c r="N254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Norrby mosse, Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>686389</v>
+        <v>686859</v>
       </c>
       <c r="R254" t="n">
-        <v>6562967</v>
+        <v>6562875</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -29449,22 +29453,12 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z254" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB254" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -29479,24 +29473,24 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122928987</t>
+          <t>https://artportalen.se/Sighting/121742517</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>122930294</v>
+        <v>122928987</v>
       </c>
       <c r="B255" t="n">
         <v>97983</v>
@@ -29535,13 +29529,13 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>686824</v>
+        <v>686389</v>
       </c>
       <c r="R255" t="n">
-        <v>6562778</v>
+        <v>6562967</v>
       </c>
       <c r="S255" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -29570,7 +29564,7 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
@@ -29580,7 +29574,7 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29606,13 +29600,13 @@
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122930294</t>
+          <t>https://artportalen.se/Sighting/122928987</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>125963374</v>
+        <v>122930294</v>
       </c>
       <c r="B256" t="n">
         <v>97983</v>
@@ -29641,19 +29635,23 @@
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
+      <c r="J256" t="inlineStr"/>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Norrby mosse, Norrby mosse, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>686873</v>
+        <v>686824</v>
       </c>
       <c r="R256" t="n">
-        <v>6562867</v>
+        <v>6562778</v>
       </c>
       <c r="S256" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -29677,12 +29675,22 @@
       </c>
       <c r="Y256" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -29697,24 +29705,24 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125963374</t>
+          <t>https://artportalen.se/Sighting/122930294</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>125976418</v>
+        <v>125963374</v>
       </c>
       <c r="B257" t="n">
         <v>97983</v>
@@ -29743,23 +29751,19 @@
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
-      <c r="J257" t="inlineStr"/>
-      <c r="K257" t="inlineStr"/>
-      <c r="L257" t="inlineStr"/>
-      <c r="N257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Norrby mosse Ö om, Srm</t>
+          <t>Norrby mosse, Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>686836</v>
+        <v>686873</v>
       </c>
       <c r="R257" t="n">
-        <v>6563105</v>
+        <v>6562867</v>
       </c>
       <c r="S257" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -29791,42 +29795,36 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC257" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i skogskärr</t>
-        </is>
-      </c>
       <c r="AD257" t="b">
         <v>0</v>
       </c>
       <c r="AE257" t="b">
         <v>0</v>
       </c>
-      <c r="AF257" t="inlineStr"/>
       <c r="AG257" t="b">
         <v>0</v>
       </c>
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125976418</t>
+          <t>https://artportalen.se/Sighting/125963374</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>126061082</v>
+        <v>125976418</v>
       </c>
       <c r="B258" t="n">
         <v>97983</v>
@@ -29855,19 +29853,23 @@
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse Ö om, Srm</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>687079</v>
+        <v>686836</v>
       </c>
       <c r="R258" t="n">
-        <v>6563240</v>
+        <v>6563105</v>
       </c>
       <c r="S258" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -29894,19 +29896,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z258" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB258" t="inlineStr">
-        <is>
-          <t>15:22</t>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i skogskärr</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -29915,30 +29912,31 @@
       <c r="AE258" t="b">
         <v>0</v>
       </c>
+      <c r="AF258" t="inlineStr"/>
       <c r="AG258" t="b">
         <v>0</v>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061082</t>
+          <t>https://artportalen.se/Sighting/125976418</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>126061090</v>
+        <v>126061082</v>
       </c>
       <c r="B259" t="n">
         <v>97983</v>
@@ -29973,10 +29971,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>686871</v>
+        <v>687079</v>
       </c>
       <c r="R259" t="n">
-        <v>6562972</v>
+        <v>6563240</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -30008,7 +30006,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -30018,7 +30016,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -30044,13 +30042,13 @@
       <c r="AY259" t="inlineStr"/>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061090</t>
+          <t>https://artportalen.se/Sighting/126061082</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>126061103</v>
+        <v>126061090</v>
       </c>
       <c r="B260" t="n">
         <v>97983</v>
@@ -30085,10 +30083,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>686811</v>
+        <v>686871</v>
       </c>
       <c r="R260" t="n">
-        <v>6562803</v>
+        <v>6562972</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -30120,7 +30118,7 @@
       </c>
       <c r="Z260" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -30130,7 +30128,7 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -30150,19 +30148,19 @@
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061103</t>
+          <t>https://artportalen.se/Sighting/126061090</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>126061111</v>
+        <v>126061103</v>
       </c>
       <c r="B261" t="n">
         <v>97983</v>
@@ -30197,10 +30195,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>687030</v>
+        <v>686811</v>
       </c>
       <c r="R261" t="n">
-        <v>6562755</v>
+        <v>6562803</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -30232,7 +30230,7 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
@@ -30242,7 +30240,7 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -30268,16 +30266,16 @@
       <c r="AY261" t="inlineStr"/>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061111</t>
+          <t>https://artportalen.se/Sighting/126061103</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>136347172</v>
+        <v>126061111</v>
       </c>
       <c r="B262" t="n">
-        <v>98215</v>
+        <v>97983</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -30303,20 +30301,16 @@
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
-      <c r="J262" t="inlineStr"/>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
-      <c r="N262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>686861</v>
+        <v>687030</v>
       </c>
       <c r="R262" t="n">
-        <v>6563127</v>
+        <v>6562755</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -30343,12 +30337,22 @@
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -30357,31 +30361,30 @@
       <c r="AE262" t="b">
         <v>0</v>
       </c>
-      <c r="AF262" t="inlineStr"/>
       <c r="AG262" t="b">
         <v>0</v>
       </c>
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136347172</t>
+          <t>https://artportalen.se/Sighting/126061111</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>136394245</v>
+        <v>136347172</v>
       </c>
       <c r="B263" t="n">
         <v>98215</v>
@@ -30410,19 +30413,23 @@
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
+      <c r="J263" t="inlineStr"/>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="N263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>687263</v>
+        <v>686861</v>
       </c>
       <c r="R263" t="n">
-        <v>6563324</v>
+        <v>6563127</v>
       </c>
       <c r="S263" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -30446,22 +30453,12 @@
       </c>
       <c r="Y263" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z263" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB263" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -30470,33 +30467,34 @@
       <c r="AE263" t="b">
         <v>0</v>
       </c>
+      <c r="AF263" t="inlineStr"/>
       <c r="AG263" t="b">
         <v>0</v>
       </c>
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136394245</t>
+          <t>https://artportalen.se/Sighting/136347172</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>122929342</v>
+        <v>136394245</v>
       </c>
       <c r="B264" t="n">
-        <v>97986</v>
+        <v>98215</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30504,16 +30502,16 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -30522,23 +30520,19 @@
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
-      <c r="J264" t="inlineStr"/>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
-      <c r="N264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>686569</v>
+        <v>687263</v>
       </c>
       <c r="R264" t="n">
-        <v>6562949</v>
+        <v>6563324</v>
       </c>
       <c r="S264" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -30562,22 +30556,22 @@
       </c>
       <c r="Y264" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="Z264" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -30592,24 +30586,24 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929342</t>
+          <t>https://artportalen.se/Sighting/136394245</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>126061110</v>
+        <v>122929342</v>
       </c>
       <c r="B265" t="n">
         <v>97986</v>
@@ -30638,19 +30632,23 @@
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>687029</v>
+        <v>686569</v>
       </c>
       <c r="R265" t="n">
-        <v>6562759</v>
+        <v>6562949</v>
       </c>
       <c r="S265" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -30674,22 +30672,22 @@
       </c>
       <c r="Y265" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z265" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -30704,27 +30702,27 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061110</t>
+          <t>https://artportalen.se/Sighting/122929342</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>101523203</v>
+        <v>126061110</v>
       </c>
       <c r="B266" t="n">
-        <v>99140</v>
+        <v>97986</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -30732,38 +30730,34 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
-      <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
-      <c r="N266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>NO Norrby Mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>687050</v>
+        <v>687029</v>
       </c>
       <c r="R266" t="n">
-        <v>6563327</v>
+        <v>6562759</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -30790,12 +30784,22 @@
       </c>
       <c r="Y266" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -30804,31 +30808,30 @@
       <c r="AE266" t="b">
         <v>0</v>
       </c>
-      <c r="AF266" t="inlineStr"/>
       <c r="AG266" t="b">
         <v>0</v>
       </c>
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101523203</t>
+          <t>https://artportalen.se/Sighting/126061110</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>117554655</v>
+        <v>101523203</v>
       </c>
       <c r="B267" t="n">
         <v>99140</v>
@@ -30858,23 +30861,19 @@
       </c>
       <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr"/>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr"/>
       <c r="N267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>NO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>687062</v>
+        <v>687050</v>
       </c>
       <c r="R267" t="n">
-        <v>6563349</v>
+        <v>6563327</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -30901,12 +30900,12 @@
       </c>
       <c r="Y267" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -30933,13 +30932,13 @@
       <c r="AY267" t="inlineStr"/>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117554655</t>
+          <t>https://artportalen.se/Sighting/101523203</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>126234400</v>
+        <v>117554655</v>
       </c>
       <c r="B268" t="n">
         <v>99140</v>
@@ -30967,16 +30966,8 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I268" t="inlineStr"/>
+      <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -30986,14 +30977,14 @@
       <c r="N268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>686788</v>
+        <v>687062</v>
       </c>
       <c r="R268" t="n">
-        <v>6563073</v>
+        <v>6563349</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -31020,12 +31011,12 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -31041,27 +31032,27 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234400</t>
+          <t>https://artportalen.se/Sighting/117554655</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>134487623</v>
+        <v>126234400</v>
       </c>
       <c r="B269" t="n">
-        <v>99217</v>
+        <v>99140</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31086,8 +31077,16 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr"/>
-      <c r="J269" t="inlineStr"/>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K269" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -31097,17 +31096,17 @@
       <c r="N269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>687067</v>
+        <v>686788</v>
       </c>
       <c r="R269" t="n">
-        <v>6563342</v>
+        <v>6563073</v>
       </c>
       <c r="S269" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -31131,17 +31130,12 @@
       </c>
       <c r="Y269" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>Ett tiotal i blom samt flera plantor med endast blad.  Återfynd.</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -31157,24 +31151,24 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134487623</t>
+          <t>https://artportalen.se/Sighting/126234400</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>134487656</v>
+        <v>134487623</v>
       </c>
       <c r="B270" t="n">
         <v>99217</v>
@@ -31217,13 +31211,13 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>686835</v>
+        <v>687067</v>
       </c>
       <c r="R270" t="n">
-        <v>6563212</v>
+        <v>6563342</v>
       </c>
       <c r="S270" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -31257,7 +31251,7 @@
       </c>
       <c r="AC270" t="inlineStr">
         <is>
-          <t>2 i blom samt några plantor med endast blad.</t>
+          <t>Ett tiotal i blom samt flera plantor med endast blad.  Återfynd.</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -31284,13 +31278,13 @@
       <c r="AY270" t="inlineStr"/>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134487656</t>
+          <t>https://artportalen.se/Sighting/134487623</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>134488457</v>
+        <v>134487656</v>
       </c>
       <c r="B271" t="n">
         <v>99217</v>
@@ -31333,10 +31327,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>687294</v>
+        <v>686835</v>
       </c>
       <c r="R271" t="n">
-        <v>6563391</v>
+        <v>6563212</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -31373,7 +31367,7 @@
       </c>
       <c r="AC271" t="inlineStr">
         <is>
-          <t>2 i blom samt fler med endast blad.</t>
+          <t>2 i blom samt några plantor med endast blad.</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -31400,43 +31394,48 @@
       <c r="AY271" t="inlineStr"/>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134488457</t>
+          <t>https://artportalen.se/Sighting/134487656</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>129564006</v>
+        <v>134488457</v>
       </c>
       <c r="B272" t="n">
-        <v>79350</v>
+        <v>99217</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>260591</v>
+        <v>221952</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr"/>
       <c r="N272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
@@ -31444,10 +31443,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>686681</v>
+        <v>687294</v>
       </c>
       <c r="R272" t="n">
-        <v>6563025</v>
+        <v>6563391</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -31474,19 +31473,24 @@
       </c>
       <c r="Y272" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>2 i blom samt fler med endast blad.</t>
         </is>
       </c>
       <c r="AD272" t="b">
         <v>0</v>
       </c>
       <c r="AE272" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF272" t="inlineStr"/>
       <c r="AG272" t="b">
@@ -31505,6 +31509,112 @@
       </c>
       <c r="AY272" t="inlineStr"/>
       <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134488457</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>129564006</v>
+      </c>
+      <c r="B273" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q273" t="n">
+        <v>686681</v>
+      </c>
+      <c r="R273" t="n">
+        <v>6563025</v>
+      </c>
+      <c r="S273" t="n">
+        <v>10</v>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE273" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF273" t="inlineStr"/>
+      <c r="AG273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT273" t="inlineStr"/>
+      <c r="AW273" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX273" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129564006</t>
         </is>
@@ -31783,6 +31893,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -5102,7 +5102,7 @@
         <v>136947605</v>
       </c>
       <c r="B41" t="n">
-        <v>92787</v>
+        <v>92789</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>136346850</v>
       </c>
       <c r="B45" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>136346893</v>
       </c>
       <c r="B46" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>136557175</v>
       </c>
       <c r="B47" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>136422293</v>
       </c>
       <c r="B55" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136631756</v>
       </c>
       <c r="B56" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>136631891</v>
       </c>
       <c r="B57" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>136631926</v>
       </c>
       <c r="B79" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>136557135</v>
       </c>
       <c r="B82" t="n">
-        <v>91594</v>
+        <v>91596</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>136635740</v>
       </c>
       <c r="B83" t="n">
-        <v>91594</v>
+        <v>91596</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>136946030</v>
       </c>
       <c r="B84" t="n">
-        <v>91594</v>
+        <v>91596</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>136778691</v>
       </c>
       <c r="B89" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>136778733</v>
       </c>
       <c r="B90" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10867,7 +10867,7 @@
         <v>136422316</v>
       </c>
       <c r="B93" t="n">
-        <v>92791</v>
+        <v>92793</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>136557228</v>
       </c>
       <c r="B94" t="n">
-        <v>92791</v>
+        <v>92793</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>136635736</v>
       </c>
       <c r="B108" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>136635737</v>
       </c>
       <c r="B109" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>136737386</v>
       </c>
       <c r="B116" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>136329900</v>
       </c>
       <c r="B250" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>136422457</v>
       </c>
       <c r="B251" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>136347172</v>
       </c>
       <c r="B264" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>136394245</v>
       </c>
       <c r="B265" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -5102,7 +5102,7 @@
         <v>136947605</v>
       </c>
       <c r="B41" t="n">
-        <v>92789</v>
+        <v>92791</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>136346850</v>
       </c>
       <c r="B45" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>136346893</v>
       </c>
       <c r="B46" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>136557175</v>
       </c>
       <c r="B47" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>136422293</v>
       </c>
       <c r="B55" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136631756</v>
       </c>
       <c r="B56" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>136631891</v>
       </c>
       <c r="B57" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>136631926</v>
       </c>
       <c r="B79" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>136557135</v>
       </c>
       <c r="B82" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>136635740</v>
       </c>
       <c r="B83" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>136946030</v>
       </c>
       <c r="B84" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>136778691</v>
       </c>
       <c r="B89" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>136778733</v>
       </c>
       <c r="B90" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10867,7 +10867,7 @@
         <v>136422316</v>
       </c>
       <c r="B93" t="n">
-        <v>92793</v>
+        <v>92795</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>136557228</v>
       </c>
       <c r="B94" t="n">
-        <v>92793</v>
+        <v>92795</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>136635736</v>
       </c>
       <c r="B108" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>136635737</v>
       </c>
       <c r="B109" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>136737386</v>
       </c>
       <c r="B116" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
@@ -29073,7 +29073,7 @@
         <v>136422457</v>
       </c>
       <c r="B251" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>136347172</v>
       </c>
       <c r="B264" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>136394245</v>
       </c>
       <c r="B265" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ288"/>
+  <dimension ref="A1:AZ289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5102,7 +5102,7 @@
         <v>136947605</v>
       </c>
       <c r="B41" t="n">
-        <v>92791</v>
+        <v>92792</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>136557175</v>
       </c>
       <c r="B47" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>136422293</v>
       </c>
       <c r="B55" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136631756</v>
       </c>
       <c r="B56" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>136631891</v>
       </c>
       <c r="B57" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>137045816</v>
       </c>
       <c r="B58" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>136631926</v>
       </c>
       <c r="B80" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>136557135</v>
       </c>
       <c r="B83" t="n">
-        <v>91598</v>
+        <v>91599</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>136635740</v>
       </c>
       <c r="B84" t="n">
-        <v>91598</v>
+        <v>91599</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>136946030</v>
       </c>
       <c r="B85" t="n">
-        <v>91598</v>
+        <v>91599</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>136778691</v>
       </c>
       <c r="B90" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>136778733</v>
       </c>
       <c r="B91" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>137045788</v>
       </c>
       <c r="B92" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>137045804</v>
       </c>
       <c r="B93" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>137045811</v>
       </c>
       <c r="B94" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>137045817</v>
       </c>
       <c r="B95" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>137045826</v>
       </c>
       <c r="B96" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>137045864</v>
       </c>
       <c r="B97" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>137045871</v>
       </c>
       <c r="B98" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>137045877</v>
       </c>
       <c r="B99" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>137045887</v>
       </c>
       <c r="B100" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>137088961</v>
       </c>
       <c r="B101" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>137089019</v>
       </c>
       <c r="B102" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>136422316</v>
       </c>
       <c r="B105" t="n">
-        <v>92795</v>
+        <v>92796</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>136557228</v>
       </c>
       <c r="B106" t="n">
-        <v>92795</v>
+        <v>92796</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>136635736</v>
       </c>
       <c r="B120" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>136635737</v>
       </c>
       <c r="B121" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>136737386</v>
       </c>
       <c r="B128" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -20121,32 +20121,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>136346869</v>
+        <v>137106201</v>
       </c>
       <c r="B174" t="n">
-        <v>58164</v>
+        <v>58169</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -20164,10 +20164,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>687222</v>
+        <v>687134</v>
       </c>
       <c r="R174" t="n">
-        <v>6563288</v>
+        <v>6563215</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20194,12 +20194,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20225,13 +20225,13 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136346869</t>
+          <t>https://artportalen.se/Sighting/137106201</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>136631771</v>
+        <v>136346869</v>
       </c>
       <c r="B175" t="n">
         <v>58164</v>
@@ -20274,13 +20274,13 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>686948</v>
+        <v>687222</v>
       </c>
       <c r="R175" t="n">
-        <v>6563152</v>
+        <v>6563288</v>
       </c>
       <c r="S175" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -20304,12 +20304,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20335,16 +20335,16 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136631771</t>
+          <t>https://artportalen.se/Sighting/136346869</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121859656</v>
+        <v>136631771</v>
       </c>
       <c r="B176" t="n">
-        <v>5199</v>
+        <v>58164</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20352,16 +20352,16 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>105930</v>
+        <v>103023</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -20370,19 +20370,27 @@
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>687094</v>
+        <v>686948</v>
       </c>
       <c r="R176" t="n">
-        <v>6563235</v>
+        <v>6563152</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -20406,22 +20414,12 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20432,48 +20430,28 @@
       </c>
       <c r="AG176" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ176" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK176" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL176" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO176" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859656</t>
+          <t>https://artportalen.se/Sighting/136631771</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>126061088</v>
+        <v>121859656</v>
       </c>
       <c r="B177" t="n">
         <v>5199</v>
@@ -20504,14 +20482,14 @@
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>686865</v>
+        <v>687094</v>
       </c>
       <c r="R177" t="n">
-        <v>6562977</v>
+        <v>6563235</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20538,22 +20516,22 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20577,12 +20555,12 @@
       </c>
       <c r="AL177" t="inlineStr">
         <is>
-          <t>Klen torr granlåga.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>Picea abies # Klen torr granlåga.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr"/>
@@ -20593,19 +20571,19 @@
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061088</t>
+          <t>https://artportalen.se/Sighting/121859656</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126061109</v>
+        <v>126061088</v>
       </c>
       <c r="B178" t="n">
         <v>5199</v>
@@ -20640,10 +20618,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>686946</v>
+        <v>686865</v>
       </c>
       <c r="R178" t="n">
-        <v>6562741</v>
+        <v>6562977</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20675,7 +20653,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -20685,7 +20663,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20725,22 +20703,22 @@
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061109</t>
+          <t>https://artportalen.se/Sighting/126061088</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121859629</v>
+        <v>126061109</v>
       </c>
       <c r="B179" t="n">
-        <v>8455</v>
+        <v>5199</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20748,34 +20726,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>686792</v>
+        <v>686946</v>
       </c>
       <c r="R179" t="n">
-        <v>6563030</v>
+        <v>6562741</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20802,22 +20780,22 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20831,17 +20809,22 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL179" t="inlineStr">
+        <is>
+          <t>Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr"/>
@@ -20852,19 +20835,19 @@
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859629</t>
+          <t>https://artportalen.se/Sighting/126061109</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>121859631</v>
+        <v>121859629</v>
       </c>
       <c r="B180" t="n">
         <v>8455</v>
@@ -20899,10 +20882,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>686934</v>
+        <v>686792</v>
       </c>
       <c r="R180" t="n">
-        <v>6563148</v>
+        <v>6563030</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20934,7 +20917,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -20944,7 +20927,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20985,13 +20968,13 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859631</t>
+          <t>https://artportalen.se/Sighting/121859629</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>122929535</v>
+        <v>121859631</v>
       </c>
       <c r="B181" t="n">
         <v>8455</v>
@@ -21019,29 +21002,20 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>686612</v>
+        <v>686934</v>
       </c>
       <c r="R181" t="n">
-        <v>6562882</v>
+        <v>6563148</v>
       </c>
       <c r="S181" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -21065,22 +21039,22 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21091,31 +21065,46 @@
       </c>
       <c r="AG181" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929535</t>
+          <t>https://artportalen.se/Sighting/121859631</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>136259916</v>
+        <v>122929535</v>
       </c>
       <c r="B182" t="n">
-        <v>8463</v>
+        <v>8455</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21140,29 +21129,29 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>686457</v>
+        <v>686612</v>
       </c>
       <c r="R182" t="n">
-        <v>6563062</v>
+        <v>6562882</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21186,12 +21175,22 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21200,34 +21199,33 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
-      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136259916</t>
+          <t>https://artportalen.se/Sighting/122929535</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>125974903</v>
+        <v>136259916</v>
       </c>
       <c r="B183" t="n">
-        <v>8444</v>
+        <v>8463</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21235,28 +21233,24 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr"/>
@@ -21268,17 +21262,17 @@
       <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>söder om Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>686838</v>
+        <v>686457</v>
       </c>
       <c r="R183" t="n">
-        <v>6562733</v>
+        <v>6563062</v>
       </c>
       <c r="S183" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21302,17 +21296,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>gammal björklåga med spår längs hela stammen</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21325,47 +21314,27 @@
       <c r="AG183" t="b">
         <v>0</v>
       </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO183" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Betula pendula</t>
-        </is>
-      </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125974903</t>
+          <t>https://artportalen.se/Sighting/136259916</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>126061086</v>
+        <v>125974903</v>
       </c>
       <c r="B184" t="n">
         <v>8444</v>
@@ -21393,20 +21362,33 @@
           <t>Janson, 1856</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>söder om Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>686932</v>
+        <v>686838</v>
       </c>
       <c r="R184" t="n">
-        <v>6563067</v>
+        <v>6562733</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21433,19 +21415,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>15:00</t>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>gammal björklåga med spår längs hela stammen</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21454,50 +21431,51 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
+      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vårtbjörk</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
         <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL184" t="inlineStr">
-        <is>
-          <t>Barklös björklåga.</t>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>Betula # Barklös björklåga.</t>
+          <t>Wood surface of dead wood # Betula pendula</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061086</t>
+          <t>https://artportalen.se/Sighting/125974903</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>126061105</v>
+        <v>126061086</v>
       </c>
       <c r="B185" t="n">
         <v>8444</v>
@@ -21532,10 +21510,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>686860</v>
+        <v>686932</v>
       </c>
       <c r="R185" t="n">
-        <v>6562743</v>
+        <v>6563067</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21567,7 +21545,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -21577,7 +21555,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21599,9 +21577,14 @@
           <t>Betula</t>
         </is>
       </c>
+      <c r="AL185" t="inlineStr">
+        <is>
+          <t>Barklös björklåga.</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Betula # Barklös björklåga.</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>
@@ -21612,22 +21595,22 @@
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061105</t>
+          <t>https://artportalen.se/Sighting/126061086</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>136635739</v>
+        <v>126061105</v>
       </c>
       <c r="B186" t="n">
-        <v>8452</v>
+        <v>8444</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21655,17 +21638,17 @@
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Utanför Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>686973</v>
+        <v>686860</v>
       </c>
       <c r="R186" t="n">
-        <v>6563106</v>
+        <v>6562743</v>
       </c>
       <c r="S186" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21689,27 +21672,22 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>Björklåga</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21720,31 +21698,46 @@
       </c>
       <c r="AG186" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO186" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Vendela Ström</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Vendela Ström</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136635739</t>
+          <t>https://artportalen.se/Sighting/126061105</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>136767157</v>
+        <v>136635739</v>
       </c>
       <c r="B187" t="n">
-        <v>56875</v>
+        <v>8452</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21752,37 +21745,37 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>205992</v>
+        <v>106554</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Norrby torp, Tyresta, Srm</t>
+          <t>Utanför Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>687260</v>
+        <v>686973</v>
       </c>
       <c r="R187" t="n">
-        <v>6563241</v>
+        <v>6563106</v>
       </c>
       <c r="S187" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21806,22 +21799,27 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>04:39</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>04:39</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Björklåga</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21836,24 +21834,24 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Vendela Ström</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Vendela Ström</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767157</t>
+          <t>https://artportalen.se/Sighting/136635739</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>136867583</v>
+        <v>136767157</v>
       </c>
       <c r="B188" t="n">
         <v>56875</v>
@@ -21888,10 +21886,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>687164</v>
+        <v>687260</v>
       </c>
       <c r="R188" t="n">
-        <v>6563337</v>
+        <v>6563241</v>
       </c>
       <c r="S188" t="n">
         <v>25</v>
@@ -21918,22 +21916,22 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>04:12</t>
+          <t>04:39</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>04:12</t>
+          <t>04:39</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21959,13 +21957,13 @@
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867583</t>
+          <t>https://artportalen.se/Sighting/136767157</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>136867591</v>
+        <v>136867583</v>
       </c>
       <c r="B189" t="n">
         <v>56875</v>
@@ -22000,10 +21998,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>686871</v>
+        <v>687164</v>
       </c>
       <c r="R189" t="n">
-        <v>6563175</v>
+        <v>6563337</v>
       </c>
       <c r="S189" t="n">
         <v>25</v>
@@ -22030,22 +22028,22 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>04:19</t>
+          <t>04:12</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>04:19</t>
+          <t>04:12</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -22071,16 +22069,16 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867591</t>
+          <t>https://artportalen.se/Sighting/136867583</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>136767122</v>
+        <v>136867591</v>
       </c>
       <c r="B190" t="n">
-        <v>56887</v>
+        <v>56875</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22088,21 +22086,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -22112,10 +22110,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>686692</v>
+        <v>686871</v>
       </c>
       <c r="R190" t="n">
-        <v>6563011</v>
+        <v>6563175</v>
       </c>
       <c r="S190" t="n">
         <v>25</v>
@@ -22142,22 +22140,22 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>04:19</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>04:19</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22183,13 +22181,13 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767122</t>
+          <t>https://artportalen.se/Sighting/136867591</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>136767160</v>
+        <v>136767122</v>
       </c>
       <c r="B191" t="n">
         <v>56887</v>
@@ -22224,10 +22222,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>687260</v>
+        <v>686692</v>
       </c>
       <c r="R191" t="n">
-        <v>6563241</v>
+        <v>6563011</v>
       </c>
       <c r="S191" t="n">
         <v>25</v>
@@ -22254,22 +22252,22 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>01:27</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>01:27</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22295,13 +22293,13 @@
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767160</t>
+          <t>https://artportalen.se/Sighting/136767122</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>136867584</v>
+        <v>136767160</v>
       </c>
       <c r="B192" t="n">
         <v>56887</v>
@@ -22336,10 +22334,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>687164</v>
+        <v>687260</v>
       </c>
       <c r="R192" t="n">
-        <v>6563337</v>
+        <v>6563241</v>
       </c>
       <c r="S192" t="n">
         <v>25</v>
@@ -22366,22 +22364,22 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>01:27</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>01:27</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22407,13 +22405,13 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867584</t>
+          <t>https://artportalen.se/Sighting/136767160</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>136867597</v>
+        <v>136867584</v>
       </c>
       <c r="B193" t="n">
         <v>56887</v>
@@ -22448,10 +22446,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>686871</v>
+        <v>687164</v>
       </c>
       <c r="R193" t="n">
-        <v>6563175</v>
+        <v>6563337</v>
       </c>
       <c r="S193" t="n">
         <v>25</v>
@@ -22478,22 +22476,22 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>23:43</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>23:43</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22519,36 +22517,40 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867597</t>
+          <t>https://artportalen.se/Sighting/136867584</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>136767120</v>
+        <v>136867597</v>
       </c>
       <c r="B194" t="n">
-        <v>56866</v>
+        <v>56887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr"/>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
@@ -22556,10 +22558,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>686692</v>
+        <v>686871</v>
       </c>
       <c r="R194" t="n">
-        <v>6563011</v>
+        <v>6563175</v>
       </c>
       <c r="S194" t="n">
         <v>25</v>
@@ -22586,22 +22588,22 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>23:43</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>23:43</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22627,13 +22629,13 @@
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767120</t>
+          <t>https://artportalen.se/Sighting/136867597</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>136767159</v>
+        <v>136767120</v>
       </c>
       <c r="B195" t="n">
         <v>56866</v>
@@ -22664,10 +22666,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>687260</v>
+        <v>686692</v>
       </c>
       <c r="R195" t="n">
-        <v>6563241</v>
+        <v>6563011</v>
       </c>
       <c r="S195" t="n">
         <v>25</v>
@@ -22694,22 +22696,22 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22735,13 +22737,13 @@
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767159</t>
+          <t>https://artportalen.se/Sighting/136767120</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>136867586</v>
+        <v>136767159</v>
       </c>
       <c r="B196" t="n">
         <v>56866</v>
@@ -22772,10 +22774,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>687164</v>
+        <v>687260</v>
       </c>
       <c r="R196" t="n">
-        <v>6563337</v>
+        <v>6563241</v>
       </c>
       <c r="S196" t="n">
         <v>25</v>
@@ -22802,22 +22804,22 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22843,13 +22845,13 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867586</t>
+          <t>https://artportalen.se/Sighting/136767159</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>136867588</v>
+        <v>136867586</v>
       </c>
       <c r="B197" t="n">
         <v>56866</v>
@@ -22880,10 +22882,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>686871</v>
+        <v>687164</v>
       </c>
       <c r="R197" t="n">
-        <v>6563175</v>
+        <v>6563337</v>
       </c>
       <c r="S197" t="n">
         <v>25</v>
@@ -22910,22 +22912,22 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>22:16</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>22:16</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22951,16 +22953,16 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867588</t>
+          <t>https://artportalen.se/Sighting/136867586</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>136767162</v>
+        <v>136867588</v>
       </c>
       <c r="B198" t="n">
-        <v>56889</v>
+        <v>56866</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22968,23 +22970,19 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
@@ -22992,10 +22990,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>687260</v>
+        <v>686871</v>
       </c>
       <c r="R198" t="n">
-        <v>6563241</v>
+        <v>6563175</v>
       </c>
       <c r="S198" t="n">
         <v>25</v>
@@ -23022,22 +23020,22 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>00:57</t>
+          <t>22:16</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>00:57</t>
+          <t>22:16</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -23063,13 +23061,13 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767162</t>
+          <t>https://artportalen.se/Sighting/136867588</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>136867594</v>
+        <v>136767162</v>
       </c>
       <c r="B199" t="n">
         <v>56889</v>
@@ -23104,10 +23102,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>686871</v>
+        <v>687260</v>
       </c>
       <c r="R199" t="n">
-        <v>6563175</v>
+        <v>6563241</v>
       </c>
       <c r="S199" t="n">
         <v>25</v>
@@ -23134,22 +23132,22 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>00:57</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>00:57</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -23175,33 +23173,33 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867594</t>
+          <t>https://artportalen.se/Sighting/136767162</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>111182876</v>
+        <v>136867594</v>
       </c>
       <c r="B200" t="n">
-        <v>58790</v>
+        <v>56889</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>208245</v>
+        <v>206002</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -23209,29 +23207,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>686971</v>
+        <v>686871</v>
       </c>
       <c r="R200" t="n">
-        <v>6563333</v>
+        <v>6563175</v>
       </c>
       <c r="S200" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -23255,12 +23244,22 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -23269,31 +23268,30 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
-      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111182876</t>
+          <t>https://artportalen.se/Sighting/136867594</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>126061089</v>
+        <v>111182876</v>
       </c>
       <c r="B201" t="n">
         <v>58790</v>
@@ -23326,21 +23324,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>686871</v>
+        <v>686971</v>
       </c>
       <c r="R201" t="n">
-        <v>6562972</v>
+        <v>6563333</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -23367,22 +23365,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23391,30 +23379,31 @@
       <c r="AE201" t="b">
         <v>0</v>
       </c>
+      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061089</t>
+          <t>https://artportalen.se/Sighting/111182876</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>126061098</v>
+        <v>126061089</v>
       </c>
       <c r="B202" t="n">
         <v>58790</v>
@@ -23442,17 +23431,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>686857</v>
+        <v>686871</v>
       </c>
       <c r="R202" t="n">
-        <v>6562875</v>
+        <v>6562972</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -23484,7 +23482,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -23494,7 +23492,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23514,19 +23512,19 @@
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061098</t>
+          <t>https://artportalen.se/Sighting/126061089</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128095464</v>
+        <v>126061098</v>
       </c>
       <c r="B203" t="n">
         <v>58790</v>
@@ -23554,30 +23552,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>687155</v>
+        <v>686857</v>
       </c>
       <c r="R203" t="n">
-        <v>6563193</v>
+        <v>6562875</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23604,12 +23589,22 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23618,34 +23613,33 @@
       <c r="AE203" t="b">
         <v>0</v>
       </c>
-      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128095464</t>
+          <t>https://artportalen.se/Sighting/126061098</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>134488564</v>
+        <v>128095464</v>
       </c>
       <c r="B204" t="n">
-        <v>58812</v>
+        <v>58790</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23676,7 +23670,11 @@
         </is>
       </c>
       <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
@@ -23686,10 +23684,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>687272</v>
+        <v>687155</v>
       </c>
       <c r="R204" t="n">
-        <v>6563263</v>
+        <v>6563193</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23716,17 +23714,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>Ca 2-3 cm lång.</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23753,16 +23746,16 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134488564</t>
+          <t>https://artportalen.se/Sighting/128095464</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>126061108</v>
+        <v>134488564</v>
       </c>
       <c r="B205" t="n">
-        <v>58817</v>
+        <v>58812</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23770,21 +23763,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -23792,26 +23785,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>686907</v>
+        <v>687272</v>
       </c>
       <c r="R205" t="n">
-        <v>6562760</v>
+        <v>6563263</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23838,22 +23826,17 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>Ca 2-3 cm lång.</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23862,33 +23845,34 @@
       <c r="AE205" t="b">
         <v>0</v>
       </c>
+      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061108</t>
+          <t>https://artportalen.se/Sighting/134488564</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>136777569</v>
+        <v>126061108</v>
       </c>
       <c r="B206" t="n">
-        <v>58872</v>
+        <v>58817</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23913,20 +23897,34 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Norrby torp, Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>687280</v>
+        <v>686907</v>
       </c>
       <c r="R206" t="n">
-        <v>6563262</v>
+        <v>6562760</v>
       </c>
       <c r="S206" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -23950,22 +23948,22 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23985,22 +23983,22 @@
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136777569</t>
+          <t>https://artportalen.se/Sighting/126061108</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>126061081</v>
+        <v>136777569</v>
       </c>
       <c r="B207" t="n">
-        <v>58815</v>
+        <v>58872</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24008,51 +24006,37 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>208250</v>
+        <v>208249</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>687058</v>
+        <v>687280</v>
       </c>
       <c r="R207" t="n">
-        <v>6563228</v>
+        <v>6563262</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -24076,22 +24060,22 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -24111,22 +24095,22 @@
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061081</t>
+          <t>https://artportalen.se/Sighting/136777569</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>117554483</v>
+        <v>126061081</v>
       </c>
       <c r="B208" t="n">
-        <v>99035</v>
+        <v>58815</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24134,41 +24118,51 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>219790</v>
+        <v>208250</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>686878</v>
+        <v>687058</v>
       </c>
       <c r="R208" t="n">
-        <v>6562971</v>
+        <v>6563228</v>
       </c>
       <c r="S208" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -24192,12 +24186,22 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -24206,31 +24210,30 @@
       <c r="AE208" t="b">
         <v>0</v>
       </c>
-      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117554483</t>
+          <t>https://artportalen.se/Sighting/126061081</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>126003792</v>
+        <v>117554483</v>
       </c>
       <c r="B209" t="n">
         <v>99035</v>
@@ -24265,17 +24268,17 @@
       <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>687046</v>
+        <v>686878</v>
       </c>
       <c r="R209" t="n">
-        <v>6563346</v>
+        <v>6562971</v>
       </c>
       <c r="S209" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -24299,12 +24302,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -24331,13 +24334,13 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126003792</t>
+          <t>https://artportalen.se/Sighting/117554483</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>126005160</v>
+        <v>126003792</v>
       </c>
       <c r="B210" t="n">
         <v>99035</v>
@@ -24376,10 +24379,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>687034</v>
+        <v>687046</v>
       </c>
       <c r="R210" t="n">
-        <v>6563204</v>
+        <v>6563346</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -24438,13 +24441,13 @@
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126005160</t>
+          <t>https://artportalen.se/Sighting/126003792</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>126061084</v>
+        <v>126005160</v>
       </c>
       <c r="B211" t="n">
         <v>99035</v>
@@ -24473,16 +24476,20 @@
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>687014</v>
+        <v>687034</v>
       </c>
       <c r="R211" t="n">
-        <v>6563215</v>
+        <v>6563204</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -24509,22 +24516,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z211" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -24533,30 +24530,31 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
+      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061084</t>
+          <t>https://artportalen.se/Sighting/126005160</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>126061091</v>
+        <v>126061084</v>
       </c>
       <c r="B212" t="n">
         <v>99035</v>
@@ -24591,10 +24589,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>686871</v>
+        <v>687014</v>
       </c>
       <c r="R212" t="n">
-        <v>6562972</v>
+        <v>6563215</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24626,7 +24624,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -24636,7 +24634,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24662,13 +24660,13 @@
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061091</t>
+          <t>https://artportalen.se/Sighting/126061084</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>126061099</v>
+        <v>126061091</v>
       </c>
       <c r="B213" t="n">
         <v>99035</v>
@@ -24703,10 +24701,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>686857</v>
+        <v>686871</v>
       </c>
       <c r="R213" t="n">
-        <v>6562875</v>
+        <v>6562972</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -24738,7 +24736,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -24748,7 +24746,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24768,19 +24766,19 @@
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061099</t>
+          <t>https://artportalen.se/Sighting/126061091</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>126061102</v>
+        <v>126061099</v>
       </c>
       <c r="B214" t="n">
         <v>99035</v>
@@ -24815,10 +24813,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>686837</v>
+        <v>686857</v>
       </c>
       <c r="R214" t="n">
-        <v>6562829</v>
+        <v>6562875</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24850,7 +24848,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -24860,7 +24858,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24886,13 +24884,13 @@
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061102</t>
+          <t>https://artportalen.se/Sighting/126061099</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>126233785</v>
+        <v>126061102</v>
       </c>
       <c r="B215" t="n">
         <v>99035</v>
@@ -24921,24 +24919,16 @@
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>686839</v>
+        <v>686837</v>
       </c>
       <c r="R215" t="n">
-        <v>6563016</v>
+        <v>6562829</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24965,12 +24955,22 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24979,31 +24979,30 @@
       <c r="AE215" t="b">
         <v>0</v>
       </c>
-      <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="b">
         <v>0</v>
       </c>
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126233785</t>
+          <t>https://artportalen.se/Sighting/126061102</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>126234010</v>
+        <v>126233785</v>
       </c>
       <c r="B216" t="n">
         <v>99035</v>
@@ -25046,10 +25045,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>687160</v>
+        <v>686839</v>
       </c>
       <c r="R216" t="n">
-        <v>6563261</v>
+        <v>6563016</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -25102,19 +25101,19 @@
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234010</t>
+          <t>https://artportalen.se/Sighting/126233785</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>126234159</v>
+        <v>126234010</v>
       </c>
       <c r="B217" t="n">
         <v>99035</v>
@@ -25142,13 +25141,13 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
@@ -25157,13 +25156,13 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>687297</v>
+        <v>687160</v>
       </c>
       <c r="R217" t="n">
-        <v>6563381</v>
+        <v>6563261</v>
       </c>
       <c r="S217" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -25193,11 +25192,6 @@
       <c r="AA217" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>Ett flertal i blomning.</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -25218,19 +25212,19 @@
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Ulf Johansson</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234159</t>
+          <t>https://artportalen.se/Sighting/126234010</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>126234439</v>
+        <v>126234159</v>
       </c>
       <c r="B218" t="n">
         <v>99035</v>
@@ -25260,34 +25254,26 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>686777</v>
+        <v>687297</v>
       </c>
       <c r="R218" t="n">
-        <v>6563073</v>
+        <v>6563381</v>
       </c>
       <c r="S218" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -25317,6 +25303,11 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>Ett flertal i blomning.</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -25332,24 +25323,24 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234439</t>
+          <t>https://artportalen.se/Sighting/126234159</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>126234644</v>
+        <v>126234439</v>
       </c>
       <c r="B219" t="n">
         <v>99035</v>
@@ -25379,7 +25370,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -25387,7 +25378,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
@@ -25396,10 +25391,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>686837</v>
+        <v>686777</v>
       </c>
       <c r="R219" t="n">
-        <v>6562967</v>
+        <v>6563073</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -25458,13 +25453,13 @@
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234644</t>
+          <t>https://artportalen.se/Sighting/126234439</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>126234771</v>
+        <v>126234644</v>
       </c>
       <c r="B220" t="n">
         <v>99035</v>
@@ -25494,7 +25489,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -25507,14 +25502,14 @@
       <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Norrby mosse OSO, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>686976</v>
+        <v>686837</v>
       </c>
       <c r="R220" t="n">
-        <v>6563107</v>
+        <v>6562967</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25573,16 +25568,16 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234771</t>
+          <t>https://artportalen.se/Sighting/126234644</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>133767702</v>
+        <v>126234771</v>
       </c>
       <c r="B221" t="n">
-        <v>99112</v>
+        <v>99035</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25607,21 +25602,29 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse OSO, Srm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>686845</v>
+        <v>686976</v>
       </c>
       <c r="R221" t="n">
-        <v>6563325</v>
+        <v>6563107</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25648,12 +25651,12 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -25669,27 +25672,27 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133767702</t>
+          <t>https://artportalen.se/Sighting/126234771</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>126061092</v>
+        <v>133767702</v>
       </c>
       <c r="B222" t="n">
-        <v>99022</v>
+        <v>99112</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25697,43 +25700,38 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>686880</v>
+        <v>686845</v>
       </c>
       <c r="R222" t="n">
-        <v>6562892</v>
+        <v>6563325</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25760,22 +25758,12 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z222" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB222" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -25784,30 +25772,31 @@
       <c r="AE222" t="b">
         <v>0</v>
       </c>
+      <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="b">
         <v>0</v>
       </c>
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061092</t>
+          <t>https://artportalen.se/Sighting/133767702</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>126061094</v>
+        <v>126061092</v>
       </c>
       <c r="B223" t="n">
         <v>99022</v>
@@ -25851,10 +25840,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>686866</v>
+        <v>686880</v>
       </c>
       <c r="R223" t="n">
-        <v>6562874</v>
+        <v>6562892</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25886,7 +25875,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -25896,7 +25885,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25922,13 +25911,13 @@
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061094</t>
+          <t>https://artportalen.se/Sighting/126061092</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>126061100</v>
+        <v>126061094</v>
       </c>
       <c r="B224" t="n">
         <v>99022</v>
@@ -25958,7 +25947,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -25972,10 +25961,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>686857</v>
+        <v>686866</v>
       </c>
       <c r="R224" t="n">
-        <v>6562875</v>
+        <v>6562874</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26007,7 +25996,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -26017,7 +26006,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -26043,43 +26032,43 @@
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061100</t>
+          <t>https://artportalen.se/Sighting/126061094</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>86686018</v>
+        <v>126061100</v>
       </c>
       <c r="B225" t="n">
-        <v>99118</v>
+        <v>99022</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -26087,23 +26076,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Tyresta S Ungfars kärr, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>686831</v>
+        <v>686857</v>
       </c>
       <c r="R225" t="n">
-        <v>6563296</v>
+        <v>6562875</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26130,17 +26112,22 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2020-07-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2020-07-04</t>
-        </is>
-      </c>
-      <c r="AC225" t="inlineStr">
-        <is>
-          <t>Från Ungfars kärrs södra spets och ca 200 meter österut. Ungefär hälften av skotten utanför parkens gräns. 4 blomstänglar. Området var bökat av vildsvin. Vissa skott var uppgrävda.</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -26149,31 +26136,30 @@
       <c r="AE225" t="b">
         <v>0</v>
       </c>
-      <c r="AF225" t="inlineStr"/>
       <c r="AG225" t="b">
         <v>0</v>
       </c>
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86686018</t>
+          <t>https://artportalen.se/Sighting/126061100</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>96672256</v>
+        <v>86686018</v>
       </c>
       <c r="B226" t="n">
         <v>99118</v>
@@ -26201,24 +26187,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr"/>
       <c r="N226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>NO Norrby mosse, Srm</t>
+          <t>Tyresta S Ungfars kärr, Srm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>686848</v>
+        <v>686831</v>
       </c>
       <c r="R226" t="n">
-        <v>6563295</v>
+        <v>6563296</v>
       </c>
       <c r="S226" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -26242,12 +26240,17 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2020-07-04</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2020-07-04</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>Från Ungfars kärrs södra spets och ca 200 meter österut. Ungefär hälften av skotten utanför parkens gräns. 4 blomstänglar. Området var bökat av vildsvin. Vissa skott var uppgrävda.</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -26263,24 +26266,24 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96672256</t>
+          <t>https://artportalen.se/Sighting/86686018</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>97242656</v>
+        <v>96672256</v>
       </c>
       <c r="B227" t="n">
         <v>99118</v>
@@ -26309,21 +26312,23 @@
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>OSO Ungfars mosse, Srm</t>
+          <t>NO Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>686846</v>
+        <v>686848</v>
       </c>
       <c r="R227" t="n">
-        <v>6563316</v>
+        <v>6563295</v>
       </c>
       <c r="S227" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -26347,22 +26352,12 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -26371,30 +26366,31 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
+      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Thomas Strid, Bodil Ravn, Ulf Johansson, Tiina Laantee</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97242656</t>
+          <t>https://artportalen.se/Sighting/96672256</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>97243108</v>
+        <v>97242656</v>
       </c>
       <c r="B228" t="n">
         <v>99118</v>
@@ -26427,17 +26423,17 @@
       <c r="L228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Tyresta, Srm</t>
+          <t>OSO Ungfars mosse, Srm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>686847</v>
+        <v>686846</v>
       </c>
       <c r="R228" t="n">
-        <v>6563308</v>
+        <v>6563316</v>
       </c>
       <c r="S228" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -26466,7 +26462,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -26476,7 +26472,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -26502,13 +26498,13 @@
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97243108</t>
+          <t>https://artportalen.se/Sighting/97242656</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>97330311</v>
+        <v>97243108</v>
       </c>
       <c r="B229" t="n">
         <v>99118</v>
@@ -26536,29 +26532,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Tyresta NP, SSV Bylsjön (*knärot* /stjälk/), Srm</t>
+          <t>Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q229" t="n">
         <v>686847</v>
       </c>
       <c r="R229" t="n">
-        <v>6563309</v>
+        <v>6563308</v>
       </c>
       <c r="S229" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -26580,24 +26569,24 @@
           <t>Österhaninge</t>
         </is>
       </c>
-      <c r="X229" t="inlineStr">
-        <is>
-          <t>AB-Han-0218</t>
-        </is>
-      </c>
       <c r="Y229" t="inlineStr">
         <is>
           <t>2021-11-20</t>
         </is>
       </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA229" t="inlineStr">
         <is>
           <t>2021-11-20</t>
         </is>
       </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>/Ej räknad/</t>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -26612,28 +26601,24 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Tiina Laantee, Ulf Johansson, Bodil Ravn, Thomas Strid</t>
-        </is>
-      </c>
-      <c r="AY229" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Thomas Strid, Bodil Ravn, Ulf Johansson, Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97330311</t>
+          <t>https://artportalen.se/Sighting/97243108</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>98104097</v>
+        <v>97330311</v>
       </c>
       <c r="B230" t="n">
         <v>99118</v>
@@ -26663,27 +26648,24 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr"/>
-      <c r="N230" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Tyresta NP, SSV Bylsjön (*knärot* /stjälk/), Srm</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>686934</v>
+        <v>686847</v>
       </c>
       <c r="R230" t="n">
-        <v>6563325</v>
+        <v>6563309</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -26708,19 +26690,24 @@
           <t>Österhaninge</t>
         </is>
       </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>AB-Han-0218</t>
+        </is>
+      </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AC230" t="inlineStr">
         <is>
-          <t>Intill djurstig och granlåga</t>
+          <t>/Ej räknad/</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -26729,31 +26716,34 @@
       <c r="AE230" t="b">
         <v>0</v>
       </c>
-      <c r="AF230" t="inlineStr"/>
       <c r="AG230" t="b">
         <v>0</v>
       </c>
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
-        </is>
-      </c>
-      <c r="AY230" t="inlineStr"/>
+          <t>Tiina Laantee, Ulf Johansson, Bodil Ravn, Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98104097</t>
+          <t>https://artportalen.se/Sighting/97330311</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>104249959</v>
+        <v>98104097</v>
       </c>
       <c r="B231" t="n">
         <v>99118</v>
@@ -26781,24 +26771,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr"/>
       <c r="N231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>687011</v>
+        <v>686934</v>
       </c>
       <c r="R231" t="n">
-        <v>6562869</v>
+        <v>6563325</v>
       </c>
       <c r="S231" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -26822,17 +26820,17 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>Samma lokal som noterades 17/11-21. Ca 25 ex. Koordinaterna har varierat något vid besöken.</t>
+          <t>Intill djurstig och granlåga</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26848,24 +26846,24 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104249959</t>
+          <t>https://artportalen.se/Sighting/98104097</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>109890506</v>
+        <v>104249959</v>
       </c>
       <c r="B232" t="n">
         <v>99118</v>
@@ -26900,17 +26898,17 @@
       <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Ö Norrby Mosse, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>686831</v>
+        <v>687011</v>
       </c>
       <c r="R232" t="n">
-        <v>6563216</v>
+        <v>6562869</v>
       </c>
       <c r="S232" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -26934,12 +26932,17 @@
       </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Samma lokal som noterades 17/11-21. Ca 25 ex. Koordinaterna har varierat något vid besöken.</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26966,13 +26969,13 @@
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109890506</t>
+          <t>https://artportalen.se/Sighting/104249959</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>119475594</v>
+        <v>109890506</v>
       </c>
       <c r="B233" t="n">
         <v>99118</v>
@@ -27000,29 +27003,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr"/>
       <c r="N233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>Ö Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>686995</v>
+        <v>686831</v>
       </c>
       <c r="R233" t="n">
-        <v>6563315</v>
+        <v>6563216</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -27049,12 +27044,12 @@
       </c>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -27081,13 +27076,13 @@
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119475594</t>
+          <t>https://artportalen.se/Sighting/109890506</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>121859637</v>
+        <v>119475594</v>
       </c>
       <c r="B234" t="n">
         <v>99118</v>
@@ -27115,17 +27110,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr"/>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>686863</v>
+        <v>686995</v>
       </c>
       <c r="R234" t="n">
-        <v>6563252</v>
+        <v>6563315</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -27152,22 +27159,12 @@
       </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z234" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB234" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -27176,30 +27173,31 @@
       <c r="AE234" t="b">
         <v>0</v>
       </c>
+      <c r="AF234" t="inlineStr"/>
       <c r="AG234" t="b">
         <v>0</v>
       </c>
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859637</t>
+          <t>https://artportalen.se/Sighting/119475594</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>121859638</v>
+        <v>121859637</v>
       </c>
       <c r="B235" t="n">
         <v>99118</v>
@@ -27234,10 +27232,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>686826</v>
+        <v>686863</v>
       </c>
       <c r="R235" t="n">
-        <v>6563286</v>
+        <v>6563252</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27269,7 +27267,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -27279,7 +27277,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -27305,13 +27303,13 @@
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859638</t>
+          <t>https://artportalen.se/Sighting/121859637</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>121859639</v>
+        <v>121859638</v>
       </c>
       <c r="B236" t="n">
         <v>99118</v>
@@ -27346,10 +27344,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>686827</v>
+        <v>686826</v>
       </c>
       <c r="R236" t="n">
-        <v>6563296</v>
+        <v>6563286</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27381,7 +27379,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -27391,7 +27389,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -27417,13 +27415,13 @@
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859639</t>
+          <t>https://artportalen.se/Sighting/121859638</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>121859640</v>
+        <v>121859639</v>
       </c>
       <c r="B237" t="n">
         <v>99118</v>
@@ -27458,10 +27456,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>686837</v>
+        <v>686827</v>
       </c>
       <c r="R237" t="n">
-        <v>6563297</v>
+        <v>6563296</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27493,7 +27491,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -27503,7 +27501,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -27529,13 +27527,13 @@
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859640</t>
+          <t>https://artportalen.se/Sighting/121859639</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>121859642</v>
+        <v>121859640</v>
       </c>
       <c r="B238" t="n">
         <v>99118</v>
@@ -27564,24 +27562,16 @@
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>686834</v>
+        <v>686837</v>
       </c>
       <c r="R238" t="n">
-        <v>6563305</v>
+        <v>6563297</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -27613,7 +27603,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -27623,7 +27613,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -27632,7 +27622,6 @@
       <c r="AE238" t="b">
         <v>0</v>
       </c>
-      <c r="AF238" t="inlineStr"/>
       <c r="AG238" t="b">
         <v>0</v>
       </c>
@@ -27650,13 +27639,13 @@
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859642</t>
+          <t>https://artportalen.se/Sighting/121859640</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>121859643</v>
+        <v>121859642</v>
       </c>
       <c r="B239" t="n">
         <v>99118</v>
@@ -27685,6 +27674,14 @@
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
@@ -27694,7 +27691,7 @@
         <v>686834</v>
       </c>
       <c r="R239" t="n">
-        <v>6563309</v>
+        <v>6563305</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -27726,7 +27723,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -27736,7 +27733,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -27745,6 +27742,7 @@
       <c r="AE239" t="b">
         <v>0</v>
       </c>
+      <c r="AF239" t="inlineStr"/>
       <c r="AG239" t="b">
         <v>0</v>
       </c>
@@ -27762,13 +27760,13 @@
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859643</t>
+          <t>https://artportalen.se/Sighting/121859642</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>121859644</v>
+        <v>121859643</v>
       </c>
       <c r="B240" t="n">
         <v>99118</v>
@@ -27803,10 +27801,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>686844</v>
+        <v>686834</v>
       </c>
       <c r="R240" t="n">
-        <v>6563303</v>
+        <v>6563309</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27838,7 +27836,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -27848,7 +27846,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -27874,13 +27872,13 @@
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859644</t>
+          <t>https://artportalen.se/Sighting/121859643</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>121859646</v>
+        <v>121859644</v>
       </c>
       <c r="B241" t="n">
         <v>99118</v>
@@ -27915,7 +27913,7 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>686841</v>
+        <v>686844</v>
       </c>
       <c r="R241" t="n">
         <v>6563303</v>
@@ -27950,7 +27948,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -27960,7 +27958,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -27986,13 +27984,13 @@
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859646</t>
+          <t>https://artportalen.se/Sighting/121859644</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>121859647</v>
+        <v>121859646</v>
       </c>
       <c r="B242" t="n">
         <v>99118</v>
@@ -28027,10 +28025,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>686854</v>
+        <v>686841</v>
       </c>
       <c r="R242" t="n">
-        <v>6563286</v>
+        <v>6563303</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -28062,7 +28060,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -28072,7 +28070,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -28098,13 +28096,13 @@
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859647</t>
+          <t>https://artportalen.se/Sighting/121859646</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>121859649</v>
+        <v>121859647</v>
       </c>
       <c r="B243" t="n">
         <v>99118</v>
@@ -28139,10 +28137,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>686851</v>
+        <v>686854</v>
       </c>
       <c r="R243" t="n">
-        <v>6563299</v>
+        <v>6563286</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -28174,7 +28172,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -28184,7 +28182,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -28210,13 +28208,13 @@
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859649</t>
+          <t>https://artportalen.se/Sighting/121859647</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>121859650</v>
+        <v>121859649</v>
       </c>
       <c r="B244" t="n">
         <v>99118</v>
@@ -28251,10 +28249,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>686895</v>
+        <v>686851</v>
       </c>
       <c r="R244" t="n">
-        <v>6563306</v>
+        <v>6563299</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -28286,7 +28284,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -28296,7 +28294,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -28322,13 +28320,13 @@
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859650</t>
+          <t>https://artportalen.se/Sighting/121859649</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>122220583</v>
+        <v>121859650</v>
       </c>
       <c r="B245" t="n">
         <v>99118</v>
@@ -28356,29 +28354,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J245" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
-      <c r="N245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>686996</v>
+        <v>686895</v>
       </c>
       <c r="R245" t="n">
-        <v>6562864</v>
+        <v>6563306</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -28405,17 +28391,22 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AC245" t="inlineStr">
-        <is>
-          <t>Samma lokal som rapporterats -21 och -22 men en ny klon. Den förra har möjligen haft lite problem med grisbök.</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -28424,31 +28415,30 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
-      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122220583</t>
+          <t>https://artportalen.se/Sighting/121859650</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>122781008</v>
+        <v>122220583</v>
       </c>
       <c r="B246" t="n">
         <v>99118</v>
@@ -28476,21 +28466,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr"/>
       <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Knärot, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>686833</v>
+        <v>686996</v>
       </c>
       <c r="R246" t="n">
-        <v>6563215</v>
+        <v>6562864</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28517,17 +28515,17 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AC246" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Samma lokal som rapporterats -21 och -22 men en ny klon. Den förra har möjligen haft lite problem med grisbök.</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -28543,24 +28541,24 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122781008</t>
+          <t>https://artportalen.se/Sighting/122220583</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>126418709</v>
+        <v>122781008</v>
       </c>
       <c r="B247" t="n">
         <v>99118</v>
@@ -28588,29 +28586,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J247" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I247" t="inlineStr"/>
+      <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr"/>
       <c r="N247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Knärot, Srm</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>686771</v>
+        <v>686833</v>
       </c>
       <c r="R247" t="n">
-        <v>6563297</v>
+        <v>6563215</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28637,17 +28627,17 @@
       </c>
       <c r="Y247" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28663,24 +28653,24 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418709</t>
+          <t>https://artportalen.se/Sighting/122781008</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>126418756</v>
+        <v>126418709</v>
       </c>
       <c r="B248" t="n">
         <v>99118</v>
@@ -28710,7 +28700,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -28727,10 +28717,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>686781</v>
+        <v>686771</v>
       </c>
       <c r="R248" t="n">
-        <v>6563292</v>
+        <v>6563297</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28767,7 +28757,7 @@
       </c>
       <c r="AC248" t="inlineStr">
         <is>
-          <t>En av dem i knopp.</t>
+          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28794,13 +28784,13 @@
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418756</t>
+          <t>https://artportalen.se/Sighting/126418709</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>127932426</v>
+        <v>126418756</v>
       </c>
       <c r="B249" t="n">
         <v>99118</v>
@@ -28830,7 +28820,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -28847,10 +28837,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>686998</v>
+        <v>686781</v>
       </c>
       <c r="R249" t="n">
-        <v>6563316</v>
+        <v>6563292</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28877,17 +28867,17 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>Återfynd, rapporterad -24 med 3 ex. Nu 5 ex.</t>
+          <t>En av dem i knopp.</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28914,13 +28904,13 @@
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127932426</t>
+          <t>https://artportalen.se/Sighting/126418756</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128341941</v>
+        <v>127932426</v>
       </c>
       <c r="B250" t="n">
         <v>99118</v>
@@ -28950,7 +28940,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -28967,10 +28957,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>687244</v>
+        <v>686998</v>
       </c>
       <c r="R250" t="n">
-        <v>6563404</v>
+        <v>6563316</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28997,12 +28987,17 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>Återfynd, rapporterad -24 med 3 ex. Nu 5 ex.</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -29029,13 +29024,13 @@
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128341941</t>
+          <t>https://artportalen.se/Sighting/127932426</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>129564285</v>
+        <v>128341941</v>
       </c>
       <c r="B251" t="n">
         <v>99118</v>
@@ -29063,8 +29058,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr"/>
-      <c r="J251" t="inlineStr"/>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr"/>
       <c r="N251" t="inlineStr"/>
@@ -29074,10 +29077,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>686625</v>
+        <v>687244</v>
       </c>
       <c r="R251" t="n">
-        <v>6563000</v>
+        <v>6563404</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -29104,12 +29107,12 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -29136,16 +29139,16 @@
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129564285</t>
+          <t>https://artportalen.se/Sighting/128341941</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>133767721</v>
+        <v>129564285</v>
       </c>
       <c r="B252" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29181,10 +29184,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>686845</v>
+        <v>686625</v>
       </c>
       <c r="R252" t="n">
-        <v>6563325</v>
+        <v>6563000</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -29211,12 +29214,12 @@
       </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -29243,38 +29246,38 @@
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133767721</t>
+          <t>https://artportalen.se/Sighting/129564285</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>96643458</v>
+        <v>133767721</v>
       </c>
       <c r="B253" t="n">
-        <v>106244</v>
+        <v>99195</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -29284,14 +29287,14 @@
       <c r="N253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Vargklåva mosse S om, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>687154</v>
+        <v>686845</v>
       </c>
       <c r="R253" t="n">
-        <v>6563329</v>
+        <v>6563325</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -29318,12 +29321,12 @@
       </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -29339,24 +29342,24 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96643458</t>
+          <t>https://artportalen.se/Sighting/133767721</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>96858761</v>
+        <v>96643458</v>
       </c>
       <c r="B254" t="n">
         <v>106244</v>
@@ -29391,17 +29394,17 @@
       <c r="N254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Vargklåva mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>687064</v>
+        <v>687154</v>
       </c>
       <c r="R254" t="n">
-        <v>6563258</v>
+        <v>6563329</v>
       </c>
       <c r="S254" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -29425,17 +29428,12 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>Två bestånd</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -29462,13 +29460,13 @@
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96858761</t>
+          <t>https://artportalen.se/Sighting/96643458</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>97204577</v>
+        <v>96858761</v>
       </c>
       <c r="B255" t="n">
         <v>106244</v>
@@ -29503,17 +29501,17 @@
       <c r="N255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>SO Norrby mosse, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>687019</v>
+        <v>687064</v>
       </c>
       <c r="R255" t="n">
-        <v>6562889</v>
+        <v>6563258</v>
       </c>
       <c r="S255" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -29537,12 +29535,17 @@
       </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>Två bestånd</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29558,24 +29561,24 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97204577</t>
+          <t>https://artportalen.se/Sighting/96858761</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>100252927</v>
+        <v>97204577</v>
       </c>
       <c r="B256" t="n">
         <v>106244</v>
@@ -29610,17 +29613,17 @@
       <c r="N256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>SO Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>687152</v>
+        <v>687019</v>
       </c>
       <c r="R256" t="n">
-        <v>6563326</v>
+        <v>6562889</v>
       </c>
       <c r="S256" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -29644,12 +29647,12 @@
       </c>
       <c r="Y256" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -29676,13 +29679,13 @@
       <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100252927</t>
+          <t>https://artportalen.se/Sighting/97204577</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>116743172</v>
+        <v>100252927</v>
       </c>
       <c r="B257" t="n">
         <v>106244</v>
@@ -29711,16 +29714,20 @@
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Ungfars kärr, Ungfars kärr, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>687088</v>
+        <v>687152</v>
       </c>
       <c r="R257" t="n">
-        <v>6563243</v>
+        <v>6563326</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29747,12 +29754,12 @@
       </c>
       <c r="Y257" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -29761,30 +29768,31 @@
       <c r="AE257" t="b">
         <v>0</v>
       </c>
+      <c r="AF257" t="inlineStr"/>
       <c r="AG257" t="b">
         <v>0</v>
       </c>
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116743172</t>
+          <t>https://artportalen.se/Sighting/100252927</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>125965889</v>
+        <v>116743172</v>
       </c>
       <c r="B258" t="n">
         <v>106244</v>
@@ -29819,10 +29827,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>687076</v>
+        <v>687088</v>
       </c>
       <c r="R258" t="n">
-        <v>6563220</v>
+        <v>6563243</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29849,12 +29857,12 @@
       </c>
       <c r="Y258" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -29880,13 +29888,13 @@
       <c r="AY258" t="inlineStr"/>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125965889</t>
+          <t>https://artportalen.se/Sighting/116743172</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>126003574</v>
+        <v>125965889</v>
       </c>
       <c r="B259" t="n">
         <v>106244</v>
@@ -29915,20 +29923,16 @@
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
-      <c r="J259" t="inlineStr"/>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr"/>
-      <c r="N259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ungfars kärr, Ungfars kärr, Srm</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>686803</v>
+        <v>687076</v>
       </c>
       <c r="R259" t="n">
-        <v>6563098</v>
+        <v>6563220</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -29955,12 +29959,12 @@
       </c>
       <c r="Y259" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -29969,31 +29973,30 @@
       <c r="AE259" t="b">
         <v>0</v>
       </c>
-      <c r="AF259" t="inlineStr"/>
       <c r="AG259" t="b">
         <v>0</v>
       </c>
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126003574</t>
+          <t>https://artportalen.se/Sighting/125965889</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>126061078</v>
+        <v>126003574</v>
       </c>
       <c r="B260" t="n">
         <v>106244</v>
@@ -30022,16 +30025,20 @@
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>687085</v>
+        <v>686803</v>
       </c>
       <c r="R260" t="n">
-        <v>6563229</v>
+        <v>6563098</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -30058,22 +30065,12 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB260" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -30082,30 +30079,31 @@
       <c r="AE260" t="b">
         <v>0</v>
       </c>
+      <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="b">
         <v>0</v>
       </c>
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061078</t>
+          <t>https://artportalen.se/Sighting/126003574</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>126061079</v>
+        <v>126061078</v>
       </c>
       <c r="B261" t="n">
         <v>106244</v>
@@ -30140,10 +30138,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>687082</v>
+        <v>687085</v>
       </c>
       <c r="R261" t="n">
-        <v>6563241</v>
+        <v>6563229</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -30175,7 +30173,7 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
@@ -30185,7 +30183,7 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -30211,13 +30209,13 @@
       <c r="AY261" t="inlineStr"/>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061079</t>
+          <t>https://artportalen.se/Sighting/126061078</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>126234373</v>
+        <v>126061079</v>
       </c>
       <c r="B262" t="n">
         <v>106244</v>
@@ -30245,29 +30243,17 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
-      <c r="N262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>686756</v>
+        <v>687082</v>
       </c>
       <c r="R262" t="n">
-        <v>6563092</v>
+        <v>6563241</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -30294,12 +30280,22 @@
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -30308,31 +30304,30 @@
       <c r="AE262" t="b">
         <v>0</v>
       </c>
-      <c r="AF262" t="inlineStr"/>
       <c r="AG262" t="b">
         <v>0</v>
       </c>
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234373</t>
+          <t>https://artportalen.se/Sighting/126061079</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>126234937</v>
+        <v>126234373</v>
       </c>
       <c r="B263" t="n">
         <v>106244</v>
@@ -30370,23 +30365,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr"/>
       <c r="N263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>687103</v>
+        <v>686756</v>
       </c>
       <c r="R263" t="n">
-        <v>6563191</v>
+        <v>6563092</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -30445,16 +30436,16 @@
       <c r="AY263" t="inlineStr"/>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234937</t>
+          <t>https://artportalen.se/Sighting/126234373</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>136329900</v>
+        <v>126234937</v>
       </c>
       <c r="B264" t="n">
-        <v>106500</v>
+        <v>106244</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30479,21 +30470,33 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr"/>
-      <c r="J264" t="inlineStr"/>
-      <c r="K264" t="inlineStr"/>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr"/>
       <c r="N264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>686462</v>
+        <v>687103</v>
       </c>
       <c r="R264" t="n">
-        <v>6563046</v>
+        <v>6563191</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -30520,12 +30523,12 @@
       </c>
       <c r="Y264" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -30541,27 +30544,27 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136329900</t>
+          <t>https://artportalen.se/Sighting/126234937</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>136422457</v>
+        <v>136329900</v>
       </c>
       <c r="B265" t="n">
-        <v>106502</v>
+        <v>106500</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -30597,10 +30600,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>687270</v>
+        <v>686462</v>
       </c>
       <c r="R265" t="n">
-        <v>6563384</v>
+        <v>6563046</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -30627,12 +30630,12 @@
       </c>
       <c r="Y265" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -30659,16 +30662,16 @@
       <c r="AY265" t="inlineStr"/>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136422457</t>
+          <t>https://artportalen.se/Sighting/136329900</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>96643468</v>
+        <v>136422457</v>
       </c>
       <c r="B266" t="n">
-        <v>97989</v>
+        <v>106503</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -30676,46 +30679,38 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr"/>
       <c r="N266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Vargklåva mosse S om, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>687268</v>
+        <v>687270</v>
       </c>
       <c r="R266" t="n">
-        <v>6563319</v>
+        <v>6563384</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -30742,17 +30737,12 @@
       </c>
       <c r="Y266" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
-        </is>
-      </c>
-      <c r="AC266" t="inlineStr">
-        <is>
-          <t>Strax nedom klippbrant</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -30768,24 +30758,24 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96643468</t>
+          <t>https://artportalen.se/Sighting/136422457</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>116746465</v>
+        <v>96643468</v>
       </c>
       <c r="B267" t="n">
         <v>97989</v>
@@ -30813,17 +30803,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I267" t="inlineStr"/>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+      <c r="N267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Norrby mosse, Norrby mosse, Srm</t>
+          <t>Vargklåva mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>686888</v>
+        <v>687268</v>
       </c>
       <c r="R267" t="n">
-        <v>6563206</v>
+        <v>6563319</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -30850,12 +30852,17 @@
       </c>
       <c r="Y267" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>Strax nedom klippbrant</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -30864,33 +30871,34 @@
       <c r="AE267" t="b">
         <v>0</v>
       </c>
+      <c r="AF267" t="inlineStr"/>
       <c r="AG267" t="b">
         <v>0</v>
       </c>
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116746465</t>
+          <t>https://artportalen.se/Sighting/96643468</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>135827249</v>
+        <v>116746465</v>
       </c>
       <c r="B268" t="n">
-        <v>98209</v>
+        <v>97989</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -30916,20 +30924,16 @@
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
-      <c r="J268" t="inlineStr"/>
-      <c r="K268" t="inlineStr"/>
-      <c r="L268" t="inlineStr"/>
-      <c r="N268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse, Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>687270</v>
+        <v>686888</v>
       </c>
       <c r="R268" t="n">
-        <v>6563321</v>
+        <v>6563206</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -30956,17 +30960,12 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>Återfynd, tidigare rapporterad 2021.</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -30975,34 +30974,33 @@
       <c r="AE268" t="b">
         <v>0</v>
       </c>
-      <c r="AF268" t="inlineStr"/>
       <c r="AG268" t="b">
         <v>0</v>
       </c>
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135827249</t>
+          <t>https://artportalen.se/Sighting/116746465</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>121742517</v>
+        <v>135827249</v>
       </c>
       <c r="B269" t="n">
-        <v>97983</v>
+        <v>98209</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31010,16 +31008,16 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -31028,16 +31026,20 @@
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
+      <c r="J269" t="inlineStr"/>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="N269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Norrby mosse, Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>686859</v>
+        <v>687270</v>
       </c>
       <c r="R269" t="n">
-        <v>6562875</v>
+        <v>6563321</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -31064,12 +31066,17 @@
       </c>
       <c r="Y269" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>Återfynd, tidigare rapporterad 2021.</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -31078,30 +31085,31 @@
       <c r="AE269" t="b">
         <v>0</v>
       </c>
+      <c r="AF269" t="inlineStr"/>
       <c r="AG269" t="b">
         <v>0</v>
       </c>
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121742517</t>
+          <t>https://artportalen.se/Sighting/135827249</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>122928987</v>
+        <v>121742517</v>
       </c>
       <c r="B270" t="n">
         <v>97983</v>
@@ -31130,20 +31138,16 @@
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
-      <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr"/>
-      <c r="L270" t="inlineStr"/>
-      <c r="N270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Norrby mosse, Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>686389</v>
+        <v>686859</v>
       </c>
       <c r="R270" t="n">
-        <v>6562967</v>
+        <v>6562875</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -31170,22 +31174,12 @@
       </c>
       <c r="Y270" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z270" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB270" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -31200,24 +31194,24 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122928987</t>
+          <t>https://artportalen.se/Sighting/121742517</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>122930294</v>
+        <v>122928987</v>
       </c>
       <c r="B271" t="n">
         <v>97983</v>
@@ -31256,13 +31250,13 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>686824</v>
+        <v>686389</v>
       </c>
       <c r="R271" t="n">
-        <v>6562778</v>
+        <v>6562967</v>
       </c>
       <c r="S271" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -31291,7 +31285,7 @@
       </c>
       <c r="Z271" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
@@ -31301,7 +31295,7 @@
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -31327,13 +31321,13 @@
       <c r="AY271" t="inlineStr"/>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122930294</t>
+          <t>https://artportalen.se/Sighting/122928987</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>125963374</v>
+        <v>122930294</v>
       </c>
       <c r="B272" t="n">
         <v>97983</v>
@@ -31362,19 +31356,23 @@
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Norrby mosse, Norrby mosse, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>686873</v>
+        <v>686824</v>
       </c>
       <c r="R272" t="n">
-        <v>6562867</v>
+        <v>6562778</v>
       </c>
       <c r="S272" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T272" t="inlineStr">
         <is>
@@ -31398,12 +31396,22 @@
       </c>
       <c r="Y272" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -31418,24 +31426,24 @@
       <c r="AT272" t="inlineStr"/>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125963374</t>
+          <t>https://artportalen.se/Sighting/122930294</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>125976418</v>
+        <v>125963374</v>
       </c>
       <c r="B273" t="n">
         <v>97983</v>
@@ -31464,23 +31472,19 @@
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Norrby mosse Ö om, Srm</t>
+          <t>Norrby mosse, Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>686836</v>
+        <v>686873</v>
       </c>
       <c r="R273" t="n">
-        <v>6563105</v>
+        <v>6562867</v>
       </c>
       <c r="S273" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -31512,42 +31516,36 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i skogskärr</t>
-        </is>
-      </c>
       <c r="AD273" t="b">
         <v>0</v>
       </c>
       <c r="AE273" t="b">
         <v>0</v>
       </c>
-      <c r="AF273" t="inlineStr"/>
       <c r="AG273" t="b">
         <v>0</v>
       </c>
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125976418</t>
+          <t>https://artportalen.se/Sighting/125963374</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>126061082</v>
+        <v>125976418</v>
       </c>
       <c r="B274" t="n">
         <v>97983</v>
@@ -31576,19 +31574,23 @@
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="N274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse Ö om, Srm</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>687079</v>
+        <v>686836</v>
       </c>
       <c r="R274" t="n">
-        <v>6563240</v>
+        <v>6563105</v>
       </c>
       <c r="S274" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -31615,19 +31617,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z274" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA274" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB274" t="inlineStr">
-        <is>
-          <t>15:22</t>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i skogskärr</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -31636,30 +31633,31 @@
       <c r="AE274" t="b">
         <v>0</v>
       </c>
+      <c r="AF274" t="inlineStr"/>
       <c r="AG274" t="b">
         <v>0</v>
       </c>
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061082</t>
+          <t>https://artportalen.se/Sighting/125976418</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>126061090</v>
+        <v>126061082</v>
       </c>
       <c r="B275" t="n">
         <v>97983</v>
@@ -31694,10 +31692,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>686871</v>
+        <v>687079</v>
       </c>
       <c r="R275" t="n">
-        <v>6562972</v>
+        <v>6563240</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -31729,7 +31727,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -31739,7 +31737,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -31765,13 +31763,13 @@
       <c r="AY275" t="inlineStr"/>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061090</t>
+          <t>https://artportalen.se/Sighting/126061082</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>126061103</v>
+        <v>126061090</v>
       </c>
       <c r="B276" t="n">
         <v>97983</v>
@@ -31806,10 +31804,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>686811</v>
+        <v>686871</v>
       </c>
       <c r="R276" t="n">
-        <v>6562803</v>
+        <v>6562972</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -31841,7 +31839,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -31851,7 +31849,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -31871,19 +31869,19 @@
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061103</t>
+          <t>https://artportalen.se/Sighting/126061090</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>126061111</v>
+        <v>126061103</v>
       </c>
       <c r="B277" t="n">
         <v>97983</v>
@@ -31918,10 +31916,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>687030</v>
+        <v>686811</v>
       </c>
       <c r="R277" t="n">
-        <v>6562755</v>
+        <v>6562803</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -31953,7 +31951,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -31963,7 +31961,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -31989,16 +31987,16 @@
       <c r="AY277" t="inlineStr"/>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061111</t>
+          <t>https://artportalen.se/Sighting/126061103</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>136347172</v>
+        <v>126061111</v>
       </c>
       <c r="B278" t="n">
-        <v>98223</v>
+        <v>97983</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -32024,20 +32022,16 @@
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="N278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>686861</v>
+        <v>687030</v>
       </c>
       <c r="R278" t="n">
-        <v>6563127</v>
+        <v>6562755</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -32064,12 +32058,22 @@
       </c>
       <c r="Y278" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB278" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -32078,31 +32082,30 @@
       <c r="AE278" t="b">
         <v>0</v>
       </c>
-      <c r="AF278" t="inlineStr"/>
       <c r="AG278" t="b">
         <v>0</v>
       </c>
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136347172</t>
+          <t>https://artportalen.se/Sighting/126061111</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>136394245</v>
+        <v>136347172</v>
       </c>
       <c r="B279" t="n">
         <v>98223</v>
@@ -32131,19 +32134,23 @@
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>687263</v>
+        <v>686861</v>
       </c>
       <c r="R279" t="n">
-        <v>6563324</v>
+        <v>6563127</v>
       </c>
       <c r="S279" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -32167,22 +32174,12 @@
       </c>
       <c r="Y279" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z279" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB279" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -32191,33 +32188,34 @@
       <c r="AE279" t="b">
         <v>0</v>
       </c>
+      <c r="AF279" t="inlineStr"/>
       <c r="AG279" t="b">
         <v>0</v>
       </c>
       <c r="AT279" t="inlineStr"/>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136394245</t>
+          <t>https://artportalen.se/Sighting/136347172</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>122929342</v>
+        <v>136394245</v>
       </c>
       <c r="B280" t="n">
-        <v>97986</v>
+        <v>98223</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -32225,16 +32223,16 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -32243,23 +32241,19 @@
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="N280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>686569</v>
+        <v>687263</v>
       </c>
       <c r="R280" t="n">
-        <v>6562949</v>
+        <v>6563324</v>
       </c>
       <c r="S280" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -32283,22 +32277,22 @@
       </c>
       <c r="Y280" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -32313,24 +32307,24 @@
       <c r="AT280" t="inlineStr"/>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929342</t>
+          <t>https://artportalen.se/Sighting/136394245</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>126061110</v>
+        <v>122929342</v>
       </c>
       <c r="B281" t="n">
         <v>97986</v>
@@ -32359,19 +32353,23 @@
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="N281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>687029</v>
+        <v>686569</v>
       </c>
       <c r="R281" t="n">
-        <v>6562759</v>
+        <v>6562949</v>
       </c>
       <c r="S281" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -32395,22 +32393,22 @@
       </c>
       <c r="Y281" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -32425,27 +32423,27 @@
       <c r="AT281" t="inlineStr"/>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
       <c r="AZ281" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061110</t>
+          <t>https://artportalen.se/Sighting/122929342</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>101523203</v>
+        <v>126061110</v>
       </c>
       <c r="B282" t="n">
-        <v>99140</v>
+        <v>97986</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -32453,38 +32451,34 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
-      <c r="J282" t="inlineStr"/>
-      <c r="K282" t="inlineStr"/>
-      <c r="L282" t="inlineStr"/>
-      <c r="N282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
-          <t>NO Norrby Mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>687050</v>
+        <v>687029</v>
       </c>
       <c r="R282" t="n">
-        <v>6563327</v>
+        <v>6562759</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -32511,12 +32505,22 @@
       </c>
       <c r="Y282" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB282" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -32525,31 +32529,30 @@
       <c r="AE282" t="b">
         <v>0</v>
       </c>
-      <c r="AF282" t="inlineStr"/>
       <c r="AG282" t="b">
         <v>0</v>
       </c>
       <c r="AT282" t="inlineStr"/>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
       <c r="AZ282" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101523203</t>
+          <t>https://artportalen.se/Sighting/126061110</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>117554655</v>
+        <v>101523203</v>
       </c>
       <c r="B283" t="n">
         <v>99140</v>
@@ -32579,23 +32582,19 @@
       </c>
       <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K283" t="inlineStr"/>
       <c r="L283" t="inlineStr"/>
       <c r="N283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>NO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>687062</v>
+        <v>687050</v>
       </c>
       <c r="R283" t="n">
-        <v>6563349</v>
+        <v>6563327</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -32622,12 +32621,12 @@
       </c>
       <c r="Y283" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AD283" t="b">
@@ -32654,13 +32653,13 @@
       <c r="AY283" t="inlineStr"/>
       <c r="AZ283" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117554655</t>
+          <t>https://artportalen.se/Sighting/101523203</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>126234400</v>
+        <v>117554655</v>
       </c>
       <c r="B284" t="n">
         <v>99140</v>
@@ -32688,16 +32687,8 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J284" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I284" t="inlineStr"/>
+      <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -32707,14 +32698,14 @@
       <c r="N284" t="inlineStr"/>
       <c r="P284" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>686788</v>
+        <v>687062</v>
       </c>
       <c r="R284" t="n">
-        <v>6563073</v>
+        <v>6563349</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -32741,12 +32732,12 @@
       </c>
       <c r="Y284" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD284" t="b">
@@ -32762,27 +32753,27 @@
       <c r="AT284" t="inlineStr"/>
       <c r="AW284" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
       <c r="AZ284" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234400</t>
+          <t>https://artportalen.se/Sighting/117554655</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>134487623</v>
+        <v>126234400</v>
       </c>
       <c r="B285" t="n">
-        <v>99217</v>
+        <v>99140</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32807,8 +32798,16 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I285" t="inlineStr"/>
-      <c r="J285" t="inlineStr"/>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K285" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -32818,17 +32817,17 @@
       <c r="N285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>687067</v>
+        <v>686788</v>
       </c>
       <c r="R285" t="n">
-        <v>6563342</v>
+        <v>6563073</v>
       </c>
       <c r="S285" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T285" t="inlineStr">
         <is>
@@ -32852,17 +32851,12 @@
       </c>
       <c r="Y285" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC285" t="inlineStr">
-        <is>
-          <t>Ett tiotal i blom samt flera plantor med endast blad.  Återfynd.</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD285" t="b">
@@ -32878,24 +32872,24 @@
       <c r="AT285" t="inlineStr"/>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
       <c r="AZ285" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134487623</t>
+          <t>https://artportalen.se/Sighting/126234400</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>134487656</v>
+        <v>134487623</v>
       </c>
       <c r="B286" t="n">
         <v>99217</v>
@@ -32938,13 +32932,13 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>686835</v>
+        <v>687067</v>
       </c>
       <c r="R286" t="n">
-        <v>6563212</v>
+        <v>6563342</v>
       </c>
       <c r="S286" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T286" t="inlineStr">
         <is>
@@ -32978,7 +32972,7 @@
       </c>
       <c r="AC286" t="inlineStr">
         <is>
-          <t>2 i blom samt några plantor med endast blad.</t>
+          <t>Ett tiotal i blom samt flera plantor med endast blad.  Återfynd.</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -33005,13 +32999,13 @@
       <c r="AY286" t="inlineStr"/>
       <c r="AZ286" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134487656</t>
+          <t>https://artportalen.se/Sighting/134487623</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>134488457</v>
+        <v>134487656</v>
       </c>
       <c r="B287" t="n">
         <v>99217</v>
@@ -33054,10 +33048,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>687294</v>
+        <v>686835</v>
       </c>
       <c r="R287" t="n">
-        <v>6563391</v>
+        <v>6563212</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -33094,7 +33088,7 @@
       </c>
       <c r="AC287" t="inlineStr">
         <is>
-          <t>2 i blom samt fler med endast blad.</t>
+          <t>2 i blom samt några plantor med endast blad.</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -33121,43 +33115,48 @@
       <c r="AY287" t="inlineStr"/>
       <c r="AZ287" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134488457</t>
+          <t>https://artportalen.se/Sighting/134487656</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>129564006</v>
+        <v>134488457</v>
       </c>
       <c r="B288" t="n">
-        <v>79350</v>
+        <v>99217</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>260591</v>
+        <v>221952</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
       <c r="J288" t="inlineStr"/>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr"/>
       <c r="N288" t="inlineStr"/>
       <c r="P288" t="inlineStr">
         <is>
@@ -33165,10 +33164,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>686681</v>
+        <v>687294</v>
       </c>
       <c r="R288" t="n">
-        <v>6563025</v>
+        <v>6563391</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -33195,19 +33194,24 @@
       </c>
       <c r="Y288" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>2 i blom samt fler med endast blad.</t>
         </is>
       </c>
       <c r="AD288" t="b">
         <v>0</v>
       </c>
       <c r="AE288" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF288" t="inlineStr"/>
       <c r="AG288" t="b">
@@ -33226,6 +33230,112 @@
       </c>
       <c r="AY288" t="inlineStr"/>
       <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134488457</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>129564006</v>
+      </c>
+      <c r="B289" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr"/>
+      <c r="J289" t="inlineStr"/>
+      <c r="K289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q289" t="n">
+        <v>686681</v>
+      </c>
+      <c r="R289" t="n">
+        <v>6563025</v>
+      </c>
+      <c r="S289" t="n">
+        <v>10</v>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y289" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD289" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE289" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF289" t="inlineStr"/>
+      <c r="AG289" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT289" t="inlineStr"/>
+      <c r="AW289" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX289" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129564006</t>
         </is>
@@ -33520,6 +33630,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ289"/>
+  <dimension ref="A1:AZ290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5102,7 +5102,7 @@
         <v>136947605</v>
       </c>
       <c r="B41" t="n">
-        <v>92792</v>
+        <v>92798</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>136557175</v>
       </c>
       <c r="B47" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136631756</v>
       </c>
       <c r="B56" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>136631891</v>
       </c>
       <c r="B57" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>137045816</v>
       </c>
       <c r="B58" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>136631926</v>
       </c>
       <c r="B80" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>136557135</v>
       </c>
       <c r="B83" t="n">
-        <v>91599</v>
+        <v>91605</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>136635740</v>
       </c>
       <c r="B84" t="n">
-        <v>91599</v>
+        <v>91605</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>136946030</v>
       </c>
       <c r="B85" t="n">
-        <v>91599</v>
+        <v>91605</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>136778691</v>
       </c>
       <c r="B90" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>136778733</v>
       </c>
       <c r="B91" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>137045788</v>
       </c>
       <c r="B92" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>137045804</v>
       </c>
       <c r="B93" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>137045811</v>
       </c>
       <c r="B94" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>137045817</v>
       </c>
       <c r="B95" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>137045826</v>
       </c>
       <c r="B96" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>137045864</v>
       </c>
       <c r="B97" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>137045871</v>
       </c>
       <c r="B98" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>137045877</v>
       </c>
       <c r="B99" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>137045887</v>
       </c>
       <c r="B100" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>137088961</v>
       </c>
       <c r="B101" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>137089019</v>
       </c>
       <c r="B102" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>136557228</v>
       </c>
       <c r="B106" t="n">
-        <v>92796</v>
+        <v>92802</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -20231,42 +20231,38 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>136346869</v>
+        <v>137143261</v>
       </c>
       <c r="B175" t="n">
-        <v>58164</v>
+        <v>58169</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
@@ -20274,10 +20270,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>687222</v>
+        <v>686827</v>
       </c>
       <c r="R175" t="n">
-        <v>6563288</v>
+        <v>6562789</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20304,12 +20300,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20335,13 +20331,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136346869</t>
+          <t>https://artportalen.se/Sighting/137143261</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>136631771</v>
+        <v>136346869</v>
       </c>
       <c r="B176" t="n">
         <v>58164</v>
@@ -20384,13 +20380,13 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>686948</v>
+        <v>687222</v>
       </c>
       <c r="R176" t="n">
-        <v>6563152</v>
+        <v>6563288</v>
       </c>
       <c r="S176" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -20414,12 +20410,12 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20445,16 +20441,16 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136631771</t>
+          <t>https://artportalen.se/Sighting/136346869</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121859656</v>
+        <v>136631771</v>
       </c>
       <c r="B177" t="n">
-        <v>5199</v>
+        <v>58164</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20462,16 +20458,16 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>105930</v>
+        <v>103023</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -20480,19 +20476,27 @@
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>687094</v>
+        <v>686948</v>
       </c>
       <c r="R177" t="n">
-        <v>6563235</v>
+        <v>6563152</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -20516,22 +20520,12 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20542,48 +20536,28 @@
       </c>
       <c r="AG177" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL177" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859656</t>
+          <t>https://artportalen.se/Sighting/136631771</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126061088</v>
+        <v>121859656</v>
       </c>
       <c r="B178" t="n">
         <v>5199</v>
@@ -20614,14 +20588,14 @@
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>686865</v>
+        <v>687094</v>
       </c>
       <c r="R178" t="n">
-        <v>6562977</v>
+        <v>6563235</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20648,22 +20622,22 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20687,12 +20661,12 @@
       </c>
       <c r="AL178" t="inlineStr">
         <is>
-          <t>Klen torr granlåga.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>Picea abies # Klen torr granlåga.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr"/>
@@ -20703,19 +20677,19 @@
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061088</t>
+          <t>https://artportalen.se/Sighting/121859656</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126061109</v>
+        <v>126061088</v>
       </c>
       <c r="B179" t="n">
         <v>5199</v>
@@ -20750,10 +20724,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>686946</v>
+        <v>686865</v>
       </c>
       <c r="R179" t="n">
-        <v>6562741</v>
+        <v>6562977</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20785,7 +20759,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -20795,7 +20769,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20835,22 +20809,22 @@
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061109</t>
+          <t>https://artportalen.se/Sighting/126061088</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>121859629</v>
+        <v>126061109</v>
       </c>
       <c r="B180" t="n">
-        <v>8455</v>
+        <v>5199</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20858,34 +20832,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>686792</v>
+        <v>686946</v>
       </c>
       <c r="R180" t="n">
-        <v>6563030</v>
+        <v>6562741</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20912,22 +20886,22 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20941,17 +20915,22 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL180" t="inlineStr">
+        <is>
+          <t>Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr"/>
@@ -20962,19 +20941,19 @@
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859629</t>
+          <t>https://artportalen.se/Sighting/126061109</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>121859631</v>
+        <v>121859629</v>
       </c>
       <c r="B181" t="n">
         <v>8455</v>
@@ -21009,10 +20988,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>686934</v>
+        <v>686792</v>
       </c>
       <c r="R181" t="n">
-        <v>6563148</v>
+        <v>6563030</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21044,7 +21023,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -21054,7 +21033,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21095,13 +21074,13 @@
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859631</t>
+          <t>https://artportalen.se/Sighting/121859629</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122929535</v>
+        <v>121859631</v>
       </c>
       <c r="B182" t="n">
         <v>8455</v>
@@ -21129,29 +21108,20 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>686612</v>
+        <v>686934</v>
       </c>
       <c r="R182" t="n">
-        <v>6562882</v>
+        <v>6563148</v>
       </c>
       <c r="S182" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21175,22 +21145,22 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21201,31 +21171,46 @@
       </c>
       <c r="AG182" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929535</t>
+          <t>https://artportalen.se/Sighting/121859631</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>136259916</v>
+        <v>122929535</v>
       </c>
       <c r="B183" t="n">
-        <v>8463</v>
+        <v>8455</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21250,29 +21235,29 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>686457</v>
+        <v>686612</v>
       </c>
       <c r="R183" t="n">
-        <v>6563062</v>
+        <v>6562882</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21296,12 +21281,22 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21310,34 +21305,33 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
-      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136259916</t>
+          <t>https://artportalen.se/Sighting/122929535</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>125974903</v>
+        <v>136259916</v>
       </c>
       <c r="B184" t="n">
-        <v>8444</v>
+        <v>8463</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21345,28 +21339,24 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
@@ -21378,17 +21368,17 @@
       <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>söder om Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>686838</v>
+        <v>686457</v>
       </c>
       <c r="R184" t="n">
-        <v>6562733</v>
+        <v>6563062</v>
       </c>
       <c r="S184" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21412,17 +21402,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>gammal björklåga med spår längs hela stammen</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21435,47 +21420,27 @@
       <c r="AG184" t="b">
         <v>0</v>
       </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Betula pendula</t>
-        </is>
-      </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125974903</t>
+          <t>https://artportalen.se/Sighting/136259916</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>126061086</v>
+        <v>125974903</v>
       </c>
       <c r="B185" t="n">
         <v>8444</v>
@@ -21503,20 +21468,33 @@
           <t>Janson, 1856</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr"/>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>söder om Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>686932</v>
+        <v>686838</v>
       </c>
       <c r="R185" t="n">
-        <v>6563067</v>
+        <v>6562733</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21543,19 +21521,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>15:00</t>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>gammal björklåga med spår längs hela stammen</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21564,50 +21537,51 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
+      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vårtbjörk</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL185" t="inlineStr">
-        <is>
-          <t>Barklös björklåga.</t>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>Betula # Barklös björklåga.</t>
+          <t>Wood surface of dead wood # Betula pendula</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061086</t>
+          <t>https://artportalen.se/Sighting/125974903</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>126061105</v>
+        <v>126061086</v>
       </c>
       <c r="B186" t="n">
         <v>8444</v>
@@ -21642,10 +21616,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>686860</v>
+        <v>686932</v>
       </c>
       <c r="R186" t="n">
-        <v>6562743</v>
+        <v>6563067</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21677,7 +21651,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -21687,7 +21661,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21709,9 +21683,14 @@
           <t>Betula</t>
         </is>
       </c>
+      <c r="AL186" t="inlineStr">
+        <is>
+          <t>Barklös björklåga.</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Betula # Barklös björklåga.</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr"/>
@@ -21722,22 +21701,22 @@
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061105</t>
+          <t>https://artportalen.se/Sighting/126061086</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>136635739</v>
+        <v>126061105</v>
       </c>
       <c r="B187" t="n">
-        <v>8452</v>
+        <v>8444</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21765,17 +21744,17 @@
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Utanför Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>686973</v>
+        <v>686860</v>
       </c>
       <c r="R187" t="n">
-        <v>6563106</v>
+        <v>6562743</v>
       </c>
       <c r="S187" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21799,27 +21778,22 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>Björklåga</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21830,31 +21804,46 @@
       </c>
       <c r="AG187" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Vendela Ström</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Vendela Ström</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136635739</t>
+          <t>https://artportalen.se/Sighting/126061105</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>136767157</v>
+        <v>136635739</v>
       </c>
       <c r="B188" t="n">
-        <v>56875</v>
+        <v>8452</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21862,37 +21851,37 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>205992</v>
+        <v>106554</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Norrby torp, Tyresta, Srm</t>
+          <t>Utanför Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>687260</v>
+        <v>686973</v>
       </c>
       <c r="R188" t="n">
-        <v>6563241</v>
+        <v>6563106</v>
       </c>
       <c r="S188" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21916,22 +21905,27 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>04:39</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>04:39</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>Björklåga</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21946,24 +21940,24 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Vendela Ström</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Vendela Ström</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767157</t>
+          <t>https://artportalen.se/Sighting/136635739</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>136867583</v>
+        <v>136767157</v>
       </c>
       <c r="B189" t="n">
         <v>56875</v>
@@ -21998,10 +21992,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>687164</v>
+        <v>687260</v>
       </c>
       <c r="R189" t="n">
-        <v>6563337</v>
+        <v>6563241</v>
       </c>
       <c r="S189" t="n">
         <v>25</v>
@@ -22028,22 +22022,22 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>04:12</t>
+          <t>04:39</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>04:12</t>
+          <t>04:39</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -22069,13 +22063,13 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867583</t>
+          <t>https://artportalen.se/Sighting/136767157</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>136867591</v>
+        <v>136867583</v>
       </c>
       <c r="B190" t="n">
         <v>56875</v>
@@ -22110,10 +22104,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>686871</v>
+        <v>687164</v>
       </c>
       <c r="R190" t="n">
-        <v>6563175</v>
+        <v>6563337</v>
       </c>
       <c r="S190" t="n">
         <v>25</v>
@@ -22140,22 +22134,22 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>04:19</t>
+          <t>04:12</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>04:19</t>
+          <t>04:12</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22181,16 +22175,16 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867591</t>
+          <t>https://artportalen.se/Sighting/136867583</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>136767122</v>
+        <v>136867591</v>
       </c>
       <c r="B191" t="n">
-        <v>56887</v>
+        <v>56875</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22198,21 +22192,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -22222,10 +22216,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>686692</v>
+        <v>686871</v>
       </c>
       <c r="R191" t="n">
-        <v>6563011</v>
+        <v>6563175</v>
       </c>
       <c r="S191" t="n">
         <v>25</v>
@@ -22252,22 +22246,22 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>04:19</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>04:19</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22293,13 +22287,13 @@
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767122</t>
+          <t>https://artportalen.se/Sighting/136867591</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>136767160</v>
+        <v>136767122</v>
       </c>
       <c r="B192" t="n">
         <v>56887</v>
@@ -22334,10 +22328,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>687260</v>
+        <v>686692</v>
       </c>
       <c r="R192" t="n">
-        <v>6563241</v>
+        <v>6563011</v>
       </c>
       <c r="S192" t="n">
         <v>25</v>
@@ -22364,22 +22358,22 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>01:27</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>01:27</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22405,13 +22399,13 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767160</t>
+          <t>https://artportalen.se/Sighting/136767122</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>136867584</v>
+        <v>136767160</v>
       </c>
       <c r="B193" t="n">
         <v>56887</v>
@@ -22446,10 +22440,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>687164</v>
+        <v>687260</v>
       </c>
       <c r="R193" t="n">
-        <v>6563337</v>
+        <v>6563241</v>
       </c>
       <c r="S193" t="n">
         <v>25</v>
@@ -22476,22 +22470,22 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>01:27</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>01:27</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22517,13 +22511,13 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867584</t>
+          <t>https://artportalen.se/Sighting/136767160</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>136867597</v>
+        <v>136867584</v>
       </c>
       <c r="B194" t="n">
         <v>56887</v>
@@ -22558,10 +22552,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>686871</v>
+        <v>687164</v>
       </c>
       <c r="R194" t="n">
-        <v>6563175</v>
+        <v>6563337</v>
       </c>
       <c r="S194" t="n">
         <v>25</v>
@@ -22588,22 +22582,22 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>23:43</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>23:43</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22629,36 +22623,40 @@
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867597</t>
+          <t>https://artportalen.se/Sighting/136867584</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>136767120</v>
+        <v>136867597</v>
       </c>
       <c r="B195" t="n">
-        <v>56866</v>
+        <v>56887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr"/>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
@@ -22666,10 +22664,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>686692</v>
+        <v>686871</v>
       </c>
       <c r="R195" t="n">
-        <v>6563011</v>
+        <v>6563175</v>
       </c>
       <c r="S195" t="n">
         <v>25</v>
@@ -22696,22 +22694,22 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>23:43</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>23:43</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22737,13 +22735,13 @@
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767120</t>
+          <t>https://artportalen.se/Sighting/136867597</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>136767159</v>
+        <v>136767120</v>
       </c>
       <c r="B196" t="n">
         <v>56866</v>
@@ -22774,10 +22772,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>687260</v>
+        <v>686692</v>
       </c>
       <c r="R196" t="n">
-        <v>6563241</v>
+        <v>6563011</v>
       </c>
       <c r="S196" t="n">
         <v>25</v>
@@ -22804,22 +22802,22 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22845,13 +22843,13 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767159</t>
+          <t>https://artportalen.se/Sighting/136767120</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>136867586</v>
+        <v>136767159</v>
       </c>
       <c r="B197" t="n">
         <v>56866</v>
@@ -22882,10 +22880,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>687164</v>
+        <v>687260</v>
       </c>
       <c r="R197" t="n">
-        <v>6563337</v>
+        <v>6563241</v>
       </c>
       <c r="S197" t="n">
         <v>25</v>
@@ -22912,22 +22910,22 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22953,13 +22951,13 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867586</t>
+          <t>https://artportalen.se/Sighting/136767159</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>136867588</v>
+        <v>136867586</v>
       </c>
       <c r="B198" t="n">
         <v>56866</v>
@@ -22990,10 +22988,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>686871</v>
+        <v>687164</v>
       </c>
       <c r="R198" t="n">
-        <v>6563175</v>
+        <v>6563337</v>
       </c>
       <c r="S198" t="n">
         <v>25</v>
@@ -23020,22 +23018,22 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>22:16</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>22:16</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -23061,16 +23059,16 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867588</t>
+          <t>https://artportalen.se/Sighting/136867586</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>136767162</v>
+        <v>136867588</v>
       </c>
       <c r="B199" t="n">
-        <v>56889</v>
+        <v>56866</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23078,23 +23076,19 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
@@ -23102,10 +23096,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>687260</v>
+        <v>686871</v>
       </c>
       <c r="R199" t="n">
-        <v>6563241</v>
+        <v>6563175</v>
       </c>
       <c r="S199" t="n">
         <v>25</v>
@@ -23132,22 +23126,22 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>00:57</t>
+          <t>22:16</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>00:57</t>
+          <t>22:16</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -23173,13 +23167,13 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767162</t>
+          <t>https://artportalen.se/Sighting/136867588</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>136867594</v>
+        <v>136767162</v>
       </c>
       <c r="B200" t="n">
         <v>56889</v>
@@ -23214,10 +23208,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>686871</v>
+        <v>687260</v>
       </c>
       <c r="R200" t="n">
-        <v>6563175</v>
+        <v>6563241</v>
       </c>
       <c r="S200" t="n">
         <v>25</v>
@@ -23244,22 +23238,22 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>00:57</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>00:57</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -23285,33 +23279,33 @@
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136867594</t>
+          <t>https://artportalen.se/Sighting/136767162</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>111182876</v>
+        <v>136867594</v>
       </c>
       <c r="B201" t="n">
-        <v>58790</v>
+        <v>56889</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>208245</v>
+        <v>206002</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -23319,29 +23313,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>686971</v>
+        <v>686871</v>
       </c>
       <c r="R201" t="n">
-        <v>6563333</v>
+        <v>6563175</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -23365,12 +23350,22 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23379,31 +23374,30 @@
       <c r="AE201" t="b">
         <v>0</v>
       </c>
-      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111182876</t>
+          <t>https://artportalen.se/Sighting/136867594</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>126061089</v>
+        <v>111182876</v>
       </c>
       <c r="B202" t="n">
         <v>58790</v>
@@ -23436,21 +23430,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>686871</v>
+        <v>686971</v>
       </c>
       <c r="R202" t="n">
-        <v>6562972</v>
+        <v>6563333</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -23477,22 +23471,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23501,30 +23485,31 @@
       <c r="AE202" t="b">
         <v>0</v>
       </c>
+      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061089</t>
+          <t>https://artportalen.se/Sighting/111182876</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>126061098</v>
+        <v>126061089</v>
       </c>
       <c r="B203" t="n">
         <v>58790</v>
@@ -23552,17 +23537,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr"/>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>686857</v>
+        <v>686871</v>
       </c>
       <c r="R203" t="n">
-        <v>6562875</v>
+        <v>6562972</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23594,7 +23588,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -23604,7 +23598,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23624,19 +23618,19 @@
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061098</t>
+          <t>https://artportalen.se/Sighting/126061089</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128095464</v>
+        <v>126061098</v>
       </c>
       <c r="B204" t="n">
         <v>58790</v>
@@ -23664,30 +23658,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>687155</v>
+        <v>686857</v>
       </c>
       <c r="R204" t="n">
-        <v>6563193</v>
+        <v>6562875</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23714,12 +23695,22 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23728,34 +23719,33 @@
       <c r="AE204" t="b">
         <v>0</v>
       </c>
-      <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="b">
         <v>0</v>
       </c>
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128095464</t>
+          <t>https://artportalen.se/Sighting/126061098</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>134488564</v>
+        <v>128095464</v>
       </c>
       <c r="B205" t="n">
-        <v>58812</v>
+        <v>58790</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23786,7 +23776,11 @@
         </is>
       </c>
       <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
@@ -23796,10 +23790,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>687272</v>
+        <v>687155</v>
       </c>
       <c r="R205" t="n">
-        <v>6563263</v>
+        <v>6563193</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23826,17 +23820,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>Ca 2-3 cm lång.</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23863,16 +23852,16 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134488564</t>
+          <t>https://artportalen.se/Sighting/128095464</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>126061108</v>
+        <v>134488564</v>
       </c>
       <c r="B206" t="n">
-        <v>58817</v>
+        <v>58812</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23880,21 +23869,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -23902,26 +23891,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>686907</v>
+        <v>687272</v>
       </c>
       <c r="R206" t="n">
-        <v>6562760</v>
+        <v>6563263</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23948,22 +23932,17 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>Ca 2-3 cm lång.</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23972,33 +23951,34 @@
       <c r="AE206" t="b">
         <v>0</v>
       </c>
+      <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="b">
         <v>0</v>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061108</t>
+          <t>https://artportalen.se/Sighting/134488564</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>136777569</v>
+        <v>126061108</v>
       </c>
       <c r="B207" t="n">
-        <v>58872</v>
+        <v>58817</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24023,20 +24003,34 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr"/>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Norrby torp, Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>687280</v>
+        <v>686907</v>
       </c>
       <c r="R207" t="n">
-        <v>6563262</v>
+        <v>6562760</v>
       </c>
       <c r="S207" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -24060,22 +24054,22 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -24095,22 +24089,22 @@
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136777569</t>
+          <t>https://artportalen.se/Sighting/126061108</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>126061081</v>
+        <v>136777569</v>
       </c>
       <c r="B208" t="n">
-        <v>58815</v>
+        <v>58872</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24118,51 +24112,37 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>208250</v>
+        <v>208249</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>687058</v>
+        <v>687280</v>
       </c>
       <c r="R208" t="n">
-        <v>6563228</v>
+        <v>6563262</v>
       </c>
       <c r="S208" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -24186,22 +24166,22 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -24221,22 +24201,22 @@
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061081</t>
+          <t>https://artportalen.se/Sighting/136777569</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>117554483</v>
+        <v>126061081</v>
       </c>
       <c r="B209" t="n">
-        <v>99035</v>
+        <v>58815</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24244,41 +24224,51 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>219790</v>
+        <v>208250</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>686878</v>
+        <v>687058</v>
       </c>
       <c r="R209" t="n">
-        <v>6562971</v>
+        <v>6563228</v>
       </c>
       <c r="S209" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -24302,12 +24292,22 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -24316,31 +24316,30 @@
       <c r="AE209" t="b">
         <v>0</v>
       </c>
-      <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="b">
         <v>0</v>
       </c>
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117554483</t>
+          <t>https://artportalen.se/Sighting/126061081</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>126003792</v>
+        <v>117554483</v>
       </c>
       <c r="B210" t="n">
         <v>99035</v>
@@ -24375,17 +24374,17 @@
       <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>687046</v>
+        <v>686878</v>
       </c>
       <c r="R210" t="n">
-        <v>6563346</v>
+        <v>6562971</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -24409,12 +24408,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24441,13 +24440,13 @@
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126003792</t>
+          <t>https://artportalen.se/Sighting/117554483</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>126005160</v>
+        <v>126003792</v>
       </c>
       <c r="B211" t="n">
         <v>99035</v>
@@ -24486,10 +24485,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>687034</v>
+        <v>687046</v>
       </c>
       <c r="R211" t="n">
-        <v>6563204</v>
+        <v>6563346</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -24548,13 +24547,13 @@
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126005160</t>
+          <t>https://artportalen.se/Sighting/126003792</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>126061084</v>
+        <v>126005160</v>
       </c>
       <c r="B212" t="n">
         <v>99035</v>
@@ -24583,16 +24582,20 @@
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>687014</v>
+        <v>687034</v>
       </c>
       <c r="R212" t="n">
-        <v>6563215</v>
+        <v>6563204</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24619,22 +24622,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24643,30 +24636,31 @@
       <c r="AE212" t="b">
         <v>0</v>
       </c>
+      <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061084</t>
+          <t>https://artportalen.se/Sighting/126005160</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>126061091</v>
+        <v>126061084</v>
       </c>
       <c r="B213" t="n">
         <v>99035</v>
@@ -24701,10 +24695,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>686871</v>
+        <v>687014</v>
       </c>
       <c r="R213" t="n">
-        <v>6562972</v>
+        <v>6563215</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -24736,7 +24730,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -24746,7 +24740,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24772,13 +24766,13 @@
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061091</t>
+          <t>https://artportalen.se/Sighting/126061084</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>126061099</v>
+        <v>126061091</v>
       </c>
       <c r="B214" t="n">
         <v>99035</v>
@@ -24813,10 +24807,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>686857</v>
+        <v>686871</v>
       </c>
       <c r="R214" t="n">
-        <v>6562875</v>
+        <v>6562972</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24848,7 +24842,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -24858,7 +24852,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24878,19 +24872,19 @@
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061099</t>
+          <t>https://artportalen.se/Sighting/126061091</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>126061102</v>
+        <v>126061099</v>
       </c>
       <c r="B215" t="n">
         <v>99035</v>
@@ -24925,10 +24919,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>686837</v>
+        <v>686857</v>
       </c>
       <c r="R215" t="n">
-        <v>6562829</v>
+        <v>6562875</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24960,7 +24954,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -24970,7 +24964,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24996,13 +24990,13 @@
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061102</t>
+          <t>https://artportalen.se/Sighting/126061099</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>126233785</v>
+        <v>126061102</v>
       </c>
       <c r="B216" t="n">
         <v>99035</v>
@@ -25031,24 +25025,16 @@
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>686839</v>
+        <v>686837</v>
       </c>
       <c r="R216" t="n">
-        <v>6563016</v>
+        <v>6562829</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -25075,12 +25061,22 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -25089,31 +25085,30 @@
       <c r="AE216" t="b">
         <v>0</v>
       </c>
-      <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="b">
         <v>0</v>
       </c>
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126233785</t>
+          <t>https://artportalen.se/Sighting/126061102</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>126234010</v>
+        <v>126233785</v>
       </c>
       <c r="B217" t="n">
         <v>99035</v>
@@ -25156,10 +25151,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>687160</v>
+        <v>686839</v>
       </c>
       <c r="R217" t="n">
-        <v>6563261</v>
+        <v>6563016</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -25212,19 +25207,19 @@
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234010</t>
+          <t>https://artportalen.se/Sighting/126233785</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>126234159</v>
+        <v>126234010</v>
       </c>
       <c r="B218" t="n">
         <v>99035</v>
@@ -25252,13 +25247,13 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
@@ -25267,13 +25262,13 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>687297</v>
+        <v>687160</v>
       </c>
       <c r="R218" t="n">
-        <v>6563381</v>
+        <v>6563261</v>
       </c>
       <c r="S218" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -25303,11 +25298,6 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>Ett flertal i blomning.</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -25328,19 +25318,19 @@
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Ulf Johansson</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234159</t>
+          <t>https://artportalen.se/Sighting/126234010</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>126234439</v>
+        <v>126234159</v>
       </c>
       <c r="B219" t="n">
         <v>99035</v>
@@ -25370,34 +25360,26 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>686777</v>
+        <v>687297</v>
       </c>
       <c r="R219" t="n">
-        <v>6563073</v>
+        <v>6563381</v>
       </c>
       <c r="S219" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -25427,6 +25409,11 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>Ett flertal i blomning.</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -25442,24 +25429,24 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234439</t>
+          <t>https://artportalen.se/Sighting/126234159</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>126234644</v>
+        <v>126234439</v>
       </c>
       <c r="B220" t="n">
         <v>99035</v>
@@ -25489,7 +25476,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -25497,7 +25484,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
@@ -25506,10 +25497,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>686837</v>
+        <v>686777</v>
       </c>
       <c r="R220" t="n">
-        <v>6562967</v>
+        <v>6563073</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25568,13 +25559,13 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234644</t>
+          <t>https://artportalen.se/Sighting/126234439</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>126234771</v>
+        <v>126234644</v>
       </c>
       <c r="B221" t="n">
         <v>99035</v>
@@ -25604,7 +25595,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -25617,14 +25608,14 @@
       <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Norrby mosse OSO, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>686976</v>
+        <v>686837</v>
       </c>
       <c r="R221" t="n">
-        <v>6563107</v>
+        <v>6562967</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25683,16 +25674,16 @@
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234771</t>
+          <t>https://artportalen.se/Sighting/126234644</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>133767702</v>
+        <v>126234771</v>
       </c>
       <c r="B222" t="n">
-        <v>99112</v>
+        <v>99035</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25717,21 +25708,29 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr"/>
       <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse OSO, Srm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>686845</v>
+        <v>686976</v>
       </c>
       <c r="R222" t="n">
-        <v>6563325</v>
+        <v>6563107</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25758,12 +25757,12 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -25779,27 +25778,27 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133767702</t>
+          <t>https://artportalen.se/Sighting/126234771</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>126061092</v>
+        <v>133767702</v>
       </c>
       <c r="B223" t="n">
-        <v>99022</v>
+        <v>99112</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25807,43 +25806,38 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>686880</v>
+        <v>686845</v>
       </c>
       <c r="R223" t="n">
-        <v>6562892</v>
+        <v>6563325</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25870,22 +25864,12 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z223" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB223" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25894,30 +25878,31 @@
       <c r="AE223" t="b">
         <v>0</v>
       </c>
+      <c r="AF223" t="inlineStr"/>
       <c r="AG223" t="b">
         <v>0</v>
       </c>
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061092</t>
+          <t>https://artportalen.se/Sighting/133767702</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>126061094</v>
+        <v>126061092</v>
       </c>
       <c r="B224" t="n">
         <v>99022</v>
@@ -25961,10 +25946,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>686866</v>
+        <v>686880</v>
       </c>
       <c r="R224" t="n">
-        <v>6562874</v>
+        <v>6562892</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25996,7 +25981,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -26006,7 +25991,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -26032,13 +26017,13 @@
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061094</t>
+          <t>https://artportalen.se/Sighting/126061092</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>126061100</v>
+        <v>126061094</v>
       </c>
       <c r="B225" t="n">
         <v>99022</v>
@@ -26068,7 +26053,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -26082,10 +26067,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>686857</v>
+        <v>686866</v>
       </c>
       <c r="R225" t="n">
-        <v>6562875</v>
+        <v>6562874</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26117,7 +26102,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -26127,7 +26112,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -26153,43 +26138,43 @@
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061100</t>
+          <t>https://artportalen.se/Sighting/126061094</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>86686018</v>
+        <v>126061100</v>
       </c>
       <c r="B226" t="n">
-        <v>99118</v>
+        <v>99022</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -26197,23 +26182,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Tyresta S Ungfars kärr, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>686831</v>
+        <v>686857</v>
       </c>
       <c r="R226" t="n">
-        <v>6563296</v>
+        <v>6562875</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26240,17 +26218,22 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2020-07-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2020-07-04</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>Från Ungfars kärrs södra spets och ca 200 meter österut. Ungefär hälften av skotten utanför parkens gräns. 4 blomstänglar. Området var bökat av vildsvin. Vissa skott var uppgrävda.</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -26259,31 +26242,30 @@
       <c r="AE226" t="b">
         <v>0</v>
       </c>
-      <c r="AF226" t="inlineStr"/>
       <c r="AG226" t="b">
         <v>0</v>
       </c>
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86686018</t>
+          <t>https://artportalen.se/Sighting/126061100</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>96672256</v>
+        <v>86686018</v>
       </c>
       <c r="B227" t="n">
         <v>99118</v>
@@ -26311,24 +26293,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr"/>
       <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>NO Norrby mosse, Srm</t>
+          <t>Tyresta S Ungfars kärr, Srm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>686848</v>
+        <v>686831</v>
       </c>
       <c r="R227" t="n">
-        <v>6563295</v>
+        <v>6563296</v>
       </c>
       <c r="S227" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -26352,12 +26346,17 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2020-07-04</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2020-07-04</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>Från Ungfars kärrs södra spets och ca 200 meter österut. Ungefär hälften av skotten utanför parkens gräns. 4 blomstänglar. Området var bökat av vildsvin. Vissa skott var uppgrävda.</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -26373,24 +26372,24 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96672256</t>
+          <t>https://artportalen.se/Sighting/86686018</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>97242656</v>
+        <v>96672256</v>
       </c>
       <c r="B228" t="n">
         <v>99118</v>
@@ -26419,21 +26418,23 @@
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>OSO Ungfars mosse, Srm</t>
+          <t>NO Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>686846</v>
+        <v>686848</v>
       </c>
       <c r="R228" t="n">
-        <v>6563316</v>
+        <v>6563295</v>
       </c>
       <c r="S228" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -26457,22 +26458,12 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="Z228" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="AB228" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -26481,30 +26472,31 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
+      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Thomas Strid, Bodil Ravn, Ulf Johansson, Tiina Laantee</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97242656</t>
+          <t>https://artportalen.se/Sighting/96672256</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>97243108</v>
+        <v>97242656</v>
       </c>
       <c r="B229" t="n">
         <v>99118</v>
@@ -26537,17 +26529,17 @@
       <c r="L229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Tyresta, Srm</t>
+          <t>OSO Ungfars mosse, Srm</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>686847</v>
+        <v>686846</v>
       </c>
       <c r="R229" t="n">
-        <v>6563308</v>
+        <v>6563316</v>
       </c>
       <c r="S229" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -26576,7 +26568,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -26586,7 +26578,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -26612,13 +26604,13 @@
       <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97243108</t>
+          <t>https://artportalen.se/Sighting/97242656</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>97330311</v>
+        <v>97243108</v>
       </c>
       <c r="B230" t="n">
         <v>99118</v>
@@ -26646,29 +26638,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Tyresta NP, SSV Bylsjön (*knärot* /stjälk/), Srm</t>
+          <t>Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q230" t="n">
         <v>686847</v>
       </c>
       <c r="R230" t="n">
-        <v>6563309</v>
+        <v>6563308</v>
       </c>
       <c r="S230" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -26690,24 +26675,24 @@
           <t>Österhaninge</t>
         </is>
       </c>
-      <c r="X230" t="inlineStr">
-        <is>
-          <t>AB-Han-0218</t>
-        </is>
-      </c>
       <c r="Y230" t="inlineStr">
         <is>
           <t>2021-11-20</t>
         </is>
       </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>2021-11-20</t>
         </is>
       </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>/Ej räknad/</t>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -26722,28 +26707,24 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Tiina Laantee, Ulf Johansson, Bodil Ravn, Thomas Strid</t>
-        </is>
-      </c>
-      <c r="AY230" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Thomas Strid, Bodil Ravn, Ulf Johansson, Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97330311</t>
+          <t>https://artportalen.se/Sighting/97243108</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>98104097</v>
+        <v>97330311</v>
       </c>
       <c r="B231" t="n">
         <v>99118</v>
@@ -26773,27 +26754,24 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="N231" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Tyresta NP, SSV Bylsjön (*knärot* /stjälk/), Srm</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>686934</v>
+        <v>686847</v>
       </c>
       <c r="R231" t="n">
-        <v>6563325</v>
+        <v>6563309</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26818,19 +26796,24 @@
           <t>Österhaninge</t>
         </is>
       </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>AB-Han-0218</t>
+        </is>
+      </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>Intill djurstig och granlåga</t>
+          <t>/Ej räknad/</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26839,31 +26822,34 @@
       <c r="AE231" t="b">
         <v>0</v>
       </c>
-      <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="b">
         <v>0</v>
       </c>
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
-        </is>
-      </c>
-      <c r="AY231" t="inlineStr"/>
+          <t>Tiina Laantee, Ulf Johansson, Bodil Ravn, Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98104097</t>
+          <t>https://artportalen.se/Sighting/97330311</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>104249959</v>
+        <v>98104097</v>
       </c>
       <c r="B232" t="n">
         <v>99118</v>
@@ -26891,24 +26877,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr"/>
       <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>687011</v>
+        <v>686934</v>
       </c>
       <c r="R232" t="n">
-        <v>6562869</v>
+        <v>6563325</v>
       </c>
       <c r="S232" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -26932,17 +26926,17 @@
       </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="AC232" t="inlineStr">
         <is>
-          <t>Samma lokal som noterades 17/11-21. Ca 25 ex. Koordinaterna har varierat något vid besöken.</t>
+          <t>Intill djurstig och granlåga</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26958,24 +26952,24 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104249959</t>
+          <t>https://artportalen.se/Sighting/98104097</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>109890506</v>
+        <v>104249959</v>
       </c>
       <c r="B233" t="n">
         <v>99118</v>
@@ -27010,17 +27004,17 @@
       <c r="N233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Ö Norrby Mosse, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>686831</v>
+        <v>687011</v>
       </c>
       <c r="R233" t="n">
-        <v>6563216</v>
+        <v>6562869</v>
       </c>
       <c r="S233" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -27044,12 +27038,17 @@
       </c>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>Samma lokal som noterades 17/11-21. Ca 25 ex. Koordinaterna har varierat något vid besöken.</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -27076,13 +27075,13 @@
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109890506</t>
+          <t>https://artportalen.se/Sighting/104249959</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>119475594</v>
+        <v>109890506</v>
       </c>
       <c r="B234" t="n">
         <v>99118</v>
@@ -27110,29 +27109,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J234" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr"/>
       <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>Ö Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>686995</v>
+        <v>686831</v>
       </c>
       <c r="R234" t="n">
-        <v>6563315</v>
+        <v>6563216</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -27159,12 +27150,12 @@
       </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -27191,13 +27182,13 @@
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119475594</t>
+          <t>https://artportalen.se/Sighting/109890506</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>121859637</v>
+        <v>119475594</v>
       </c>
       <c r="B235" t="n">
         <v>99118</v>
@@ -27225,17 +27216,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr"/>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>686863</v>
+        <v>686995</v>
       </c>
       <c r="R235" t="n">
-        <v>6563252</v>
+        <v>6563315</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27262,22 +27265,12 @@
       </c>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z235" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB235" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -27286,30 +27279,31 @@
       <c r="AE235" t="b">
         <v>0</v>
       </c>
+      <c r="AF235" t="inlineStr"/>
       <c r="AG235" t="b">
         <v>0</v>
       </c>
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859637</t>
+          <t>https://artportalen.se/Sighting/119475594</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>121859638</v>
+        <v>121859637</v>
       </c>
       <c r="B236" t="n">
         <v>99118</v>
@@ -27344,10 +27338,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>686826</v>
+        <v>686863</v>
       </c>
       <c r="R236" t="n">
-        <v>6563286</v>
+        <v>6563252</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27379,7 +27373,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -27389,7 +27383,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -27415,13 +27409,13 @@
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859638</t>
+          <t>https://artportalen.se/Sighting/121859637</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>121859639</v>
+        <v>121859638</v>
       </c>
       <c r="B237" t="n">
         <v>99118</v>
@@ -27456,10 +27450,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>686827</v>
+        <v>686826</v>
       </c>
       <c r="R237" t="n">
-        <v>6563296</v>
+        <v>6563286</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27491,7 +27485,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -27501,7 +27495,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -27527,13 +27521,13 @@
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859639</t>
+          <t>https://artportalen.se/Sighting/121859638</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>121859640</v>
+        <v>121859639</v>
       </c>
       <c r="B238" t="n">
         <v>99118</v>
@@ -27568,10 +27562,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>686837</v>
+        <v>686827</v>
       </c>
       <c r="R238" t="n">
-        <v>6563297</v>
+        <v>6563296</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -27603,7 +27597,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -27613,7 +27607,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -27639,13 +27633,13 @@
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859640</t>
+          <t>https://artportalen.se/Sighting/121859639</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>121859642</v>
+        <v>121859640</v>
       </c>
       <c r="B239" t="n">
         <v>99118</v>
@@ -27674,24 +27668,16 @@
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>686834</v>
+        <v>686837</v>
       </c>
       <c r="R239" t="n">
-        <v>6563305</v>
+        <v>6563297</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -27723,7 +27709,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -27733,7 +27719,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -27742,7 +27728,6 @@
       <c r="AE239" t="b">
         <v>0</v>
       </c>
-      <c r="AF239" t="inlineStr"/>
       <c r="AG239" t="b">
         <v>0</v>
       </c>
@@ -27760,13 +27745,13 @@
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859642</t>
+          <t>https://artportalen.se/Sighting/121859640</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>121859643</v>
+        <v>121859642</v>
       </c>
       <c r="B240" t="n">
         <v>99118</v>
@@ -27795,6 +27780,14 @@
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
@@ -27804,7 +27797,7 @@
         <v>686834</v>
       </c>
       <c r="R240" t="n">
-        <v>6563309</v>
+        <v>6563305</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27836,7 +27829,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -27846,7 +27839,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -27855,6 +27848,7 @@
       <c r="AE240" t="b">
         <v>0</v>
       </c>
+      <c r="AF240" t="inlineStr"/>
       <c r="AG240" t="b">
         <v>0</v>
       </c>
@@ -27872,13 +27866,13 @@
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859643</t>
+          <t>https://artportalen.se/Sighting/121859642</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>121859644</v>
+        <v>121859643</v>
       </c>
       <c r="B241" t="n">
         <v>99118</v>
@@ -27913,10 +27907,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>686844</v>
+        <v>686834</v>
       </c>
       <c r="R241" t="n">
-        <v>6563303</v>
+        <v>6563309</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27948,7 +27942,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -27958,7 +27952,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -27984,13 +27978,13 @@
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859644</t>
+          <t>https://artportalen.se/Sighting/121859643</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>121859646</v>
+        <v>121859644</v>
       </c>
       <c r="B242" t="n">
         <v>99118</v>
@@ -28025,7 +28019,7 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>686841</v>
+        <v>686844</v>
       </c>
       <c r="R242" t="n">
         <v>6563303</v>
@@ -28060,7 +28054,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -28070,7 +28064,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -28096,13 +28090,13 @@
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859646</t>
+          <t>https://artportalen.se/Sighting/121859644</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>121859647</v>
+        <v>121859646</v>
       </c>
       <c r="B243" t="n">
         <v>99118</v>
@@ -28137,10 +28131,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>686854</v>
+        <v>686841</v>
       </c>
       <c r="R243" t="n">
-        <v>6563286</v>
+        <v>6563303</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -28172,7 +28166,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -28182,7 +28176,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -28208,13 +28202,13 @@
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859647</t>
+          <t>https://artportalen.se/Sighting/121859646</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>121859649</v>
+        <v>121859647</v>
       </c>
       <c r="B244" t="n">
         <v>99118</v>
@@ -28249,10 +28243,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>686851</v>
+        <v>686854</v>
       </c>
       <c r="R244" t="n">
-        <v>6563299</v>
+        <v>6563286</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -28284,7 +28278,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -28294,7 +28288,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -28320,13 +28314,13 @@
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859649</t>
+          <t>https://artportalen.se/Sighting/121859647</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>121859650</v>
+        <v>121859649</v>
       </c>
       <c r="B245" t="n">
         <v>99118</v>
@@ -28361,10 +28355,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>686895</v>
+        <v>686851</v>
       </c>
       <c r="R245" t="n">
-        <v>6563306</v>
+        <v>6563299</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -28396,7 +28390,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -28406,7 +28400,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -28432,13 +28426,13 @@
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859650</t>
+          <t>https://artportalen.se/Sighting/121859649</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>122220583</v>
+        <v>121859650</v>
       </c>
       <c r="B246" t="n">
         <v>99118</v>
@@ -28466,29 +28460,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J246" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>686996</v>
+        <v>686895</v>
       </c>
       <c r="R246" t="n">
-        <v>6562864</v>
+        <v>6563306</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28515,17 +28497,22 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>Samma lokal som rapporterats -21 och -22 men en ny klon. Den förra har möjligen haft lite problem med grisbök.</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -28534,31 +28521,30 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
-      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122220583</t>
+          <t>https://artportalen.se/Sighting/121859650</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>122781008</v>
+        <v>122220583</v>
       </c>
       <c r="B247" t="n">
         <v>99118</v>
@@ -28586,21 +28572,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr"/>
-      <c r="J247" t="inlineStr"/>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr"/>
       <c r="N247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Knärot, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>686833</v>
+        <v>686996</v>
       </c>
       <c r="R247" t="n">
-        <v>6563215</v>
+        <v>6562864</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28627,17 +28621,17 @@
       </c>
       <c r="Y247" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Samma lokal som rapporterats -21 och -22 men en ny klon. Den förra har möjligen haft lite problem med grisbök.</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28653,24 +28647,24 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122781008</t>
+          <t>https://artportalen.se/Sighting/122220583</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>126418709</v>
+        <v>122781008</v>
       </c>
       <c r="B248" t="n">
         <v>99118</v>
@@ -28698,29 +28692,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J248" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr"/>
       <c r="N248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Knärot, Srm</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>686771</v>
+        <v>686833</v>
       </c>
       <c r="R248" t="n">
-        <v>6563297</v>
+        <v>6563215</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28747,17 +28733,17 @@
       </c>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC248" t="inlineStr">
         <is>
-          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28773,24 +28759,24 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418709</t>
+          <t>https://artportalen.se/Sighting/122781008</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>126418756</v>
+        <v>126418709</v>
       </c>
       <c r="B249" t="n">
         <v>99118</v>
@@ -28820,7 +28806,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -28837,10 +28823,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>686781</v>
+        <v>686771</v>
       </c>
       <c r="R249" t="n">
-        <v>6563292</v>
+        <v>6563297</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28877,7 +28863,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>En av dem i knopp.</t>
+          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28904,13 +28890,13 @@
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418756</t>
+          <t>https://artportalen.se/Sighting/126418709</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>127932426</v>
+        <v>126418756</v>
       </c>
       <c r="B250" t="n">
         <v>99118</v>
@@ -28940,7 +28926,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -28957,10 +28943,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>686998</v>
+        <v>686781</v>
       </c>
       <c r="R250" t="n">
-        <v>6563316</v>
+        <v>6563292</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28987,17 +28973,17 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AC250" t="inlineStr">
         <is>
-          <t>Återfynd, rapporterad -24 med 3 ex. Nu 5 ex.</t>
+          <t>En av dem i knopp.</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -29024,13 +29010,13 @@
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127932426</t>
+          <t>https://artportalen.se/Sighting/126418756</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128341941</v>
+        <v>127932426</v>
       </c>
       <c r="B251" t="n">
         <v>99118</v>
@@ -29060,7 +29046,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -29077,10 +29063,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>687244</v>
+        <v>686998</v>
       </c>
       <c r="R251" t="n">
-        <v>6563404</v>
+        <v>6563316</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -29107,12 +29093,17 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>Återfynd, rapporterad -24 med 3 ex. Nu 5 ex.</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -29139,13 +29130,13 @@
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128341941</t>
+          <t>https://artportalen.se/Sighting/127932426</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129564285</v>
+        <v>128341941</v>
       </c>
       <c r="B252" t="n">
         <v>99118</v>
@@ -29173,8 +29164,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr"/>
-      <c r="J252" t="inlineStr"/>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr"/>
       <c r="N252" t="inlineStr"/>
@@ -29184,10 +29183,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>686625</v>
+        <v>687244</v>
       </c>
       <c r="R252" t="n">
-        <v>6563000</v>
+        <v>6563404</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -29214,12 +29213,12 @@
       </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -29246,16 +29245,16 @@
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129564285</t>
+          <t>https://artportalen.se/Sighting/128341941</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>133767721</v>
+        <v>129564285</v>
       </c>
       <c r="B253" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29291,10 +29290,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>686845</v>
+        <v>686625</v>
       </c>
       <c r="R253" t="n">
-        <v>6563325</v>
+        <v>6563000</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -29321,12 +29320,12 @@
       </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -29353,38 +29352,38 @@
       <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133767721</t>
+          <t>https://artportalen.se/Sighting/129564285</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>96643458</v>
+        <v>133767721</v>
       </c>
       <c r="B254" t="n">
-        <v>106244</v>
+        <v>99195</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -29394,14 +29393,14 @@
       <c r="N254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Vargklåva mosse S om, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>687154</v>
+        <v>686845</v>
       </c>
       <c r="R254" t="n">
-        <v>6563329</v>
+        <v>6563325</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -29428,12 +29427,12 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -29449,24 +29448,24 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96643458</t>
+          <t>https://artportalen.se/Sighting/133767721</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>96858761</v>
+        <v>96643458</v>
       </c>
       <c r="B255" t="n">
         <v>106244</v>
@@ -29501,17 +29500,17 @@
       <c r="N255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Vargklåva mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>687064</v>
+        <v>687154</v>
       </c>
       <c r="R255" t="n">
-        <v>6563258</v>
+        <v>6563329</v>
       </c>
       <c r="S255" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -29535,17 +29534,12 @@
       </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>Två bestånd</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29572,13 +29566,13 @@
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96858761</t>
+          <t>https://artportalen.se/Sighting/96643458</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>97204577</v>
+        <v>96858761</v>
       </c>
       <c r="B256" t="n">
         <v>106244</v>
@@ -29613,17 +29607,17 @@
       <c r="N256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>SO Norrby mosse, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>687019</v>
+        <v>687064</v>
       </c>
       <c r="R256" t="n">
-        <v>6562889</v>
+        <v>6563258</v>
       </c>
       <c r="S256" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -29647,12 +29641,17 @@
       </c>
       <c r="Y256" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>Två bestånd</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -29668,24 +29667,24 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97204577</t>
+          <t>https://artportalen.se/Sighting/96858761</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>100252927</v>
+        <v>97204577</v>
       </c>
       <c r="B257" t="n">
         <v>106244</v>
@@ -29720,17 +29719,17 @@
       <c r="N257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>SO Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>687152</v>
+        <v>687019</v>
       </c>
       <c r="R257" t="n">
-        <v>6563326</v>
+        <v>6562889</v>
       </c>
       <c r="S257" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -29754,12 +29753,12 @@
       </c>
       <c r="Y257" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -29786,13 +29785,13 @@
       <c r="AY257" t="inlineStr"/>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100252927</t>
+          <t>https://artportalen.se/Sighting/97204577</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>116743172</v>
+        <v>100252927</v>
       </c>
       <c r="B258" t="n">
         <v>106244</v>
@@ -29821,16 +29820,20 @@
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Ungfars kärr, Ungfars kärr, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>687088</v>
+        <v>687152</v>
       </c>
       <c r="R258" t="n">
-        <v>6563243</v>
+        <v>6563326</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29857,12 +29860,12 @@
       </c>
       <c r="Y258" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -29871,30 +29874,31 @@
       <c r="AE258" t="b">
         <v>0</v>
       </c>
+      <c r="AF258" t="inlineStr"/>
       <c r="AG258" t="b">
         <v>0</v>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116743172</t>
+          <t>https://artportalen.se/Sighting/100252927</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>125965889</v>
+        <v>116743172</v>
       </c>
       <c r="B259" t="n">
         <v>106244</v>
@@ -29929,10 +29933,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>687076</v>
+        <v>687088</v>
       </c>
       <c r="R259" t="n">
-        <v>6563220</v>
+        <v>6563243</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -29959,12 +29963,12 @@
       </c>
       <c r="Y259" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -29990,13 +29994,13 @@
       <c r="AY259" t="inlineStr"/>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125965889</t>
+          <t>https://artportalen.se/Sighting/116743172</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>126003574</v>
+        <v>125965889</v>
       </c>
       <c r="B260" t="n">
         <v>106244</v>
@@ -30025,20 +30029,16 @@
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ungfars kärr, Ungfars kärr, Srm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>686803</v>
+        <v>687076</v>
       </c>
       <c r="R260" t="n">
-        <v>6563098</v>
+        <v>6563220</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -30065,12 +30065,12 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -30079,31 +30079,30 @@
       <c r="AE260" t="b">
         <v>0</v>
       </c>
-      <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="b">
         <v>0</v>
       </c>
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126003574</t>
+          <t>https://artportalen.se/Sighting/125965889</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>126061078</v>
+        <v>126003574</v>
       </c>
       <c r="B261" t="n">
         <v>106244</v>
@@ -30132,16 +30131,20 @@
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>687085</v>
+        <v>686803</v>
       </c>
       <c r="R261" t="n">
-        <v>6563229</v>
+        <v>6563098</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -30168,22 +30171,12 @@
       </c>
       <c r="Y261" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z261" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB261" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -30192,30 +30185,31 @@
       <c r="AE261" t="b">
         <v>0</v>
       </c>
+      <c r="AF261" t="inlineStr"/>
       <c r="AG261" t="b">
         <v>0</v>
       </c>
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061078</t>
+          <t>https://artportalen.se/Sighting/126003574</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>126061079</v>
+        <v>126061078</v>
       </c>
       <c r="B262" t="n">
         <v>106244</v>
@@ -30250,10 +30244,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>687082</v>
+        <v>687085</v>
       </c>
       <c r="R262" t="n">
-        <v>6563241</v>
+        <v>6563229</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -30285,7 +30279,7 @@
       </c>
       <c r="Z262" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
@@ -30295,7 +30289,7 @@
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -30321,13 +30315,13 @@
       <c r="AY262" t="inlineStr"/>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061079</t>
+          <t>https://artportalen.se/Sighting/126061078</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>126234373</v>
+        <v>126061079</v>
       </c>
       <c r="B263" t="n">
         <v>106244</v>
@@ -30355,29 +30349,17 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
-      <c r="N263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>686756</v>
+        <v>687082</v>
       </c>
       <c r="R263" t="n">
-        <v>6563092</v>
+        <v>6563241</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -30404,12 +30386,22 @@
       </c>
       <c r="Y263" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -30418,31 +30410,30 @@
       <c r="AE263" t="b">
         <v>0</v>
       </c>
-      <c r="AF263" t="inlineStr"/>
       <c r="AG263" t="b">
         <v>0</v>
       </c>
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234373</t>
+          <t>https://artportalen.se/Sighting/126061079</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>126234937</v>
+        <v>126234373</v>
       </c>
       <c r="B264" t="n">
         <v>106244</v>
@@ -30480,23 +30471,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr"/>
       <c r="N264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>687103</v>
+        <v>686756</v>
       </c>
       <c r="R264" t="n">
-        <v>6563191</v>
+        <v>6563092</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -30555,16 +30542,16 @@
       <c r="AY264" t="inlineStr"/>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234937</t>
+          <t>https://artportalen.se/Sighting/126234373</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>136329900</v>
+        <v>126234937</v>
       </c>
       <c r="B265" t="n">
-        <v>106500</v>
+        <v>106244</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -30589,21 +30576,33 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I265" t="inlineStr"/>
-      <c r="J265" t="inlineStr"/>
-      <c r="K265" t="inlineStr"/>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr"/>
       <c r="N265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>686462</v>
+        <v>687103</v>
       </c>
       <c r="R265" t="n">
-        <v>6563046</v>
+        <v>6563191</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -30630,12 +30629,12 @@
       </c>
       <c r="Y265" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -30651,27 +30650,27 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136329900</t>
+          <t>https://artportalen.se/Sighting/126234937</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>136422457</v>
+        <v>136329900</v>
       </c>
       <c r="B266" t="n">
-        <v>106503</v>
+        <v>106500</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -30707,10 +30706,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>687270</v>
+        <v>686462</v>
       </c>
       <c r="R266" t="n">
-        <v>6563384</v>
+        <v>6563046</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -30737,12 +30736,12 @@
       </c>
       <c r="Y266" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -30769,16 +30768,16 @@
       <c r="AY266" t="inlineStr"/>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136422457</t>
+          <t>https://artportalen.se/Sighting/136329900</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>96643468</v>
+        <v>136422457</v>
       </c>
       <c r="B267" t="n">
-        <v>97989</v>
+        <v>106503</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -30786,46 +30785,38 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr"/>
+      <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr"/>
       <c r="N267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Vargklåva mosse S om, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>687268</v>
+        <v>687270</v>
       </c>
       <c r="R267" t="n">
-        <v>6563319</v>
+        <v>6563384</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -30852,17 +30843,12 @@
       </c>
       <c r="Y267" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
-        </is>
-      </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>Strax nedom klippbrant</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -30878,24 +30864,24 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96643468</t>
+          <t>https://artportalen.se/Sighting/136422457</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>116746465</v>
+        <v>96643468</v>
       </c>
       <c r="B268" t="n">
         <v>97989</v>
@@ -30923,17 +30909,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I268" t="inlineStr"/>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+      <c r="N268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Norrby mosse, Norrby mosse, Srm</t>
+          <t>Vargklåva mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>686888</v>
+        <v>687268</v>
       </c>
       <c r="R268" t="n">
-        <v>6563206</v>
+        <v>6563319</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -30960,12 +30958,17 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>Strax nedom klippbrant</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -30974,33 +30977,34 @@
       <c r="AE268" t="b">
         <v>0</v>
       </c>
+      <c r="AF268" t="inlineStr"/>
       <c r="AG268" t="b">
         <v>0</v>
       </c>
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116746465</t>
+          <t>https://artportalen.se/Sighting/96643468</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>135827249</v>
+        <v>116746465</v>
       </c>
       <c r="B269" t="n">
-        <v>98209</v>
+        <v>97989</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31026,20 +31030,16 @@
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
-      <c r="J269" t="inlineStr"/>
-      <c r="K269" t="inlineStr"/>
-      <c r="L269" t="inlineStr"/>
-      <c r="N269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse, Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>687270</v>
+        <v>686888</v>
       </c>
       <c r="R269" t="n">
-        <v>6563321</v>
+        <v>6563206</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -31066,17 +31066,12 @@
       </c>
       <c r="Y269" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>Återfynd, tidigare rapporterad 2021.</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -31085,34 +31080,33 @@
       <c r="AE269" t="b">
         <v>0</v>
       </c>
-      <c r="AF269" t="inlineStr"/>
       <c r="AG269" t="b">
         <v>0</v>
       </c>
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135827249</t>
+          <t>https://artportalen.se/Sighting/116746465</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>121742517</v>
+        <v>135827249</v>
       </c>
       <c r="B270" t="n">
-        <v>97983</v>
+        <v>98209</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -31120,16 +31114,16 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -31138,16 +31132,20 @@
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
+      <c r="J270" t="inlineStr"/>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Norrby mosse, Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>686859</v>
+        <v>687270</v>
       </c>
       <c r="R270" t="n">
-        <v>6562875</v>
+        <v>6563321</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -31174,12 +31172,17 @@
       </c>
       <c r="Y270" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>Återfynd, tidigare rapporterad 2021.</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -31188,30 +31191,31 @@
       <c r="AE270" t="b">
         <v>0</v>
       </c>
+      <c r="AF270" t="inlineStr"/>
       <c r="AG270" t="b">
         <v>0</v>
       </c>
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121742517</t>
+          <t>https://artportalen.se/Sighting/135827249</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>122928987</v>
+        <v>121742517</v>
       </c>
       <c r="B271" t="n">
         <v>97983</v>
@@ -31240,20 +31244,16 @@
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
-      <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
-      <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Norrby mosse, Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>686389</v>
+        <v>686859</v>
       </c>
       <c r="R271" t="n">
-        <v>6562967</v>
+        <v>6562875</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -31280,22 +31280,12 @@
       </c>
       <c r="Y271" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z271" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB271" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -31310,24 +31300,24 @@
       <c r="AT271" t="inlineStr"/>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122928987</t>
+          <t>https://artportalen.se/Sighting/121742517</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122930294</v>
+        <v>122928987</v>
       </c>
       <c r="B272" t="n">
         <v>97983</v>
@@ -31366,13 +31356,13 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>686824</v>
+        <v>686389</v>
       </c>
       <c r="R272" t="n">
-        <v>6562778</v>
+        <v>6562967</v>
       </c>
       <c r="S272" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T272" t="inlineStr">
         <is>
@@ -31401,7 +31391,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -31411,7 +31401,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -31437,13 +31427,13 @@
       <c r="AY272" t="inlineStr"/>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122930294</t>
+          <t>https://artportalen.se/Sighting/122928987</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>125963374</v>
+        <v>122930294</v>
       </c>
       <c r="B273" t="n">
         <v>97983</v>
@@ -31472,19 +31462,23 @@
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Norrby mosse, Norrby mosse, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>686873</v>
+        <v>686824</v>
       </c>
       <c r="R273" t="n">
-        <v>6562867</v>
+        <v>6562778</v>
       </c>
       <c r="S273" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -31508,12 +31502,22 @@
       </c>
       <c r="Y273" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -31528,24 +31532,24 @@
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125963374</t>
+          <t>https://artportalen.se/Sighting/122930294</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>125976418</v>
+        <v>125963374</v>
       </c>
       <c r="B274" t="n">
         <v>97983</v>
@@ -31574,23 +31578,19 @@
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="N274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Norrby mosse Ö om, Srm</t>
+          <t>Norrby mosse, Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>686836</v>
+        <v>686873</v>
       </c>
       <c r="R274" t="n">
-        <v>6563105</v>
+        <v>6562867</v>
       </c>
       <c r="S274" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -31622,42 +31622,36 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC274" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i skogskärr</t>
-        </is>
-      </c>
       <c r="AD274" t="b">
         <v>0</v>
       </c>
       <c r="AE274" t="b">
         <v>0</v>
       </c>
-      <c r="AF274" t="inlineStr"/>
       <c r="AG274" t="b">
         <v>0</v>
       </c>
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125976418</t>
+          <t>https://artportalen.se/Sighting/125963374</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>126061082</v>
+        <v>125976418</v>
       </c>
       <c r="B275" t="n">
         <v>97983</v>
@@ -31686,19 +31680,23 @@
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse Ö om, Srm</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>687079</v>
+        <v>686836</v>
       </c>
       <c r="R275" t="n">
-        <v>6563240</v>
+        <v>6563105</v>
       </c>
       <c r="S275" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -31725,19 +31723,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z275" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA275" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB275" t="inlineStr">
-        <is>
-          <t>15:22</t>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i skogskärr</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -31746,30 +31739,31 @@
       <c r="AE275" t="b">
         <v>0</v>
       </c>
+      <c r="AF275" t="inlineStr"/>
       <c r="AG275" t="b">
         <v>0</v>
       </c>
       <c r="AT275" t="inlineStr"/>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061082</t>
+          <t>https://artportalen.se/Sighting/125976418</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>126061090</v>
+        <v>126061082</v>
       </c>
       <c r="B276" t="n">
         <v>97983</v>
@@ -31804,10 +31798,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>686871</v>
+        <v>687079</v>
       </c>
       <c r="R276" t="n">
-        <v>6562972</v>
+        <v>6563240</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -31839,7 +31833,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -31849,7 +31843,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -31875,13 +31869,13 @@
       <c r="AY276" t="inlineStr"/>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061090</t>
+          <t>https://artportalen.se/Sighting/126061082</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>126061103</v>
+        <v>126061090</v>
       </c>
       <c r="B277" t="n">
         <v>97983</v>
@@ -31916,10 +31910,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>686811</v>
+        <v>686871</v>
       </c>
       <c r="R277" t="n">
-        <v>6562803</v>
+        <v>6562972</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -31951,7 +31945,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -31961,7 +31955,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -31981,19 +31975,19 @@
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061103</t>
+          <t>https://artportalen.se/Sighting/126061090</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>126061111</v>
+        <v>126061103</v>
       </c>
       <c r="B278" t="n">
         <v>97983</v>
@@ -32028,10 +32022,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>687030</v>
+        <v>686811</v>
       </c>
       <c r="R278" t="n">
-        <v>6562755</v>
+        <v>6562803</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -32063,7 +32057,7 @@
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
@@ -32073,7 +32067,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -32099,16 +32093,16 @@
       <c r="AY278" t="inlineStr"/>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061111</t>
+          <t>https://artportalen.se/Sighting/126061103</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>136347172</v>
+        <v>126061111</v>
       </c>
       <c r="B279" t="n">
-        <v>98223</v>
+        <v>97983</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -32134,20 +32128,16 @@
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="N279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>686861</v>
+        <v>687030</v>
       </c>
       <c r="R279" t="n">
-        <v>6563127</v>
+        <v>6562755</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -32174,12 +32164,22 @@
       </c>
       <c r="Y279" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB279" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -32188,31 +32188,30 @@
       <c r="AE279" t="b">
         <v>0</v>
       </c>
-      <c r="AF279" t="inlineStr"/>
       <c r="AG279" t="b">
         <v>0</v>
       </c>
       <c r="AT279" t="inlineStr"/>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136347172</t>
+          <t>https://artportalen.se/Sighting/126061111</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>136394245</v>
+        <v>136347172</v>
       </c>
       <c r="B280" t="n">
         <v>98223</v>
@@ -32241,19 +32240,23 @@
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="N280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>687263</v>
+        <v>686861</v>
       </c>
       <c r="R280" t="n">
-        <v>6563324</v>
+        <v>6563127</v>
       </c>
       <c r="S280" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -32277,22 +32280,12 @@
       </c>
       <c r="Y280" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z280" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB280" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -32301,33 +32294,34 @@
       <c r="AE280" t="b">
         <v>0</v>
       </c>
+      <c r="AF280" t="inlineStr"/>
       <c r="AG280" t="b">
         <v>0</v>
       </c>
       <c r="AT280" t="inlineStr"/>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136394245</t>
+          <t>https://artportalen.se/Sighting/136347172</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>122929342</v>
+        <v>136394245</v>
       </c>
       <c r="B281" t="n">
-        <v>97986</v>
+        <v>98223</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32335,16 +32329,16 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -32353,23 +32347,19 @@
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="N281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>686569</v>
+        <v>687263</v>
       </c>
       <c r="R281" t="n">
-        <v>6562949</v>
+        <v>6563324</v>
       </c>
       <c r="S281" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -32393,22 +32383,22 @@
       </c>
       <c r="Y281" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -32423,24 +32413,24 @@
       <c r="AT281" t="inlineStr"/>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
       <c r="AZ281" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929342</t>
+          <t>https://artportalen.se/Sighting/136394245</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>126061110</v>
+        <v>122929342</v>
       </c>
       <c r="B282" t="n">
         <v>97986</v>
@@ -32469,19 +32459,23 @@
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
+      <c r="J282" t="inlineStr"/>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
+      <c r="N282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>687029</v>
+        <v>686569</v>
       </c>
       <c r="R282" t="n">
-        <v>6562759</v>
+        <v>6562949</v>
       </c>
       <c r="S282" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
@@ -32505,22 +32499,22 @@
       </c>
       <c r="Y282" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -32535,27 +32529,27 @@
       <c r="AT282" t="inlineStr"/>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
       <c r="AZ282" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061110</t>
+          <t>https://artportalen.se/Sighting/122929342</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>101523203</v>
+        <v>126061110</v>
       </c>
       <c r="B283" t="n">
-        <v>99140</v>
+        <v>97986</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -32563,38 +32557,34 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
-      <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
-      <c r="L283" t="inlineStr"/>
-      <c r="N283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
-          <t>NO Norrby Mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>687050</v>
+        <v>687029</v>
       </c>
       <c r="R283" t="n">
-        <v>6563327</v>
+        <v>6562759</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -32621,12 +32611,22 @@
       </c>
       <c r="Y283" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD283" t="b">
@@ -32635,31 +32635,30 @@
       <c r="AE283" t="b">
         <v>0</v>
       </c>
-      <c r="AF283" t="inlineStr"/>
       <c r="AG283" t="b">
         <v>0</v>
       </c>
       <c r="AT283" t="inlineStr"/>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
       <c r="AZ283" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101523203</t>
+          <t>https://artportalen.se/Sighting/126061110</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>117554655</v>
+        <v>101523203</v>
       </c>
       <c r="B284" t="n">
         <v>99140</v>
@@ -32689,23 +32688,19 @@
       </c>
       <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr"/>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr"/>
       <c r="N284" t="inlineStr"/>
       <c r="P284" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>NO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>687062</v>
+        <v>687050</v>
       </c>
       <c r="R284" t="n">
-        <v>6563349</v>
+        <v>6563327</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -32732,12 +32727,12 @@
       </c>
       <c r="Y284" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AD284" t="b">
@@ -32764,13 +32759,13 @@
       <c r="AY284" t="inlineStr"/>
       <c r="AZ284" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117554655</t>
+          <t>https://artportalen.se/Sighting/101523203</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>126234400</v>
+        <v>117554655</v>
       </c>
       <c r="B285" t="n">
         <v>99140</v>
@@ -32798,16 +32793,8 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I285" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J285" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I285" t="inlineStr"/>
+      <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -32817,14 +32804,14 @@
       <c r="N285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>686788</v>
+        <v>687062</v>
       </c>
       <c r="R285" t="n">
-        <v>6563073</v>
+        <v>6563349</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -32851,12 +32838,12 @@
       </c>
       <c r="Y285" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD285" t="b">
@@ -32872,27 +32859,27 @@
       <c r="AT285" t="inlineStr"/>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
       <c r="AZ285" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234400</t>
+          <t>https://artportalen.se/Sighting/117554655</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>134487623</v>
+        <v>126234400</v>
       </c>
       <c r="B286" t="n">
-        <v>99217</v>
+        <v>99140</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32917,8 +32904,16 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I286" t="inlineStr"/>
-      <c r="J286" t="inlineStr"/>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K286" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -32928,17 +32923,17 @@
       <c r="N286" t="inlineStr"/>
       <c r="P286" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>687067</v>
+        <v>686788</v>
       </c>
       <c r="R286" t="n">
-        <v>6563342</v>
+        <v>6563073</v>
       </c>
       <c r="S286" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T286" t="inlineStr">
         <is>
@@ -32962,17 +32957,12 @@
       </c>
       <c r="Y286" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC286" t="inlineStr">
-        <is>
-          <t>Ett tiotal i blom samt flera plantor med endast blad.  Återfynd.</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -32988,24 +32978,24 @@
       <c r="AT286" t="inlineStr"/>
       <c r="AW286" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
       <c r="AZ286" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134487623</t>
+          <t>https://artportalen.se/Sighting/126234400</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>134487656</v>
+        <v>134487623</v>
       </c>
       <c r="B287" t="n">
         <v>99217</v>
@@ -33048,13 +33038,13 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>686835</v>
+        <v>687067</v>
       </c>
       <c r="R287" t="n">
-        <v>6563212</v>
+        <v>6563342</v>
       </c>
       <c r="S287" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T287" t="inlineStr">
         <is>
@@ -33088,7 +33078,7 @@
       </c>
       <c r="AC287" t="inlineStr">
         <is>
-          <t>2 i blom samt några plantor med endast blad.</t>
+          <t>Ett tiotal i blom samt flera plantor med endast blad.  Återfynd.</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -33115,13 +33105,13 @@
       <c r="AY287" t="inlineStr"/>
       <c r="AZ287" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134487656</t>
+          <t>https://artportalen.se/Sighting/134487623</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>134488457</v>
+        <v>134487656</v>
       </c>
       <c r="B288" t="n">
         <v>99217</v>
@@ -33164,10 +33154,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>687294</v>
+        <v>686835</v>
       </c>
       <c r="R288" t="n">
-        <v>6563391</v>
+        <v>6563212</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -33204,7 +33194,7 @@
       </c>
       <c r="AC288" t="inlineStr">
         <is>
-          <t>2 i blom samt fler med endast blad.</t>
+          <t>2 i blom samt några plantor med endast blad.</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -33231,43 +33221,48 @@
       <c r="AY288" t="inlineStr"/>
       <c r="AZ288" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134488457</t>
+          <t>https://artportalen.se/Sighting/134487656</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>129564006</v>
+        <v>134488457</v>
       </c>
       <c r="B289" t="n">
-        <v>79350</v>
+        <v>99217</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>260591</v>
+        <v>221952</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
       <c r="J289" t="inlineStr"/>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr"/>
       <c r="N289" t="inlineStr"/>
       <c r="P289" t="inlineStr">
         <is>
@@ -33275,10 +33270,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>686681</v>
+        <v>687294</v>
       </c>
       <c r="R289" t="n">
-        <v>6563025</v>
+        <v>6563391</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -33305,19 +33300,24 @@
       </c>
       <c r="Y289" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC289" t="inlineStr">
+        <is>
+          <t>2 i blom samt fler med endast blad.</t>
         </is>
       </c>
       <c r="AD289" t="b">
         <v>0</v>
       </c>
       <c r="AE289" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF289" t="inlineStr"/>
       <c r="AG289" t="b">
@@ -33336,6 +33336,112 @@
       </c>
       <c r="AY289" t="inlineStr"/>
       <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134488457</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>129564006</v>
+      </c>
+      <c r="B290" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr"/>
+      <c r="J290" t="inlineStr"/>
+      <c r="K290" t="inlineStr"/>
+      <c r="N290" t="inlineStr"/>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q290" t="n">
+        <v>686681</v>
+      </c>
+      <c r="R290" t="n">
+        <v>6563025</v>
+      </c>
+      <c r="S290" t="n">
+        <v>10</v>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y290" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD290" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE290" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF290" t="inlineStr"/>
+      <c r="AG290" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT290" t="inlineStr"/>
+      <c r="AW290" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX290" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129564006</t>
         </is>
@@ -33631,6 +33737,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -5771,7 +5771,7 @@
         <v>136557175</v>
       </c>
       <c r="B47" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -2220,7 +2220,7 @@
         <v>137220225</v>
       </c>
       <c r="B15" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>137220403</v>
       </c>
       <c r="B35" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>136947605</v>
       </c>
       <c r="B43" t="n">
-        <v>92817</v>
+        <v>92819</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>136631756</v>
       </c>
       <c r="B58" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>136631891</v>
       </c>
       <c r="B59" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>136631926</v>
       </c>
       <c r="B81" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>136635740</v>
       </c>
       <c r="B85" t="n">
-        <v>91624</v>
+        <v>91626</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>136946030</v>
       </c>
       <c r="B86" t="n">
-        <v>91624</v>
+        <v>91626</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>136778691</v>
       </c>
       <c r="B91" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>136778733</v>
       </c>
       <c r="B92" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>137088961</v>
       </c>
       <c r="B93" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>137089019</v>
       </c>
       <c r="B94" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>136635736</v>
       </c>
       <c r="B112" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
         <v>136635737</v>
       </c>
       <c r="B113" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>136737386</v>
       </c>
       <c r="B120" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>136946079</v>
       </c>
       <c r="B128" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>136767158</v>
       </c>
       <c r="B132" t="n">
-        <v>56895</v>
+        <v>56897</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>136972809</v>
       </c>
       <c r="B136" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>136631248</v>
       </c>
       <c r="B159" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>136632140</v>
       </c>
       <c r="B160" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>136947588</v>
       </c>
       <c r="B161" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>136947615</v>
       </c>
       <c r="B162" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>136973330</v>
       </c>
       <c r="B163" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>137106201</v>
       </c>
       <c r="B164" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>137143261</v>
       </c>
       <c r="B165" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>137220247</v>
       </c>
       <c r="B166" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>136631771</v>
       </c>
       <c r="B168" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>136635739</v>
       </c>
       <c r="B179" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>136767157</v>
       </c>
       <c r="B180" t="n">
-        <v>56888</v>
+        <v>56890</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         <v>136867583</v>
       </c>
       <c r="B181" t="n">
-        <v>56888</v>
+        <v>56890</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>136867591</v>
       </c>
       <c r="B182" t="n">
-        <v>56888</v>
+        <v>56890</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>136767122</v>
       </c>
       <c r="B183" t="n">
-        <v>56900</v>
+        <v>56902</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         <v>136767160</v>
       </c>
       <c r="B184" t="n">
-        <v>56900</v>
+        <v>56902</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>136867584</v>
       </c>
       <c r="B185" t="n">
-        <v>56900</v>
+        <v>56902</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>136867597</v>
       </c>
       <c r="B186" t="n">
-        <v>56900</v>
+        <v>56902</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>136767120</v>
       </c>
       <c r="B187" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>136767159</v>
       </c>
       <c r="B188" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>136867586</v>
       </c>
       <c r="B189" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>136867588</v>
       </c>
       <c r="B190" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>136767162</v>
       </c>
       <c r="B191" t="n">
-        <v>56902</v>
+        <v>56904</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>136867594</v>
       </c>
       <c r="B192" t="n">
-        <v>56902</v>
+        <v>56904</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>136777569</v>
       </c>
       <c r="B199" t="n">
-        <v>58885</v>
+        <v>58887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>137220238</v>
       </c>
       <c r="B281" t="n">
-        <v>98440</v>
+        <v>98442</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -2220,7 +2220,7 @@
         <v>137220225</v>
       </c>
       <c r="B15" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>137220403</v>
       </c>
       <c r="B35" t="n">
-        <v>92768</v>
+        <v>92771</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>136947605</v>
       </c>
       <c r="B43" t="n">
-        <v>92819</v>
+        <v>92822</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>137045816</v>
       </c>
       <c r="B60" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>136946030</v>
       </c>
       <c r="B87" t="n">
-        <v>91626</v>
+        <v>91629</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>136778691</v>
       </c>
       <c r="B92" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>136778733</v>
       </c>
       <c r="B93" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>137045788</v>
       </c>
       <c r="B94" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>137045804</v>
       </c>
       <c r="B95" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>137045811</v>
       </c>
       <c r="B96" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>137045817</v>
       </c>
       <c r="B97" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>137045826</v>
       </c>
       <c r="B98" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>137045864</v>
       </c>
       <c r="B99" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>137045871</v>
       </c>
       <c r="B100" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>137045877</v>
       </c>
       <c r="B101" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>137045887</v>
       </c>
       <c r="B102" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>137088961</v>
       </c>
       <c r="B103" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>137089019</v>
       </c>
       <c r="B104" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>137220238</v>
       </c>
       <c r="B293" t="n">
-        <v>98442</v>
+        <v>98445</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -2220,7 +2220,7 @@
         <v>137220225</v>
       </c>
       <c r="B15" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>137220403</v>
       </c>
       <c r="B35" t="n">
-        <v>92771</v>
+        <v>92781</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>136947605</v>
       </c>
       <c r="B43" t="n">
-        <v>92822</v>
+        <v>92832</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>137045816</v>
       </c>
       <c r="B60" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>136946030</v>
       </c>
       <c r="B87" t="n">
-        <v>91629</v>
+        <v>91639</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>136778691</v>
       </c>
       <c r="B92" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>136778733</v>
       </c>
       <c r="B93" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>137045788</v>
       </c>
       <c r="B94" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>137045804</v>
       </c>
       <c r="B95" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>137045811</v>
       </c>
       <c r="B96" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>137045817</v>
       </c>
       <c r="B97" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>137045826</v>
       </c>
       <c r="B98" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>137045864</v>
       </c>
       <c r="B99" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>137045871</v>
       </c>
       <c r="B100" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>137045877</v>
       </c>
       <c r="B101" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>137045887</v>
       </c>
       <c r="B102" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>137088961</v>
       </c>
       <c r="B103" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>137089019</v>
       </c>
       <c r="B104" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>136737386</v>
       </c>
       <c r="B130" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>136946079</v>
       </c>
       <c r="B138" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>136767158</v>
       </c>
       <c r="B142" t="n">
-        <v>56897</v>
+        <v>56907</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>136972809</v>
       </c>
       <c r="B146" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>136947588</v>
       </c>
       <c r="B171" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>136947615</v>
       </c>
       <c r="B172" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>136973330</v>
       </c>
       <c r="B173" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>137045648</v>
       </c>
       <c r="B174" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>137045793</v>
       </c>
       <c r="B175" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>137106201</v>
       </c>
       <c r="B176" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>137143261</v>
       </c>
       <c r="B177" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>137220247</v>
       </c>
       <c r="B178" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>136767157</v>
       </c>
       <c r="B192" t="n">
-        <v>56890</v>
+        <v>56900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>136867583</v>
       </c>
       <c r="B193" t="n">
-        <v>56890</v>
+        <v>56900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>136867591</v>
       </c>
       <c r="B194" t="n">
-        <v>56890</v>
+        <v>56900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>136767122</v>
       </c>
       <c r="B195" t="n">
-        <v>56902</v>
+        <v>56912</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>136767160</v>
       </c>
       <c r="B196" t="n">
-        <v>56902</v>
+        <v>56912</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>136867584</v>
       </c>
       <c r="B197" t="n">
-        <v>56902</v>
+        <v>56912</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>136867597</v>
       </c>
       <c r="B198" t="n">
-        <v>56902</v>
+        <v>56912</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>136767120</v>
       </c>
       <c r="B199" t="n">
-        <v>56881</v>
+        <v>56891</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>136767159</v>
       </c>
       <c r="B200" t="n">
-        <v>56881</v>
+        <v>56891</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>136867586</v>
       </c>
       <c r="B201" t="n">
-        <v>56881</v>
+        <v>56891</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>136867588</v>
       </c>
       <c r="B202" t="n">
-        <v>56881</v>
+        <v>56891</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>136767162</v>
       </c>
       <c r="B203" t="n">
-        <v>56904</v>
+        <v>56914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>136867594</v>
       </c>
       <c r="B204" t="n">
-        <v>56904</v>
+        <v>56914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>136777569</v>
       </c>
       <c r="B211" t="n">
-        <v>58887</v>
+        <v>58897</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>137220238</v>
       </c>
       <c r="B293" t="n">
-        <v>98445</v>
+        <v>98455</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -2220,7 +2220,7 @@
         <v>137220225</v>
       </c>
       <c r="B15" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>137220403</v>
       </c>
       <c r="B35" t="n">
-        <v>92781</v>
+        <v>92782</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>136947605</v>
       </c>
       <c r="B43" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>137045816</v>
       </c>
       <c r="B60" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>136946030</v>
       </c>
       <c r="B87" t="n">
-        <v>91639</v>
+        <v>91640</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>136778691</v>
       </c>
       <c r="B92" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>136778733</v>
       </c>
       <c r="B93" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>137045788</v>
       </c>
       <c r="B94" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>137045804</v>
       </c>
       <c r="B95" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>137045811</v>
       </c>
       <c r="B96" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>137045817</v>
       </c>
       <c r="B97" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>137045826</v>
       </c>
       <c r="B98" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>137045864</v>
       </c>
       <c r="B99" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>137045871</v>
       </c>
       <c r="B100" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>137045877</v>
       </c>
       <c r="B101" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>137045887</v>
       </c>
       <c r="B102" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>137088961</v>
       </c>
       <c r="B103" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>137089019</v>
       </c>
       <c r="B104" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>137220238</v>
       </c>
       <c r="B293" t="n">
-        <v>98455</v>
+        <v>98456</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -2220,7 +2220,7 @@
         <v>137220225</v>
       </c>
       <c r="B15" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>137220403</v>
       </c>
       <c r="B35" t="n">
-        <v>92782</v>
+        <v>92785</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>136947605</v>
       </c>
       <c r="B43" t="n">
-        <v>92833</v>
+        <v>92836</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>137045816</v>
       </c>
       <c r="B60" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>136946030</v>
       </c>
       <c r="B87" t="n">
-        <v>91640</v>
+        <v>91643</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>136778691</v>
       </c>
       <c r="B92" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>136778733</v>
       </c>
       <c r="B93" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>137045788</v>
       </c>
       <c r="B94" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>137045804</v>
       </c>
       <c r="B95" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>137045811</v>
       </c>
       <c r="B96" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>137045817</v>
       </c>
       <c r="B97" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>137045826</v>
       </c>
       <c r="B98" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>137045864</v>
       </c>
       <c r="B99" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>137045871</v>
       </c>
       <c r="B100" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>137045877</v>
       </c>
       <c r="B101" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>137045887</v>
       </c>
       <c r="B102" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>137088961</v>
       </c>
       <c r="B103" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>137089019</v>
       </c>
       <c r="B104" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>136946079</v>
       </c>
       <c r="B138" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>136767158</v>
       </c>
       <c r="B142" t="n">
-        <v>56907</v>
+        <v>56908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>136972809</v>
       </c>
       <c r="B146" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>136947588</v>
       </c>
       <c r="B171" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>136947615</v>
       </c>
       <c r="B172" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>136973330</v>
       </c>
       <c r="B173" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>137045648</v>
       </c>
       <c r="B174" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>137045793</v>
       </c>
       <c r="B175" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>137106201</v>
       </c>
       <c r="B176" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>137143261</v>
       </c>
       <c r="B177" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>137220247</v>
       </c>
       <c r="B178" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>136767157</v>
       </c>
       <c r="B192" t="n">
-        <v>56900</v>
+        <v>56901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>136867583</v>
       </c>
       <c r="B193" t="n">
-        <v>56900</v>
+        <v>56901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>136867591</v>
       </c>
       <c r="B194" t="n">
-        <v>56900</v>
+        <v>56901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>136767122</v>
       </c>
       <c r="B195" t="n">
-        <v>56912</v>
+        <v>56913</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>136767160</v>
       </c>
       <c r="B196" t="n">
-        <v>56912</v>
+        <v>56913</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>136867584</v>
       </c>
       <c r="B197" t="n">
-        <v>56912</v>
+        <v>56913</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>136867597</v>
       </c>
       <c r="B198" t="n">
-        <v>56912</v>
+        <v>56913</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>136767120</v>
       </c>
       <c r="B199" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>136767159</v>
       </c>
       <c r="B200" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>136867586</v>
       </c>
       <c r="B201" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>136867588</v>
       </c>
       <c r="B202" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>136767162</v>
       </c>
       <c r="B203" t="n">
-        <v>56914</v>
+        <v>56915</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>136867594</v>
       </c>
       <c r="B204" t="n">
-        <v>56914</v>
+        <v>56915</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>136777569</v>
       </c>
       <c r="B211" t="n">
-        <v>58897</v>
+        <v>58899</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>137220238</v>
       </c>
       <c r="B293" t="n">
-        <v>98456</v>
+        <v>98461</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -2220,7 +2220,7 @@
         <v>137220225</v>
       </c>
       <c r="B15" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>137220403</v>
       </c>
       <c r="B35" t="n">
-        <v>92785</v>
+        <v>92787</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>136947605</v>
       </c>
       <c r="B43" t="n">
-        <v>92836</v>
+        <v>92838</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>137045816</v>
       </c>
       <c r="B60" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>136946030</v>
       </c>
       <c r="B87" t="n">
-        <v>91643</v>
+        <v>91645</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>136778691</v>
       </c>
       <c r="B92" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>136778733</v>
       </c>
       <c r="B93" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>137045788</v>
       </c>
       <c r="B94" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>137045804</v>
       </c>
       <c r="B95" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>137045811</v>
       </c>
       <c r="B96" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>137045817</v>
       </c>
       <c r="B97" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>137045826</v>
       </c>
       <c r="B98" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>137045864</v>
       </c>
       <c r="B99" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>137045871</v>
       </c>
       <c r="B100" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>137045877</v>
       </c>
       <c r="B101" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>137045887</v>
       </c>
       <c r="B102" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>137088961</v>
       </c>
       <c r="B103" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>137089019</v>
       </c>
       <c r="B104" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>137220238</v>
       </c>
       <c r="B293" t="n">
-        <v>98461</v>
+        <v>98463</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -2220,7 +2220,7 @@
         <v>137220225</v>
       </c>
       <c r="B15" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>137220403</v>
       </c>
       <c r="B35" t="n">
-        <v>92787</v>
+        <v>92792</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>136947605</v>
       </c>
       <c r="B43" t="n">
-        <v>92838</v>
+        <v>92843</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>137045816</v>
       </c>
       <c r="B60" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>136946030</v>
       </c>
       <c r="B87" t="n">
-        <v>91645</v>
+        <v>91650</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>137045788</v>
       </c>
       <c r="B94" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>137045804</v>
       </c>
       <c r="B95" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>137045811</v>
       </c>
       <c r="B96" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>137045817</v>
       </c>
       <c r="B97" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>137045826</v>
       </c>
       <c r="B98" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>137045864</v>
       </c>
       <c r="B99" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>137045871</v>
       </c>
       <c r="B100" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>137045877</v>
       </c>
       <c r="B101" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>137045887</v>
       </c>
       <c r="B102" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>137088961</v>
       </c>
       <c r="B103" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>137089019</v>
       </c>
       <c r="B104" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>136946079</v>
       </c>
       <c r="B138" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>136947588</v>
       </c>
       <c r="B171" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>136947615</v>
       </c>
       <c r="B172" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>136973330</v>
       </c>
       <c r="B173" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>137045648</v>
       </c>
       <c r="B174" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>137045793</v>
       </c>
       <c r="B175" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>137106201</v>
       </c>
       <c r="B176" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>137143261</v>
       </c>
       <c r="B177" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>137220247</v>
       </c>
       <c r="B178" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>137220238</v>
       </c>
       <c r="B293" t="n">
-        <v>98463</v>
+        <v>98469</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -2220,7 +2220,7 @@
         <v>137220225</v>
       </c>
       <c r="B15" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>137220403</v>
       </c>
       <c r="B35" t="n">
-        <v>92792</v>
+        <v>92804</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>136947605</v>
       </c>
       <c r="B43" t="n">
-        <v>92843</v>
+        <v>92855</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>137045816</v>
       </c>
       <c r="B60" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>136946030</v>
       </c>
       <c r="B87" t="n">
-        <v>91650</v>
+        <v>91662</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>137045788</v>
       </c>
       <c r="B94" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>137045804</v>
       </c>
       <c r="B95" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>137045811</v>
       </c>
       <c r="B96" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>137045817</v>
       </c>
       <c r="B97" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>137045826</v>
       </c>
       <c r="B98" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>137045864</v>
       </c>
       <c r="B99" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>137045871</v>
       </c>
       <c r="B100" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>137045877</v>
       </c>
       <c r="B101" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>137045887</v>
       </c>
       <c r="B102" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>137088961</v>
       </c>
       <c r="B103" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>137089019</v>
       </c>
       <c r="B104" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>137220238</v>
       </c>
       <c r="B293" t="n">
-        <v>98469</v>
+        <v>98481</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -2220,7 +2220,7 @@
         <v>137220225</v>
       </c>
       <c r="B15" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>137220403</v>
       </c>
       <c r="B35" t="n">
-        <v>92804</v>
+        <v>92805</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>136947605</v>
       </c>
       <c r="B43" t="n">
-        <v>92855</v>
+        <v>92856</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>137045816</v>
       </c>
       <c r="B60" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>136946030</v>
       </c>
       <c r="B87" t="n">
-        <v>91662</v>
+        <v>91663</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>137045788</v>
       </c>
       <c r="B94" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>137045804</v>
       </c>
       <c r="B95" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>137045811</v>
       </c>
       <c r="B96" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>137045817</v>
       </c>
       <c r="B97" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>137045826</v>
       </c>
       <c r="B98" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>137045864</v>
       </c>
       <c r="B99" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>137045871</v>
       </c>
       <c r="B100" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>137045877</v>
       </c>
       <c r="B101" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>137045887</v>
       </c>
       <c r="B102" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>137088961</v>
       </c>
       <c r="B103" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>137089019</v>
       </c>
       <c r="B104" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>137220238</v>
       </c>
       <c r="B293" t="n">
-        <v>98481</v>
+        <v>98482</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -2220,7 +2220,7 @@
         <v>137220225</v>
       </c>
       <c r="B15" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>137476341</v>
       </c>
       <c r="B16" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>137477223</v>
       </c>
       <c r="B17" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>137478093</v>
       </c>
       <c r="B18" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>137478379</v>
       </c>
       <c r="B19" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>137478526</v>
       </c>
       <c r="B20" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>137478534</v>
       </c>
       <c r="B21" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>137478552</v>
       </c>
       <c r="B22" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>137220403</v>
       </c>
       <c r="B42" t="n">
-        <v>92808</v>
+        <v>92812</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>136947605</v>
       </c>
       <c r="B50" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>137045816</v>
       </c>
       <c r="B67" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>137479367</v>
       </c>
       <c r="B90" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>136946030</v>
       </c>
       <c r="B95" t="n">
-        <v>91667</v>
+        <v>91670</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>137045788</v>
       </c>
       <c r="B102" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>137045804</v>
       </c>
       <c r="B103" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>137045811</v>
       </c>
       <c r="B104" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>137045817</v>
       </c>
       <c r="B105" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>137045826</v>
       </c>
       <c r="B106" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>137045864</v>
       </c>
       <c r="B107" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>137045871</v>
       </c>
       <c r="B108" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>137045877</v>
       </c>
       <c r="B109" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>137045887</v>
       </c>
       <c r="B110" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>137088961</v>
       </c>
       <c r="B111" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>137089019</v>
       </c>
       <c r="B112" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>136946079</v>
       </c>
       <c r="B146" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>137476360</v>
       </c>
       <c r="B147" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>136945987</v>
       </c>
       <c r="B155" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>136972809</v>
       </c>
       <c r="B156" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>136947588</v>
       </c>
       <c r="B181" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>136947615</v>
       </c>
       <c r="B182" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>136973330</v>
       </c>
       <c r="B183" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>137045648</v>
       </c>
       <c r="B184" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>137045793</v>
       </c>
       <c r="B185" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>137106201</v>
       </c>
       <c r="B186" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>137143261</v>
       </c>
       <c r="B187" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>137220247</v>
       </c>
       <c r="B188" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>137478542</v>
       </c>
       <c r="B189" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>137480533</v>
       </c>
       <c r="B282" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
         <v>137220238</v>
       </c>
       <c r="B305" t="n">
-        <v>98485</v>
+        <v>98489</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
